--- a/research/traditional_assets/database/data/australia/australia_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_chemical_diversified.xlsx
@@ -647,10 +647,10 @@
         <v>-0.05198813628800848</v>
       </c>
       <c r="X2">
-        <v>0.09291483221746358</v>
+        <v>0.09288454156935251</v>
       </c>
       <c r="Y2">
-        <v>-0.1449029685054721</v>
+        <v>-0.144872677857361</v>
       </c>
       <c r="Z2">
         <v>0.9553555309106851</v>
@@ -659,10 +659,10 @@
         <v>0.07342738503597863</v>
       </c>
       <c r="AB2">
-        <v>0.07797810033322249</v>
+        <v>0.07795643507328461</v>
       </c>
       <c r="AC2">
-        <v>-0.004550715297243851</v>
+        <v>-0.004529050037305971</v>
       </c>
       <c r="AD2">
         <v>1355.8</v>
@@ -781,10 +781,10 @@
         <v>-0.05198813628800848</v>
       </c>
       <c r="X3">
-        <v>0.09291483221746358</v>
+        <v>0.09288454156935251</v>
       </c>
       <c r="Y3">
-        <v>-0.1449029685054721</v>
+        <v>-0.144872677857361</v>
       </c>
       <c r="Z3">
         <v>0.9553555309106851</v>
@@ -793,10 +793,10 @@
         <v>0.07342738503597863</v>
       </c>
       <c r="AB3">
-        <v>0.07797810033322249</v>
+        <v>0.07795643507328461</v>
       </c>
       <c r="AC3">
-        <v>-0.004550715297243851</v>
+        <v>-0.004529050037305971</v>
       </c>
       <c r="AD3">
         <v>1355.8</v>
@@ -1133,49 +1133,49 @@
         <v>2.2593984962406</v>
       </c>
       <c r="F2">
-        <v>4.50673637195662</v>
+        <v>4.56133878369642</v>
       </c>
       <c r="G2">
         <v>2.82693911592994</v>
       </c>
       <c r="H2">
-        <v>2.87901793160967</v>
+        <v>2.97829441201001</v>
       </c>
       <c r="I2">
         <v>0.2847541637788</v>
       </c>
       <c r="J2">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="K2">
         <v>3405.5</v>
       </c>
       <c r="L2">
-        <v>3387.72259989474</v>
+        <v>3419.49394907933</v>
       </c>
       <c r="M2">
         <v>4020.2</v>
       </c>
       <c r="N2">
-        <v>4027.39959989474</v>
+        <v>4106.78394907933</v>
       </c>
       <c r="O2">
         <v>1355.8</v>
       </c>
       <c r="P2">
-        <v>1380.777</v>
+        <v>1428.39</v>
       </c>
       <c r="Q2">
-        <v>0.0779781003332225</v>
+        <v>0.07795643507328461</v>
       </c>
       <c r="R2">
-        <v>0.07791240062174611</v>
+        <v>0.0771816047146282</v>
       </c>
       <c r="S2">
         <v>0.04046</v>
       </c>
       <c r="T2">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09291483221746361</v>
+        <v>0.0928845415693525</v>
       </c>
       <c r="X2">
-        <v>0.0931812684813325</v>
+        <v>0.0936694353066117</v>
       </c>
       <c r="Y2">
         <v>1.08740280760629</v>
       </c>
       <c r="Z2">
-        <v>1.09355211405064</v>
+        <v>1.10552968375547</v>
       </c>
       <c r="AA2">
         <v>1355.8</v>
@@ -1230,7 +1230,7 @@
         <v>3405.5</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08264633145864847</v>
+        <v>0.08262264254354745</v>
       </c>
       <c r="C2">
-        <v>4308.20578633954</v>
+        <v>4308.37199480726</v>
       </c>
       <c r="D2">
-        <v>3567.10578633954</v>
+        <v>3567.27199480726</v>
       </c>
       <c r="E2">
         <v>-1355.8</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08264633145864847</v>
+        <v>0.08262264254354745</v>
       </c>
       <c r="T2">
         <v>0.8504074490426664</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0824396924642725</v>
+        <v>0.08240627461591679</v>
       </c>
       <c r="C3">
-        <v>4278.477781612011</v>
+        <v>4279.492598103548</v>
       </c>
       <c r="D3">
-        <v>3584.990781612012</v>
+        <v>3586.005598103548</v>
       </c>
       <c r="E3">
         <v>-1308.187</v>
@@ -1533,37 +1533,37 @@
         <v>360.3</v>
       </c>
       <c r="M3">
-        <v>2.4615921</v>
+        <v>2.3949339</v>
       </c>
       <c r="N3">
-        <v>357.8384079</v>
+        <v>357.9050661</v>
       </c>
       <c r="O3">
-        <v>107.35152237</v>
+        <v>107.37151983</v>
       </c>
       <c r="P3">
-        <v>250.48688553</v>
+        <v>250.53354627</v>
       </c>
       <c r="Q3">
-        <v>489.68688553</v>
+        <v>489.73354627</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08290686107502274</v>
+        <v>0.08288300466254223</v>
       </c>
       <c r="T3">
         <v>0.8564204310055943</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.3686855348618</v>
+        <v>150.442565450345</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08223305346989657</v>
+        <v>0.08218990668828616</v>
       </c>
       <c r="C4">
-        <v>4248.930026620819</v>
+        <v>4250.810999960111</v>
       </c>
       <c r="D4">
-        <v>3603.056026620819</v>
+        <v>3604.93699996011</v>
       </c>
       <c r="E4">
         <v>-1260.574</v>
@@ -1615,37 +1615,37 @@
         <v>360.3</v>
       </c>
       <c r="M4">
-        <v>4.923184200000001</v>
+        <v>4.7898678</v>
       </c>
       <c r="N4">
-        <v>355.3768158</v>
+        <v>355.5101322</v>
       </c>
       <c r="O4">
-        <v>106.61304474</v>
+        <v>106.65303966</v>
       </c>
       <c r="P4">
-        <v>248.76377106</v>
+        <v>248.85709254</v>
       </c>
       <c r="Q4">
-        <v>487.96377106</v>
+        <v>488.05709254</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08317270762234344</v>
+        <v>0.08314868029416955</v>
       </c>
       <c r="T4">
         <v>0.862556126886133</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.18434276743088</v>
+        <v>75.2212827251725</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08202641447552063</v>
+        <v>0.08197353876065552</v>
       </c>
       <c r="C5">
-        <v>4219.565260073808</v>
+        <v>4222.330349684049</v>
       </c>
       <c r="D5">
-        <v>3621.304260073807</v>
+        <v>3624.069349684049</v>
       </c>
       <c r="E5">
         <v>-1212.961</v>
@@ -1697,37 +1697,37 @@
         <v>360.3</v>
       </c>
       <c r="M5">
-        <v>7.3847763</v>
+        <v>7.1848017</v>
       </c>
       <c r="N5">
-        <v>352.9152237</v>
+        <v>353.1151983</v>
       </c>
       <c r="O5">
-        <v>105.87456711</v>
+        <v>105.93455949</v>
       </c>
       <c r="P5">
-        <v>247.04065659</v>
+        <v>247.18063881</v>
       </c>
       <c r="Q5">
-        <v>486.24065659</v>
+        <v>486.38063881</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08344403554177385</v>
+        <v>0.08341983377387167</v>
       </c>
       <c r="T5">
         <v>0.8688183319600848</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.78956184495393</v>
+        <v>50.14752181678168</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08181977548114466</v>
+        <v>0.08175717083302488</v>
       </c>
       <c r="C6">
-        <v>4190.38627644369</v>
+        <v>4194.053863795993</v>
       </c>
       <c r="D6">
-        <v>3639.73827644369</v>
+        <v>3643.405863795992</v>
       </c>
       <c r="E6">
         <v>-1165.348</v>
@@ -1779,37 +1779,37 @@
         <v>360.3</v>
       </c>
       <c r="M6">
-        <v>9.846368400000001</v>
+        <v>9.579735599999999</v>
       </c>
       <c r="N6">
-        <v>350.4536316</v>
+        <v>350.7202644</v>
       </c>
       <c r="O6">
-        <v>105.13608948</v>
+        <v>105.21607932</v>
       </c>
       <c r="P6">
-        <v>245.31754212</v>
+        <v>245.50418508</v>
       </c>
       <c r="Q6">
-        <v>484.51754212</v>
+        <v>484.70418508</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08372101612619237</v>
+        <v>0.08369663628440091</v>
       </c>
       <c r="T6">
         <v>0.8752109996397441</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.59217138371544</v>
+        <v>37.61064136258626</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08161313648676874</v>
+        <v>0.08154080290539424</v>
       </c>
       <c r="C7">
-        <v>4161.395927394634</v>
+        <v>4165.98482783283</v>
       </c>
       <c r="D7">
-        <v>3658.360927394633</v>
+        <v>3662.94982783283</v>
       </c>
       <c r="E7">
         <v>-1117.735</v>
@@ -1861,37 +1861,37 @@
         <v>360.3</v>
       </c>
       <c r="M7">
-        <v>12.3079605</v>
+        <v>11.9746695</v>
       </c>
       <c r="N7">
-        <v>347.9920395</v>
+        <v>348.3253305</v>
       </c>
       <c r="O7">
-        <v>104.39761185</v>
+        <v>104.49759915</v>
       </c>
       <c r="P7">
-        <v>243.59442765</v>
+        <v>243.82773135</v>
       </c>
       <c r="Q7">
-        <v>482.79442765</v>
+        <v>483.02773135</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08400382788080919</v>
+        <v>0.08397926621620447</v>
       </c>
       <c r="T7">
         <v>0.8817382497968698</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.27373710697236</v>
+        <v>30.088513090069</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0814064974923928</v>
+        <v>0.08132443497776361</v>
       </c>
       <c r="C8">
-        <v>4132.597123252898</v>
+        <v>4138.126598208782</v>
       </c>
       <c r="D8">
-        <v>3677.175123252898</v>
+        <v>3682.704598208781</v>
       </c>
       <c r="E8">
         <v>-1070.122</v>
@@ -1943,37 +1943,37 @@
         <v>360.3</v>
       </c>
       <c r="M8">
-        <v>14.7695526</v>
+        <v>14.3696034</v>
       </c>
       <c r="N8">
-        <v>345.5304474</v>
+        <v>345.9303966</v>
       </c>
       <c r="O8">
-        <v>103.65913422</v>
+        <v>103.77911898</v>
       </c>
       <c r="P8">
-        <v>241.87131318</v>
+        <v>242.15127762</v>
       </c>
       <c r="Q8">
-        <v>481.07131318</v>
+        <v>481.35127762</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08429265690680085</v>
+        <v>0.08426790955081234</v>
       </c>
       <c r="T8">
         <v>0.8884043776169132</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.39478092247696</v>
+        <v>25.07376090839083</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08119985849801685</v>
+        <v>0.08110806705013296</v>
       </c>
       <c r="C9">
-        <v>4103.992834523056</v>
+        <v>4110.482604137019</v>
       </c>
       <c r="D9">
-        <v>3696.183834523057</v>
+        <v>3702.673604137019</v>
       </c>
       <c r="E9">
         <v>-1022.509</v>
@@ -2025,37 +2025,37 @@
         <v>360.3</v>
       </c>
       <c r="M9">
-        <v>17.2311447</v>
+        <v>16.7645373</v>
       </c>
       <c r="N9">
-        <v>343.0688553</v>
+        <v>343.5354627</v>
       </c>
       <c r="O9">
-        <v>102.92065659</v>
+        <v>103.06063881</v>
       </c>
       <c r="P9">
-        <v>240.14819871</v>
+        <v>240.47482389</v>
       </c>
       <c r="Q9">
-        <v>479.34819871</v>
+        <v>479.67482389</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08458769730969554</v>
+        <v>0.08456276026896017</v>
       </c>
       <c r="T9">
         <v>0.8952138630244844</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.90981221926597</v>
+        <v>21.491795064335</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08099321950364091</v>
+        <v>0.08089169912250231</v>
       </c>
       <c r="C10">
-        <v>4075.586093451499</v>
+        <v>4083.056349614134</v>
       </c>
       <c r="D10">
-        <v>3715.390093451499</v>
+        <v>3722.860349614134</v>
       </c>
       <c r="E10">
         <v>-974.8959999999997</v>
@@ -2107,37 +2107,37 @@
         <v>360.3</v>
       </c>
       <c r="M10">
-        <v>19.6927368</v>
+        <v>19.1594712</v>
       </c>
       <c r="N10">
-        <v>340.6072632</v>
+        <v>341.1405288</v>
       </c>
       <c r="O10">
-        <v>102.18217896</v>
+        <v>102.34215864</v>
       </c>
       <c r="P10">
-        <v>238.42508424</v>
+        <v>238.79837016</v>
       </c>
       <c r="Q10">
-        <v>477.62508424</v>
+        <v>477.99837016</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08488915163439228</v>
+        <v>0.08486402078532861</v>
       </c>
       <c r="T10">
         <v>0.9021713807235244</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.29608569185772</v>
+        <v>18.80532068129313</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08078658050926496</v>
+        <v>0.08067533119487168</v>
       </c>
       <c r="C11">
-        <v>4047.379995638947</v>
+        <v>4055.851415469894</v>
       </c>
       <c r="D11">
-        <v>3734.796995638947</v>
+        <v>3743.268415469894</v>
       </c>
       <c r="E11">
         <v>-927.2829999999998</v>
@@ -2189,37 +2189,37 @@
         <v>360.3</v>
       </c>
       <c r="M11">
-        <v>22.1543289</v>
+        <v>21.5544051</v>
       </c>
       <c r="N11">
-        <v>338.1456711</v>
+        <v>338.7455949</v>
       </c>
       <c r="O11">
-        <v>101.44370133</v>
+        <v>101.62367847</v>
       </c>
       <c r="P11">
-        <v>236.70196977</v>
+        <v>237.12191643</v>
       </c>
       <c r="Q11">
-        <v>475.90196977</v>
+        <v>476.32191643</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08519723132886259</v>
+        <v>0.08517190241194689</v>
       </c>
       <c r="T11">
         <v>0.9092818108994664</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.26318728165131</v>
+        <v>16.71584060559389</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08057994151488901</v>
+        <v>0.08045896326724103</v>
       </c>
       <c r="C12">
-        <v>4019.377701703752</v>
+        <v>4028.871461484778</v>
       </c>
       <c r="D12">
-        <v>3754.407701703752</v>
+        <v>3763.901461484778</v>
       </c>
       <c r="E12">
         <v>-879.6699999999998</v>
@@ -2271,37 +2271,37 @@
         <v>360.3</v>
       </c>
       <c r="M12">
-        <v>24.615921</v>
+        <v>23.949339</v>
       </c>
       <c r="N12">
-        <v>335.684079</v>
+        <v>336.350661</v>
       </c>
       <c r="O12">
-        <v>100.7052237</v>
+        <v>100.9051983</v>
       </c>
       <c r="P12">
-        <v>234.9788553</v>
+        <v>235.4454627</v>
       </c>
       <c r="Q12">
-        <v>474.1788553</v>
+        <v>474.6454627</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08551215723876557</v>
+        <v>0.08548662585249003</v>
       </c>
       <c r="T12">
         <v>0.9165502506348737</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.63686855348618</v>
+        <v>15.0442565450345</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08037330252051307</v>
+        <v>0.08024259533961038</v>
       </c>
       <c r="C13">
-        <v>3991.582438997886</v>
+        <v>4002.120228577931</v>
       </c>
       <c r="D13">
-        <v>3774.225438997885</v>
+        <v>3784.763228577931</v>
       </c>
       <c r="E13">
         <v>-832.0569999999998</v>
@@ -2353,37 +2353,37 @@
         <v>360.3</v>
       </c>
       <c r="M13">
-        <v>27.0775131</v>
+        <v>26.3442729</v>
       </c>
       <c r="N13">
-        <v>333.2224869</v>
+        <v>333.9557271</v>
       </c>
       <c r="O13">
-        <v>99.96674607000001</v>
+        <v>100.18671813</v>
       </c>
       <c r="P13">
-        <v>233.25574083</v>
+        <v>233.76900897</v>
       </c>
       <c r="Q13">
-        <v>472.45574083</v>
+        <v>472.96900897</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08583416013540794</v>
+        <v>0.0858084217298993</v>
       </c>
       <c r="T13">
         <v>0.9239820260946724</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.30624413953289</v>
+        <v>13.67659685912227</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08025906352613713</v>
+        <v>0.08015222741197975</v>
       </c>
       <c r="C14">
-        <v>3955.015610309872</v>
+        <v>3963.288947227009</v>
       </c>
       <c r="D14">
-        <v>3785.271610309871</v>
+        <v>3793.544947227009</v>
       </c>
       <c r="E14">
         <v>-784.4439999999998</v>
@@ -2435,37 +2435,37 @@
         <v>360.3</v>
       </c>
       <c r="M14">
-        <v>30.1675968</v>
+        <v>29.5962408</v>
       </c>
       <c r="N14">
-        <v>330.1324032</v>
+        <v>330.7037592</v>
       </c>
       <c r="O14">
-        <v>99.03972096</v>
+        <v>99.21112776000001</v>
       </c>
       <c r="P14">
-        <v>231.09268224</v>
+        <v>231.49263144</v>
       </c>
       <c r="Q14">
-        <v>470.29268224</v>
+        <v>470.69263144</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08616348127970128</v>
+        <v>0.08613753114997699</v>
       </c>
       <c r="T14">
         <v>0.9315827055421937</v>
       </c>
       <c r="U14">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.94327815996268</v>
+        <v>12.17384337540598</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08006012453176117</v>
+        <v>0.07994635948434911</v>
       </c>
       <c r="C15">
-        <v>3926.793853897051</v>
+        <v>3935.834628260126</v>
       </c>
       <c r="D15">
-        <v>3804.662853897051</v>
+        <v>3813.703628260126</v>
       </c>
       <c r="E15">
         <v>-736.8309999999998</v>
@@ -2517,37 +2517,37 @@
         <v>360.3</v>
       </c>
       <c r="M15">
-        <v>32.6815632</v>
+        <v>32.0625942</v>
       </c>
       <c r="N15">
-        <v>327.6184368</v>
+        <v>328.2374058</v>
       </c>
       <c r="O15">
-        <v>98.28553104000001</v>
+        <v>98.47122174</v>
       </c>
       <c r="P15">
-        <v>229.33290576</v>
+        <v>229.76618406</v>
       </c>
       <c r="Q15">
-        <v>468.53290576</v>
+        <v>468.96618406</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08650037302501284</v>
+        <v>0.08647420630384954</v>
       </c>
       <c r="T15">
         <v>0.9393581132528763</v>
       </c>
       <c r="U15">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.02456445535017</v>
+        <v>11.23739388499013</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07986118553738522</v>
+        <v>0.07974049155671845</v>
       </c>
       <c r="C16">
-        <v>3898.771795982983</v>
+        <v>3908.59569801432</v>
       </c>
       <c r="D16">
-        <v>3824.253795982983</v>
+        <v>3834.077698014319</v>
       </c>
       <c r="E16">
         <v>-689.2179999999997</v>
@@ -2599,37 +2599,37 @@
         <v>360.3</v>
       </c>
       <c r="M16">
-        <v>35.19552960000001</v>
+        <v>34.5289476</v>
       </c>
       <c r="N16">
-        <v>325.1044704</v>
+        <v>325.7710524</v>
       </c>
       <c r="O16">
-        <v>97.53134112000001</v>
+        <v>97.73131572000001</v>
       </c>
       <c r="P16">
-        <v>227.57312928</v>
+        <v>228.03973668</v>
       </c>
       <c r="Q16">
-        <v>466.77312928</v>
+        <v>467.23973668</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08684509946207584</v>
+        <v>0.08681871111246332</v>
       </c>
       <c r="T16">
         <v>0.9473143443986911</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.2370955656823</v>
+        <v>10.43472289320512</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07989324654300929</v>
+        <v>0.07971312362908781</v>
       </c>
       <c r="C17">
-        <v>3847.987893954464</v>
+        <v>3863.707616570362</v>
       </c>
       <c r="D17">
-        <v>3821.082893954464</v>
+        <v>3836.802616570362</v>
       </c>
       <c r="E17">
         <v>-641.6049999999999</v>
@@ -2681,37 +2681,37 @@
         <v>360.3</v>
       </c>
       <c r="M17">
-        <v>39.280725</v>
+        <v>38.20943249999999</v>
       </c>
       <c r="N17">
-        <v>321.019275</v>
+        <v>322.0905675</v>
       </c>
       <c r="O17">
-        <v>96.30578249999999</v>
+        <v>96.62717025000001</v>
       </c>
       <c r="P17">
-        <v>224.7134925</v>
+        <v>225.46339725</v>
       </c>
       <c r="Q17">
-        <v>463.9134925</v>
+        <v>464.66339725</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.0871979371094227</v>
+        <v>0.0871713219165739</v>
       </c>
       <c r="T17">
         <v>0.9554577809832311</v>
       </c>
       <c r="U17">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.172437626851337</v>
+        <v>9.429608775267733</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07970970754863334</v>
+        <v>0.07951915570145716</v>
       </c>
       <c r="C18">
-        <v>3818.598744148076</v>
+        <v>3835.51881922453</v>
       </c>
       <c r="D18">
-        <v>3839.306744148075</v>
+        <v>3856.22681922453</v>
       </c>
       <c r="E18">
         <v>-593.9919999999998</v>
@@ -2763,37 +2763,37 @@
         <v>360.3</v>
       </c>
       <c r="M18">
-        <v>41.89944</v>
+        <v>40.756728</v>
       </c>
       <c r="N18">
-        <v>318.40056</v>
+        <v>319.543272</v>
       </c>
       <c r="O18">
-        <v>95.52016800000001</v>
+        <v>95.8629816</v>
       </c>
       <c r="P18">
-        <v>222.880392</v>
+        <v>223.6802904</v>
       </c>
       <c r="Q18">
-        <v>462.080392</v>
+        <v>462.8802904</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08755917565313492</v>
+        <v>0.08753232821602044</v>
       </c>
       <c r="T18">
         <v>0.963795108915022</v>
       </c>
       <c r="U18">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.59916027517313</v>
+        <v>8.840258226813498</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07952616855425738</v>
+        <v>0.07932518777382652</v>
       </c>
       <c r="C19">
-        <v>3789.384256990004</v>
+        <v>3807.527696621855</v>
       </c>
       <c r="D19">
-        <v>3857.705256990003</v>
+        <v>3875.848696621854</v>
       </c>
       <c r="E19">
         <v>-546.3789999999998</v>
@@ -2845,37 +2845,37 @@
         <v>360.3</v>
       </c>
       <c r="M19">
-        <v>44.518155</v>
+        <v>43.3040235</v>
       </c>
       <c r="N19">
-        <v>315.781845</v>
+        <v>316.9959765</v>
       </c>
       <c r="O19">
-        <v>94.7345535</v>
+        <v>95.09879294999999</v>
       </c>
       <c r="P19">
-        <v>221.0472915</v>
+        <v>221.89718355</v>
       </c>
       <c r="Q19">
-        <v>460.2472915</v>
+        <v>461.09718355</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08792911874006915</v>
+        <v>0.0879020334624416</v>
       </c>
       <c r="T19">
         <v>0.9723333363150488</v>
       </c>
       <c r="U19">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.093327317810004</v>
+        <v>8.320243037000939</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07953162955988145</v>
+        <v>0.07913121984619589</v>
       </c>
       <c r="C20">
-        <v>3741.22128406759</v>
+        <v>3779.737281716964</v>
       </c>
       <c r="D20">
-        <v>3857.15528406759</v>
+        <v>3895.671281716964</v>
       </c>
       <c r="E20">
         <v>-498.7659999999998</v>
@@ -2927,45 +2927,45 @@
         <v>360.3</v>
       </c>
       <c r="M20">
-        <v>48.422421</v>
+        <v>45.851319</v>
       </c>
       <c r="N20">
-        <v>311.877579</v>
+        <v>314.448681</v>
       </c>
       <c r="O20">
-        <v>93.56327370000001</v>
+        <v>94.33460430000001</v>
       </c>
       <c r="P20">
-        <v>218.3143053</v>
+        <v>220.1140767</v>
       </c>
       <c r="Q20">
-        <v>457.5143053</v>
+        <v>459.3140767</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08830808482912372</v>
+        <v>0.08828075590999498</v>
       </c>
       <c r="T20">
         <v>0.9810798131638565</v>
       </c>
       <c r="U20">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03955</v>
+        <v>0.03745</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.440767986383829</v>
+        <v>7.858007312723109</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07935859056550551</v>
+        <v>0.07904365191856526</v>
       </c>
       <c r="C21">
-        <v>3711.111467783897</v>
+        <v>3741.139885889275</v>
       </c>
       <c r="D21">
-        <v>3874.658467783897</v>
+        <v>3904.686885889275</v>
       </c>
       <c r="E21">
         <v>-451.1529999999999</v>
@@ -3009,37 +3009,37 @@
         <v>360.3</v>
       </c>
       <c r="M21">
-        <v>51.1125555</v>
+        <v>49.12233209999999</v>
       </c>
       <c r="N21">
-        <v>309.1874445</v>
+        <v>311.1776679</v>
       </c>
       <c r="O21">
-        <v>92.75623335</v>
+        <v>93.35330037</v>
       </c>
       <c r="P21">
-        <v>216.43121115</v>
+        <v>217.82436753</v>
       </c>
       <c r="Q21">
-        <v>455.63121115</v>
+        <v>457.02436753</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08869640810556234</v>
+        <v>0.0886688295290929</v>
       </c>
       <c r="T21">
         <v>0.990042252403993</v>
       </c>
       <c r="U21">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.049148618679417</v>
+        <v>7.334749483524624</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07918555157112957</v>
+        <v>0.0788552839909346</v>
       </c>
       <c r="C22">
-        <v>3681.161229207871</v>
+        <v>3713.062544100439</v>
       </c>
       <c r="D22">
-        <v>3892.321229207871</v>
+        <v>3924.222544100438</v>
       </c>
       <c r="E22">
         <v>-403.5399999999998</v>
@@ -3091,37 +3091,37 @@
         <v>360.3</v>
       </c>
       <c r="M22">
-        <v>53.80269</v>
+        <v>51.707718</v>
       </c>
       <c r="N22">
-        <v>306.49731</v>
+        <v>308.592282</v>
       </c>
       <c r="O22">
-        <v>91.94919300000001</v>
+        <v>92.5776846</v>
       </c>
       <c r="P22">
-        <v>214.548117</v>
+        <v>216.0145974</v>
       </c>
       <c r="Q22">
-        <v>453.748117</v>
+        <v>455.2145974</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08909443946391196</v>
+        <v>0.08906660498866825</v>
       </c>
       <c r="T22">
         <v>0.9992287526251331</v>
       </c>
       <c r="U22">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.696691187745446</v>
+        <v>6.968012009348392</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07901251257675362</v>
+        <v>0.07866691606330398</v>
       </c>
       <c r="C23">
-        <v>3651.372760654356</v>
+        <v>3685.181664132196</v>
       </c>
       <c r="D23">
-        <v>3910.145760654355</v>
+        <v>3943.954664132195</v>
       </c>
       <c r="E23">
         <v>-355.9269999999999</v>
@@ -3173,37 +3173,37 @@
         <v>360.3</v>
       </c>
       <c r="M23">
-        <v>56.4928245</v>
+        <v>54.2931039</v>
       </c>
       <c r="N23">
-        <v>303.8071755</v>
+        <v>306.0068961</v>
       </c>
       <c r="O23">
-        <v>91.14215265</v>
+        <v>91.80206883</v>
       </c>
       <c r="P23">
-        <v>212.66502285</v>
+        <v>214.20482727</v>
       </c>
       <c r="Q23">
-        <v>451.86502285</v>
+        <v>453.40482727</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0895025475655109</v>
+        <v>0.089474450713043</v>
       </c>
       <c r="T23">
         <v>1.008647822472124</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.377801131186139</v>
+        <v>6.636201913665135</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07905507358237766</v>
+        <v>0.07847854813567333</v>
       </c>
       <c r="C24">
-        <v>3599.360482763411</v>
+        <v>3657.500224561374</v>
       </c>
       <c r="D24">
-        <v>3905.74648276341</v>
+        <v>3963.886224561374</v>
       </c>
       <c r="E24">
         <v>-308.3139999999999</v>
@@ -3255,45 +3255,45 @@
         <v>360.3</v>
       </c>
       <c r="M24">
-        <v>60.6494394</v>
+        <v>56.8784898</v>
       </c>
       <c r="N24">
-        <v>299.6505606</v>
+        <v>303.4215102</v>
       </c>
       <c r="O24">
-        <v>89.89516818</v>
+        <v>91.02645305999999</v>
       </c>
       <c r="P24">
-        <v>209.75539242</v>
+        <v>212.39505714</v>
       </c>
       <c r="Q24">
-        <v>448.95539242</v>
+        <v>451.59505714</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08992111997740726</v>
+        <v>0.089892754020094</v>
       </c>
       <c r="T24">
         <v>1.018308406930577</v>
       </c>
       <c r="U24">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.04053</v>
+        <v>0.03801</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.940697944851903</v>
+        <v>6.334556372134901</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07889183458800172</v>
+        <v>0.07845118020804269</v>
       </c>
       <c r="C25">
-        <v>3568.67458627106</v>
+        <v>3612.799849194063</v>
       </c>
       <c r="D25">
-        <v>3922.673586271059</v>
+        <v>3966.798849194063</v>
       </c>
       <c r="E25">
         <v>-260.7009999999998</v>
@@ -3337,37 +3337,37 @@
         <v>360.3</v>
       </c>
       <c r="M25">
-        <v>63.4062321</v>
+        <v>60.55897470000001</v>
       </c>
       <c r="N25">
-        <v>296.8937679</v>
+        <v>299.7410253</v>
       </c>
       <c r="O25">
-        <v>89.06813036999999</v>
+        <v>89.92230758999999</v>
       </c>
       <c r="P25">
-        <v>207.82563753</v>
+        <v>209.81871771</v>
       </c>
       <c r="Q25">
-        <v>447.02563753</v>
+        <v>449.01871771</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09035056440000223</v>
+        <v>0.09032192234810738</v>
       </c>
       <c r="T25">
         <v>1.028219915660678</v>
       </c>
       <c r="U25">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.682406729858341</v>
+        <v>5.949572326560541</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07872859559362579</v>
+        <v>0.07826981228041203</v>
       </c>
       <c r="C26">
-        <v>3538.136049069648</v>
+        <v>3584.597587068912</v>
       </c>
       <c r="D26">
-        <v>3939.748049069648</v>
+        <v>3986.209587068911</v>
       </c>
       <c r="E26">
         <v>-213.088</v>
@@ -3419,37 +3419,37 @@
         <v>360.3</v>
       </c>
       <c r="M26">
-        <v>66.16302479999999</v>
+        <v>63.1919736</v>
       </c>
       <c r="N26">
-        <v>294.1369752000001</v>
+        <v>297.1080264</v>
       </c>
       <c r="O26">
-        <v>88.24109256000001</v>
+        <v>89.13240792000001</v>
       </c>
       <c r="P26">
-        <v>205.89588264</v>
+        <v>207.97561848</v>
       </c>
       <c r="Q26">
-        <v>445.09588264</v>
+        <v>447.17561848</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09079130999161286</v>
+        <v>0.09076238457948951</v>
       </c>
       <c r="T26">
         <v>1.038392253567887</v>
       </c>
       <c r="U26">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.445639782780912</v>
+        <v>5.70167347962052</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07856535659924983</v>
+        <v>0.07808844435278139</v>
       </c>
       <c r="C27">
-        <v>3507.746803831209</v>
+        <v>3556.586224208903</v>
       </c>
       <c r="D27">
-        <v>3956.971803831208</v>
+        <v>4005.811224208903</v>
       </c>
       <c r="E27">
         <v>-165.4749999999999</v>
@@ -3501,37 +3501,37 @@
         <v>360.3</v>
       </c>
       <c r="M27">
-        <v>68.91981749999999</v>
+        <v>65.8249725</v>
       </c>
       <c r="N27">
-        <v>291.3801825</v>
+        <v>294.4750275</v>
       </c>
       <c r="O27">
-        <v>87.41405475000001</v>
+        <v>88.34250824999999</v>
       </c>
       <c r="P27">
-        <v>203.9661277500001</v>
+        <v>206.13251925</v>
       </c>
       <c r="Q27">
-        <v>443.16612775</v>
+        <v>445.33251925</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09124380879899978</v>
+        <v>0.09121459247037519</v>
       </c>
       <c r="T27">
         <v>1.048835853819289</v>
       </c>
       <c r="U27">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.227814191469675</v>
+        <v>5.473606540435699</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07840211760487388</v>
+        <v>0.07790707642515074</v>
       </c>
       <c r="C28">
-        <v>3477.508817173127</v>
+        <v>3528.768590693171</v>
       </c>
       <c r="D28">
-        <v>3974.346817173127</v>
+        <v>4025.606590693171</v>
       </c>
       <c r="E28">
         <v>-117.8619999999999</v>
@@ -3583,37 +3583,37 @@
         <v>360.3</v>
       </c>
       <c r="M28">
-        <v>71.6766102</v>
+        <v>68.45797140000001</v>
       </c>
       <c r="N28">
-        <v>288.6233898</v>
+        <v>291.8420286</v>
       </c>
       <c r="O28">
-        <v>86.58701694000001</v>
+        <v>87.55260858</v>
       </c>
       <c r="P28">
-        <v>202.03637286</v>
+        <v>204.28942002</v>
       </c>
       <c r="Q28">
-        <v>441.23637286</v>
+        <v>443.48942002</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09170853730388362</v>
+        <v>0.09167902219614966</v>
       </c>
       <c r="T28">
         <v>1.059561713536944</v>
       </c>
       <c r="U28">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.026744414874687</v>
+        <v>5.263083211957402</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07823887861049793</v>
+        <v>0.07772570849752011</v>
       </c>
       <c r="C29">
-        <v>3447.424090406697</v>
+        <v>3501.147572819838</v>
       </c>
       <c r="D29">
-        <v>3991.875090406696</v>
+        <v>4045.598572819837</v>
       </c>
       <c r="E29">
         <v>-70.2489999999998</v>
@@ -3665,37 +3665,37 @@
         <v>360.3</v>
       </c>
       <c r="M29">
-        <v>74.4334029</v>
+        <v>71.09097030000001</v>
       </c>
       <c r="N29">
-        <v>285.8665971</v>
+        <v>289.2090297</v>
       </c>
       <c r="O29">
-        <v>85.75997913</v>
+        <v>86.76270890999999</v>
       </c>
       <c r="P29">
-        <v>200.10661797</v>
+        <v>202.44632079</v>
       </c>
       <c r="Q29">
-        <v>439.30661797</v>
+        <v>441.64632079</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09218599809657252</v>
+        <v>0.09215617602400016</v>
       </c>
       <c r="T29">
         <v>1.070581432424946</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.840568695805255</v>
+        <v>5.068154204107127</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07807563961612199</v>
+        <v>0.07754434056988946</v>
       </c>
       <c r="C30">
-        <v>3417.494660305573</v>
+        <v>3473.726114508978</v>
       </c>
       <c r="D30">
-        <v>4009.558660305573</v>
+        <v>4065.790114508977</v>
       </c>
       <c r="E30">
         <v>-22.63599999999974</v>
@@ -3747,37 +3747,37 @@
         <v>360.3</v>
       </c>
       <c r="M30">
-        <v>77.19019560000001</v>
+        <v>73.72396920000001</v>
       </c>
       <c r="N30">
-        <v>283.1098044</v>
+        <v>286.5760308</v>
       </c>
       <c r="O30">
-        <v>84.93294132000001</v>
+        <v>85.97280924</v>
       </c>
       <c r="P30">
-        <v>198.17686308</v>
+        <v>200.60322156</v>
       </c>
       <c r="Q30">
-        <v>437.37686308</v>
+        <v>439.80322156</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09267672168905833</v>
+        <v>0.09264658412484648</v>
       </c>
       <c r="T30">
         <v>1.081907254615392</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.667691242383638</v>
+        <v>4.887148696817587</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07791240062174606</v>
+        <v>0.07736297264225883</v>
       </c>
       <c r="C31">
-        <v>3387.722599894738</v>
+        <v>3446.507218747755</v>
       </c>
       <c r="D31">
-        <v>4027.399599894738</v>
+        <v>4086.184218747755</v>
       </c>
       <c r="E31">
         <v>24.97699999999986</v>
@@ -3829,37 +3829,37 @@
         <v>360.3</v>
       </c>
       <c r="M31">
-        <v>79.94698829999999</v>
+        <v>76.35696809999999</v>
       </c>
       <c r="N31">
-        <v>280.3530117</v>
+        <v>283.9430319000001</v>
       </c>
       <c r="O31">
-        <v>84.10590351</v>
+        <v>85.18290957000001</v>
       </c>
       <c r="P31">
-        <v>196.24710819</v>
+        <v>198.7601223300001</v>
       </c>
       <c r="Q31">
-        <v>435.44710819</v>
+        <v>437.96012233</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09318126848133247</v>
+        <v>0.09315080653839272</v>
       </c>
       <c r="T31">
         <v>1.09355211405064</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.506736371956617</v>
+        <v>4.718626327961811</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0782951616273701</v>
+        <v>0.07718160471462819</v>
       </c>
       <c r="C32">
-        <v>3298.524096209296</v>
+        <v>3419.49394907933</v>
       </c>
       <c r="D32">
-        <v>3985.814096209295</v>
+        <v>4106.783949079329</v>
       </c>
       <c r="E32">
         <v>72.58999999999992</v>
@@ -3911,45 +3911,45 @@
         <v>360.3</v>
       </c>
       <c r="M32">
-        <v>86.41759499999999</v>
+        <v>78.98996699999999</v>
       </c>
       <c r="N32">
-        <v>273.882405</v>
+        <v>281.310033</v>
       </c>
       <c r="O32">
-        <v>82.1647215</v>
+        <v>84.39300990000001</v>
       </c>
       <c r="P32">
-        <v>191.7176835</v>
+        <v>196.9170231</v>
       </c>
       <c r="Q32">
-        <v>430.9176835</v>
+        <v>436.1170231</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09370023089624302</v>
+        <v>0.0936694353066117</v>
       </c>
       <c r="T32">
         <v>1.105529683755466</v>
       </c>
       <c r="U32">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.04235</v>
+        <v>0.03871</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.169289830386973</v>
+        <v>4.561338783696416</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07815012263299416</v>
+        <v>0.07754273678699754</v>
       </c>
       <c r="C33">
-        <v>3266.567570298172</v>
+        <v>3331.066561384714</v>
       </c>
       <c r="D33">
-        <v>4001.470570298171</v>
+        <v>4065.969561384713</v>
       </c>
       <c r="E33">
         <v>120.203</v>
@@ -3993,37 +3993,37 @@
         <v>360.3</v>
       </c>
       <c r="M33">
-        <v>89.29818149999998</v>
+        <v>85.31297339999999</v>
       </c>
       <c r="N33">
-        <v>271.0018185</v>
+        <v>274.9870266</v>
       </c>
       <c r="O33">
-        <v>81.30054555</v>
+        <v>82.49610798</v>
       </c>
       <c r="P33">
-        <v>189.70127295</v>
+        <v>192.49091862</v>
       </c>
       <c r="Q33">
-        <v>428.90127295</v>
+        <v>431.69091862</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09423423569999154</v>
+        <v>0.09420309679275006</v>
       </c>
       <c r="T33">
         <v>1.117854429393766</v>
       </c>
       <c r="U33">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.034796610051909</v>
+        <v>4.223273268306929</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07860988363861821</v>
+        <v>0.0773788688593669</v>
       </c>
       <c r="C34">
-        <v>3169.742725476905</v>
+        <v>3301.872575623271</v>
       </c>
       <c r="D34">
-        <v>3952.258725476905</v>
+        <v>4084.388575623271</v>
       </c>
       <c r="E34">
         <v>167.816</v>
@@ -4075,45 +4075,45 @@
         <v>360.3</v>
       </c>
       <c r="M34">
-        <v>96.2925312</v>
+        <v>88.0650048</v>
       </c>
       <c r="N34">
-        <v>264.0074688</v>
+        <v>272.2349952</v>
       </c>
       <c r="O34">
-        <v>79.20224064</v>
+        <v>81.67049856</v>
       </c>
       <c r="P34">
-        <v>184.80522816</v>
+        <v>190.56449664</v>
       </c>
       <c r="Q34">
-        <v>424.00522816</v>
+        <v>429.76449664</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09478394652737973</v>
+        <v>0.09475245420495132</v>
       </c>
       <c r="T34">
         <v>1.130541667550839</v>
       </c>
       <c r="U34">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04424</v>
+        <v>0.04046</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.741723221000966</v>
+        <v>4.091295978672337</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07848374464424228</v>
+        <v>0.07802350093173625</v>
       </c>
       <c r="C35">
-        <v>3135.510476140753</v>
+        <v>3182.748046998006</v>
       </c>
       <c r="D35">
-        <v>3965.639476140753</v>
+        <v>4012.877046998005</v>
       </c>
       <c r="E35">
         <v>215.4290000000001</v>
@@ -4157,37 +4157,37 @@
         <v>360.3</v>
       </c>
       <c r="M35">
-        <v>99.30167279999999</v>
+        <v>96.31633770000001</v>
       </c>
       <c r="N35">
-        <v>260.9983272</v>
+        <v>263.9836623</v>
       </c>
       <c r="O35">
-        <v>78.29949816</v>
+        <v>79.19509868999999</v>
       </c>
       <c r="P35">
-        <v>182.69882904</v>
+        <v>184.78856361</v>
       </c>
       <c r="Q35">
-        <v>421.89882904</v>
+        <v>423.98856361</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09535006663319742</v>
+        <v>0.09531821034587501</v>
       </c>
       <c r="T35">
         <v>1.143607629234989</v>
       </c>
       <c r="U35">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04424</v>
+        <v>0.04291</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.628337668849422</v>
+        <v>3.74079837962942</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07835760564986631</v>
+        <v>0.07788413300410561</v>
       </c>
       <c r="C36">
-        <v>3101.369138221245</v>
+        <v>3150.382694664956</v>
       </c>
       <c r="D36">
-        <v>3979.111138221244</v>
+        <v>4028.124694664956</v>
       </c>
       <c r="E36">
         <v>263.0420000000001</v>
@@ -4239,37 +4239,37 @@
         <v>360.3</v>
       </c>
       <c r="M36">
-        <v>102.3108144</v>
+        <v>99.2350146</v>
       </c>
       <c r="N36">
-        <v>257.9891856</v>
+        <v>261.0649854</v>
       </c>
       <c r="O36">
-        <v>77.39675568000001</v>
+        <v>78.31949562</v>
       </c>
       <c r="P36">
-        <v>180.59242992</v>
+        <v>182.74548978</v>
       </c>
       <c r="Q36">
-        <v>419.79242992</v>
+        <v>421.94548978</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09593334189373684</v>
+        <v>0.09590111061228124</v>
       </c>
       <c r="T36">
         <v>1.157069529151991</v>
       </c>
       <c r="U36">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.04424</v>
+        <v>0.04291</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.521621855059733</v>
+        <v>3.630774897875614</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07938296665549038</v>
+        <v>0.07774476507647497</v>
       </c>
       <c r="C37">
-        <v>2946.828178943771</v>
+        <v>3118.133656645291</v>
       </c>
       <c r="D37">
-        <v>3872.18317894377</v>
+        <v>4043.488656645291</v>
       </c>
       <c r="E37">
         <v>310.6550000000002</v>
@@ -4321,45 +4321,45 @@
         <v>360.3</v>
       </c>
       <c r="M37">
-        <v>113.1522945</v>
+        <v>102.1536915</v>
       </c>
       <c r="N37">
-        <v>247.1477055</v>
+        <v>258.1463085</v>
       </c>
       <c r="O37">
-        <v>74.14431164999999</v>
+        <v>77.44389255</v>
       </c>
       <c r="P37">
-        <v>173.00339385</v>
+        <v>180.70241595</v>
       </c>
       <c r="Q37">
-        <v>412.20339385</v>
+        <v>419.90241595</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09653456408536981</v>
+        <v>0.09650194627149997</v>
       </c>
       <c r="T37">
         <v>1.170945641374133</v>
       </c>
       <c r="U37">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04753000000000001</v>
+        <v>0.04291</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.184204099369809</v>
+        <v>3.527038472222025</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07928972766111445</v>
+        <v>0.07831099714884433</v>
       </c>
       <c r="C38">
-        <v>2908.700333617017</v>
+        <v>3008.817161612374</v>
       </c>
       <c r="D38">
-        <v>3881.668333617016</v>
+        <v>3981.785161612373</v>
       </c>
       <c r="E38">
         <v>358.268</v>
@@ -4403,37 +4403,37 @@
         <v>360.3</v>
       </c>
       <c r="M38">
-        <v>116.3852172</v>
+        <v>109.8717588</v>
       </c>
       <c r="N38">
-        <v>243.9147828</v>
+        <v>250.4282412</v>
       </c>
       <c r="O38">
-        <v>73.17443484</v>
+        <v>75.12847236</v>
       </c>
       <c r="P38">
-        <v>170.74034796</v>
+        <v>175.29976884</v>
       </c>
       <c r="Q38">
-        <v>409.94034796</v>
+        <v>414.49976884</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09715457447049131</v>
+        <v>0.09712155804506926</v>
       </c>
       <c r="T38">
         <v>1.185255382103216</v>
       </c>
       <c r="U38">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04753000000000001</v>
+        <v>0.04487</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.095753985498426</v>
+        <v>3.279277622704261</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07919648866673849</v>
+        <v>0.07819122922121369</v>
       </c>
       <c r="C39">
-        <v>2870.619071356614</v>
+        <v>2974.097978232277</v>
       </c>
       <c r="D39">
-        <v>3891.200071356613</v>
+        <v>3994.678978232276</v>
       </c>
       <c r="E39">
         <v>405.8810000000001</v>
@@ -4485,37 +4485,37 @@
         <v>360.3</v>
       </c>
       <c r="M39">
-        <v>119.6181399</v>
+        <v>112.9237521</v>
       </c>
       <c r="N39">
-        <v>240.6818601</v>
+        <v>247.3762479</v>
       </c>
       <c r="O39">
-        <v>72.20455803</v>
+        <v>74.21287436999999</v>
       </c>
       <c r="P39">
-        <v>168.47730207</v>
+        <v>173.16337353</v>
       </c>
       <c r="Q39">
-        <v>407.67730207</v>
+        <v>412.36337353</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09779426772498172</v>
+        <v>0.09776084003367251</v>
       </c>
       <c r="T39">
         <v>1.200019400315762</v>
       </c>
       <c r="U39">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04753000000000001</v>
+        <v>0.04487</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.012084958863333</v>
+        <v>3.190648497766309</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08157704967236254</v>
+        <v>0.07807146129358304</v>
       </c>
       <c r="C40">
-        <v>2593.438694570631</v>
+        <v>2939.46257165158</v>
       </c>
       <c r="D40">
-        <v>3661.632694570631</v>
+        <v>4007.65657165158</v>
       </c>
       <c r="E40">
         <v>453.4939999999999</v>
@@ -4567,45 +4567,45 @@
         <v>360.3</v>
       </c>
       <c r="M40">
-        <v>139.6774968</v>
+        <v>115.9757454</v>
       </c>
       <c r="N40">
-        <v>220.6225032</v>
+        <v>244.3242546</v>
       </c>
       <c r="O40">
-        <v>66.18675096000001</v>
+        <v>73.29727638</v>
       </c>
       <c r="P40">
-        <v>154.43575224</v>
+        <v>171.02697822</v>
       </c>
       <c r="Q40">
-        <v>393.63575224</v>
+        <v>410.22697822</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09845459624574603</v>
+        <v>0.09842074402190813</v>
       </c>
       <c r="T40">
         <v>1.215259677180326</v>
       </c>
       <c r="U40">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.05404</v>
+        <v>0.04487</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.579513581317274</v>
+        <v>3.106684063614564</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0815489106779866</v>
+        <v>0.0779516933659524</v>
       </c>
       <c r="C41">
-        <v>2548.380945820319</v>
+        <v>2904.911761033605</v>
       </c>
       <c r="D41">
-        <v>3664.187945820319</v>
+        <v>4020.718761033605</v>
       </c>
       <c r="E41">
         <v>501.107</v>
@@ -4649,45 +4649,45 @@
         <v>360.3</v>
       </c>
       <c r="M41">
-        <v>143.3532204</v>
+        <v>119.0277387</v>
       </c>
       <c r="N41">
-        <v>216.9467796</v>
+        <v>241.2722613</v>
       </c>
       <c r="O41">
-        <v>65.08403388000001</v>
+        <v>72.38167839</v>
       </c>
       <c r="P41">
-        <v>151.86274572</v>
+        <v>168.89058291</v>
       </c>
       <c r="Q41">
-        <v>391.06274572</v>
+        <v>408.09058291</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09913657488194524</v>
+        <v>0.09910228420647935</v>
       </c>
       <c r="T41">
         <v>1.230999635253565</v>
       </c>
       <c r="U41">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.05404</v>
+        <v>0.04487</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.513372207437343</v>
+        <v>3.027025497880857</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08283677168361064</v>
+        <v>0.08001592543832176</v>
       </c>
       <c r="C42">
-        <v>2387.360117902127</v>
+        <v>2643.447775117453</v>
       </c>
       <c r="D42">
-        <v>3550.780117902126</v>
+        <v>3806.867775117452</v>
       </c>
       <c r="E42">
         <v>548.72</v>
@@ -4731,45 +4731,45 @@
         <v>360.3</v>
       </c>
       <c r="M42">
-        <v>155.980188</v>
+        <v>136.934988</v>
       </c>
       <c r="N42">
-        <v>204.319812</v>
+        <v>223.365012</v>
       </c>
       <c r="O42">
-        <v>61.29594360000001</v>
+        <v>67.0095036</v>
       </c>
       <c r="P42">
-        <v>143.0238684</v>
+        <v>156.3555084</v>
       </c>
       <c r="Q42">
-        <v>382.2238684</v>
+        <v>395.5555084</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09984128613935109</v>
+        <v>0.09980654239720294</v>
       </c>
       <c r="T42">
         <v>1.247264258595911</v>
       </c>
       <c r="U42">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.309908743025749</v>
+        <v>2.631175605755338</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08284153268923471</v>
+        <v>0.07995075751069111</v>
       </c>
       <c r="C43">
-        <v>2339.340890624054</v>
+        <v>2602.237732180586</v>
       </c>
       <c r="D43">
-        <v>3550.373890624054</v>
+        <v>3813.270732180586</v>
       </c>
       <c r="E43">
         <v>596.3330000000001</v>
@@ -4813,45 +4813,45 @@
         <v>360.3</v>
       </c>
       <c r="M43">
-        <v>159.8796927</v>
+        <v>140.3583627</v>
       </c>
       <c r="N43">
-        <v>200.4203073</v>
+        <v>219.9416373</v>
       </c>
       <c r="O43">
-        <v>60.12609219</v>
+        <v>65.98249119</v>
       </c>
       <c r="P43">
-        <v>140.29421511</v>
+        <v>153.95914611</v>
       </c>
       <c r="Q43">
-        <v>379.49421511</v>
+        <v>393.15914611</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1005698859139571</v>
+        <v>0.1005346737469341</v>
       </c>
       <c r="T43">
         <v>1.264080225102404</v>
       </c>
       <c r="U43">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.253569505390975</v>
+        <v>2.567000590980818</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08284629369485877</v>
+        <v>0.07988558958306047</v>
       </c>
       <c r="C44">
-        <v>2291.321756284276</v>
+        <v>2561.049264425239</v>
       </c>
       <c r="D44">
-        <v>3549.967756284276</v>
+        <v>3819.695264425239</v>
       </c>
       <c r="E44">
         <v>643.9459999999999</v>
@@ -4895,45 +4895,45 @@
         <v>360.3</v>
       </c>
       <c r="M44">
-        <v>163.7791974</v>
+        <v>143.7817374</v>
       </c>
       <c r="N44">
-        <v>196.5208026000001</v>
+        <v>216.5182626</v>
       </c>
       <c r="O44">
-        <v>58.95624078000002</v>
+        <v>64.95547878000001</v>
       </c>
       <c r="P44">
-        <v>137.5645618200001</v>
+        <v>151.56278382</v>
       </c>
       <c r="Q44">
-        <v>376.76456182</v>
+        <v>390.76278382</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.101323609818722</v>
+        <v>0.1012879130742422</v>
       </c>
       <c r="T44">
         <v>1.281476052522914</v>
       </c>
       <c r="U44">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.199913088595952</v>
+        <v>2.505881529290798</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08285105470048282</v>
+        <v>0.08099432165542984</v>
       </c>
       <c r="C45">
-        <v>2243.302714850904</v>
+        <v>2406.999477822945</v>
       </c>
       <c r="D45">
-        <v>3549.561714850903</v>
+        <v>3713.258477822944</v>
       </c>
       <c r="E45">
         <v>691.559</v>
@@ -4977,37 +4977,37 @@
         <v>360.3</v>
       </c>
       <c r="M45">
-        <v>167.6787021</v>
+        <v>155.1898122</v>
       </c>
       <c r="N45">
-        <v>192.6212979</v>
+        <v>205.1101878</v>
       </c>
       <c r="O45">
-        <v>57.78638937000001</v>
+        <v>61.53305634000001</v>
       </c>
       <c r="P45">
-        <v>134.83490853</v>
+        <v>143.57713146</v>
       </c>
       <c r="Q45">
-        <v>374.03490853</v>
+        <v>382.77713146</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1021037801762856</v>
+        <v>0.1020675818516313</v>
       </c>
       <c r="T45">
         <v>1.299482259852917</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.14875231909372</v>
+        <v>2.321673020234508</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08285581570610687</v>
+        <v>0.08095645372779919</v>
       </c>
       <c r="C46">
-        <v>2195.283766292059</v>
+        <v>2362.923816720491</v>
       </c>
       <c r="D46">
-        <v>3549.155766292059</v>
+        <v>3716.795816720491</v>
       </c>
       <c r="E46">
         <v>739.172</v>
@@ -5059,37 +5059,37 @@
         <v>360.3</v>
       </c>
       <c r="M46">
-        <v>171.5782068</v>
+        <v>158.7988776</v>
       </c>
       <c r="N46">
-        <v>188.7217932</v>
+        <v>201.5011224</v>
       </c>
       <c r="O46">
-        <v>56.61653796000001</v>
+        <v>60.45033672</v>
       </c>
       <c r="P46">
-        <v>132.10525524</v>
+        <v>141.05078568</v>
       </c>
       <c r="Q46">
-        <v>371.30525524</v>
+        <v>380.25078568</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1029118137609051</v>
+        <v>0.1028750959424986</v>
       </c>
       <c r="T46">
         <v>1.318131546016133</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.099917039114318</v>
+        <v>2.268907724320087</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08286057671173093</v>
+        <v>0.08091858580016856</v>
       </c>
       <c r="C47">
-        <v>2147.26491057588</v>
+        <v>2318.854901551765</v>
       </c>
       <c r="D47">
-        <v>3548.749910575879</v>
+        <v>3720.339901551764</v>
       </c>
       <c r="E47">
         <v>786.7849999999999</v>
@@ -5141,37 +5141,37 @@
         <v>360.3</v>
       </c>
       <c r="M47">
-        <v>175.4777115</v>
+        <v>162.407943</v>
       </c>
       <c r="N47">
-        <v>184.8222885</v>
+        <v>197.892057</v>
       </c>
       <c r="O47">
-        <v>55.44668655000001</v>
+        <v>59.3676171</v>
       </c>
       <c r="P47">
-        <v>129.37560195</v>
+        <v>138.5244399</v>
       </c>
       <c r="Q47">
-        <v>368.57560195</v>
+        <v>377.7244399</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1037492303849653</v>
+        <v>0.1037119741821246</v>
       </c>
       <c r="T47">
         <v>1.33745898803983</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.053252216022888</v>
+        <v>2.218487552668529</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08286533771735498</v>
+        <v>0.08088071787253791</v>
       </c>
       <c r="C48">
-        <v>2099.246147670522</v>
+        <v>2274.792751632582</v>
       </c>
       <c r="D48">
-        <v>3548.344147670522</v>
+        <v>3723.890751632582</v>
       </c>
       <c r="E48">
         <v>834.3980000000001</v>
@@ -5223,37 +5223,37 @@
         <v>360.3</v>
       </c>
       <c r="M48">
-        <v>179.3772162</v>
+        <v>166.0170084</v>
       </c>
       <c r="N48">
-        <v>180.9227838</v>
+        <v>194.2829916</v>
       </c>
       <c r="O48">
-        <v>54.27683514</v>
+        <v>58.28489748</v>
       </c>
       <c r="P48">
-        <v>126.64594866</v>
+        <v>135.99809412</v>
       </c>
       <c r="Q48">
-        <v>365.84594866</v>
+        <v>375.19809412</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1046176624395462</v>
+        <v>0.1045798479121072</v>
       </c>
       <c r="T48">
         <v>1.35750226124959</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.00861629828326</v>
+        <v>2.170259562393126</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08823279872297904</v>
+        <v>0.08084284994490727</v>
       </c>
       <c r="C49">
-        <v>1646.464541987284</v>
+        <v>2230.737386352571</v>
       </c>
       <c r="D49">
-        <v>3143.175541987284</v>
+        <v>3727.448386352571</v>
       </c>
       <c r="E49">
         <v>882.011</v>
@@ -5305,45 +5305,45 @@
         <v>360.3</v>
       </c>
       <c r="M49">
-        <v>219.7530402</v>
+        <v>169.6260738</v>
       </c>
       <c r="N49">
-        <v>140.5469598</v>
+        <v>190.6739262</v>
       </c>
       <c r="O49">
-        <v>42.16408794000001</v>
+        <v>57.20217786</v>
       </c>
       <c r="P49">
-        <v>98.38287186000002</v>
+        <v>133.47174834</v>
       </c>
       <c r="Q49">
-        <v>337.58287186</v>
+        <v>372.67174834</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1055188655150548</v>
+        <v>0.1054804715941647</v>
       </c>
       <c r="T49">
         <v>1.378301884391793</v>
       </c>
       <c r="U49">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.639567760573808</v>
+        <v>2.12408382702306</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08835165972860308</v>
+        <v>0.08080498201727662</v>
       </c>
       <c r="C50">
-        <v>1590.923746851237</v>
+        <v>2186.688825175529</v>
       </c>
       <c r="D50">
-        <v>3135.247746851236</v>
+        <v>3731.012825175529</v>
       </c>
       <c r="E50">
         <v>929.6239999999998</v>
@@ -5387,45 +5387,45 @@
         <v>360.3</v>
       </c>
       <c r="M50">
-        <v>224.4286368</v>
+        <v>173.2351392</v>
       </c>
       <c r="N50">
-        <v>135.8713632</v>
+        <v>187.0648608</v>
       </c>
       <c r="O50">
-        <v>40.76140896000001</v>
+        <v>56.11945824000001</v>
       </c>
       <c r="P50">
-        <v>95.10995424000004</v>
+        <v>130.94540256</v>
       </c>
       <c r="Q50">
-        <v>334.30995424</v>
+        <v>370.14540256</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1064547302473136</v>
+        <v>0.1064157346486089</v>
       </c>
       <c r="T50">
         <v>1.399901493039466</v>
       </c>
       <c r="U50">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.605410098895187</v>
+        <v>2.079832080626746</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08847052073422715</v>
+        <v>0.08076711408964599</v>
       </c>
       <c r="C51">
-        <v>1535.422842463915</v>
+        <v>2142.64708763977</v>
       </c>
       <c r="D51">
-        <v>3127.359842463915</v>
+        <v>3734.58408763977</v>
       </c>
       <c r="E51">
         <v>977.2370000000001</v>
@@ -5469,45 +5469,45 @@
         <v>360.3</v>
       </c>
       <c r="M51">
-        <v>229.1042334</v>
+        <v>176.8442046</v>
       </c>
       <c r="N51">
-        <v>131.1957666</v>
+        <v>183.4557954</v>
       </c>
       <c r="O51">
-        <v>39.35872998</v>
+        <v>55.03673862</v>
       </c>
       <c r="P51">
-        <v>91.83703662000002</v>
+        <v>128.41905678</v>
       </c>
       <c r="Q51">
-        <v>331.03703662</v>
+        <v>367.61905678</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1074272955573081</v>
+        <v>0.1073876746855803</v>
       </c>
       <c r="T51">
         <v>1.422348145163518</v>
       </c>
       <c r="U51">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.572646627489163</v>
+        <v>2.037386527960894</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08858938173985119</v>
+        <v>0.08569924616201534</v>
       </c>
       <c r="C52">
-        <v>1479.9615285</v>
+        <v>1681.057541988464</v>
       </c>
       <c r="D52">
-        <v>3119.511528499999</v>
+        <v>3320.607541988464</v>
       </c>
       <c r="E52">
         <v>1024.85</v>
@@ -5551,37 +5551,37 @@
         <v>360.3</v>
       </c>
       <c r="M52">
-        <v>233.77983</v>
+        <v>214.2585</v>
       </c>
       <c r="N52">
-        <v>126.52017</v>
+        <v>146.0415</v>
       </c>
       <c r="O52">
-        <v>37.95605100000001</v>
+        <v>43.81245000000001</v>
       </c>
       <c r="P52">
-        <v>88.56411900000003</v>
+        <v>102.22905</v>
       </c>
       <c r="Q52">
-        <v>327.7641190000001</v>
+        <v>341.42905</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1084387634797024</v>
+        <v>0.1083984923240307</v>
       </c>
       <c r="T52">
         <v>1.445692663372533</v>
       </c>
       <c r="U52">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.06874</v>
+        <v>0.063</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.54119369493938</v>
+        <v>1.681613564922745</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08870824274547524</v>
+        <v>0.0857607782343847</v>
       </c>
       <c r="C53">
-        <v>1424.539507641359</v>
+        <v>1628.858714594554</v>
       </c>
       <c r="D53">
-        <v>3111.702507641359</v>
+        <v>3316.021714594553</v>
       </c>
       <c r="E53">
         <v>1072.463</v>
@@ -5633,37 +5633,37 @@
         <v>360.3</v>
       </c>
       <c r="M53">
-        <v>238.4554266</v>
+        <v>218.54367</v>
       </c>
       <c r="N53">
-        <v>121.8445734</v>
+        <v>141.75633</v>
       </c>
       <c r="O53">
-        <v>36.55337202</v>
+        <v>42.52689900000001</v>
       </c>
       <c r="P53">
-        <v>85.29120138000002</v>
+        <v>99.22943100000001</v>
       </c>
       <c r="Q53">
-        <v>324.49120138</v>
+        <v>338.429431</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1094915158070923</v>
+        <v>0.1094505678252749</v>
       </c>
       <c r="T53">
         <v>1.469990019059466</v>
       </c>
       <c r="U53">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.06874</v>
+        <v>0.063</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.510974210724882</v>
+        <v>1.64864074992426</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.116087605631826</v>
+        <v>0.08582231030675405</v>
       </c>
       <c r="C54">
-        <v>238.8710673506807</v>
+        <v>1576.672535976551</v>
       </c>
       <c r="D54">
-        <v>1973.64706735068</v>
+        <v>3311.44853597655</v>
       </c>
       <c r="E54">
         <v>1120.076</v>
@@ -5715,45 +5715,45 @@
         <v>360.3</v>
       </c>
       <c r="M54">
-        <v>405.0533136</v>
+        <v>222.82884</v>
       </c>
       <c r="N54">
-        <v>-44.75331360000001</v>
+        <v>137.47116</v>
       </c>
       <c r="O54">
-        <v>-13.42599408</v>
+        <v>41.241348</v>
       </c>
       <c r="P54">
-        <v>-31.32731952000001</v>
+        <v>96.22981200000001</v>
       </c>
       <c r="Q54">
-        <v>207.87268048</v>
+        <v>335.429812</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1119112265797563</v>
+        <v>0.1105464798057376</v>
       </c>
       <c r="T54">
-        <v>1.525836557483828</v>
+        <v>1.495299764566688</v>
       </c>
       <c r="U54">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V54">
-        <v>0.2668537606551751</v>
+        <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.1199427247568134</v>
+        <v>0.063</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8895125355172504</v>
+        <v>1.616936120118024</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1172656056318259</v>
+        <v>0.0858838423791234</v>
       </c>
       <c r="C55">
-        <v>160.6823919254552</v>
+        <v>1524.498953874139</v>
       </c>
       <c r="D55">
-        <v>1943.071391925455</v>
+        <v>3306.887953874138</v>
       </c>
       <c r="E55">
         <v>1167.689</v>
@@ -5797,45 +5797,45 @@
         <v>360.3</v>
       </c>
       <c r="M55">
-        <v>412.8428004</v>
+        <v>227.11401</v>
       </c>
       <c r="N55">
-        <v>-52.54280039999998</v>
+        <v>133.18599</v>
       </c>
       <c r="O55">
-        <v>-15.76284011999999</v>
+        <v>39.95579700000001</v>
       </c>
       <c r="P55">
-        <v>-36.77996027999998</v>
+        <v>93.23019300000001</v>
       </c>
       <c r="Q55">
-        <v>202.42003972</v>
+        <v>332.430193</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1133178484218787</v>
+        <v>0.1116890263385604</v>
       </c>
       <c r="T55">
-        <v>1.558301165089867</v>
+        <v>1.521686520521026</v>
       </c>
       <c r="U55">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V55">
-        <v>0.2618187840390398</v>
+        <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.1207664469312131</v>
+        <v>0.063</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8727292801301326</v>
+        <v>1.586427891436552</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1184436056318259</v>
+        <v>0.08594537445149275</v>
       </c>
       <c r="C56">
-        <v>83.42661872487179</v>
+        <v>1472.337916314502</v>
       </c>
       <c r="D56">
-        <v>1913.428618724872</v>
+        <v>3302.339916314502</v>
       </c>
       <c r="E56">
         <v>1215.302</v>
@@ -5879,45 +5879,45 @@
         <v>360.3</v>
       </c>
       <c r="M56">
-        <v>420.6322872000001</v>
+        <v>231.39918</v>
       </c>
       <c r="N56">
-        <v>-60.33228720000005</v>
+        <v>128.90082</v>
       </c>
       <c r="O56">
-        <v>-18.09968616000002</v>
+        <v>38.670246</v>
       </c>
       <c r="P56">
-        <v>-42.23260104000003</v>
+        <v>90.23057400000002</v>
       </c>
       <c r="Q56">
-        <v>196.96739896</v>
+        <v>329.430574</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1147856277353978</v>
+        <v>0.112881248807593</v>
       </c>
       <c r="T56">
-        <v>1.592177277374429</v>
+        <v>1.549220526734249</v>
       </c>
       <c r="U56">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V56">
-        <v>0.2569702880383168</v>
+        <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.1215596608769314</v>
+        <v>0.063</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8565676267943892</v>
+        <v>1.55704959715069</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1196216056318259</v>
+        <v>0.08600690652386211</v>
       </c>
       <c r="C57">
-        <v>7.061693289825598</v>
+        <v>1420.18937161035</v>
       </c>
       <c r="D57">
-        <v>1884.676693289825</v>
+        <v>3297.804371610349</v>
       </c>
       <c r="E57">
         <v>1262.915</v>
@@ -5961,45 +5961,45 @@
         <v>360.3</v>
       </c>
       <c r="M57">
-        <v>428.421774</v>
+        <v>235.68435</v>
       </c>
       <c r="N57">
-        <v>-68.12177400000002</v>
+        <v>124.61565</v>
       </c>
       <c r="O57">
-        <v>-20.43653220000001</v>
+        <v>37.384695</v>
       </c>
       <c r="P57">
-        <v>-47.68524180000001</v>
+        <v>87.23095500000002</v>
       </c>
       <c r="Q57">
-        <v>191.5147582</v>
+        <v>326.430955</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1163186416850734</v>
+        <v>0.1141264589419158</v>
       </c>
       <c r="T57">
-        <v>1.627558994649417</v>
+        <v>1.577978266556948</v>
       </c>
       <c r="U57">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V57">
-        <v>0.2522981009830746</v>
+        <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.122324030679169</v>
+        <v>0.063</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8409936699435823</v>
+        <v>1.528739604475223</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.120799605631826</v>
+        <v>0.08606843859623148</v>
       </c>
       <c r="C58">
-        <v>-68.45194855193495</v>
+        <v>1368.053268357957</v>
       </c>
       <c r="D58">
-        <v>1856.776051448065</v>
+        <v>3293.281268357957</v>
       </c>
       <c r="E58">
         <v>1310.528</v>
@@ -6043,45 +6043,45 @@
         <v>360.3</v>
       </c>
       <c r="M58">
-        <v>436.2112608</v>
+        <v>239.96952</v>
       </c>
       <c r="N58">
-        <v>-75.91126080000004</v>
+        <v>120.33048</v>
       </c>
       <c r="O58">
-        <v>-22.77337824000001</v>
+        <v>36.099144</v>
       </c>
       <c r="P58">
-        <v>-53.13788256000002</v>
+        <v>84.231336</v>
       </c>
       <c r="Q58">
-        <v>186.06211744</v>
+        <v>323.431336</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1179213380870068</v>
+        <v>0.1154282695368897</v>
       </c>
       <c r="T58">
-        <v>1.66454897180054</v>
+        <v>1.608043176371587</v>
       </c>
       <c r="U58">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V58">
-        <v>0.247792777751234</v>
+        <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.1230611015598981</v>
+        <v>0.063</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8259759258374468</v>
+        <v>1.501440682966737</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.121977605631826</v>
+        <v>0.1117964476652739</v>
       </c>
       <c r="C59">
-        <v>-143.1515623270825</v>
+        <v>120.1546961932399</v>
       </c>
       <c r="D59">
-        <v>1829.689437672917</v>
+        <v>2092.99569619324</v>
       </c>
       <c r="E59">
         <v>1358.141</v>
@@ -6125,37 +6125,37 @@
         <v>360.3</v>
       </c>
       <c r="M59">
-        <v>444.0007476</v>
+        <v>398.4065388</v>
       </c>
       <c r="N59">
-        <v>-83.7007476</v>
+        <v>-38.10653880000001</v>
       </c>
       <c r="O59">
-        <v>-25.11022428</v>
+        <v>-11.43196164</v>
       </c>
       <c r="P59">
-        <v>-58.59052332</v>
+        <v>-26.67457716000001</v>
       </c>
       <c r="Q59">
-        <v>180.60947668</v>
+        <v>212.52542284</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1195985785076349</v>
+        <v>0.1181912343993743</v>
       </c>
       <c r="T59">
-        <v>1.703259413005203</v>
+        <v>1.671852988438205</v>
       </c>
       <c r="U59">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2434455360363001</v>
+        <v>0.2713057881167487</v>
       </c>
       <c r="W59">
-        <v>0.1237723103044613</v>
+        <v>0.1069723103044613</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8114851201210005</v>
+        <v>0.9043526270558289</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.154668378611247</v>
+        <v>0.1128064476652739</v>
       </c>
       <c r="C60">
-        <v>-718.0284225679807</v>
+        <v>43.0180798960082</v>
       </c>
       <c r="D60">
-        <v>1302.425577432018</v>
+        <v>2063.472079896007</v>
       </c>
       <c r="E60">
         <v>1405.753999999999</v>
@@ -6207,45 +6207,45 @@
         <v>360.3</v>
       </c>
       <c r="M60">
-        <v>595.9433531999999</v>
+        <v>405.3961271999999</v>
       </c>
       <c r="N60">
-        <v>-235.6433531999999</v>
+        <v>-45.0961271999999</v>
       </c>
       <c r="O60">
-        <v>-70.69300595999998</v>
+        <v>-13.52883815999997</v>
       </c>
       <c r="P60">
-        <v>-164.9503472399999</v>
+        <v>-31.56728903999993</v>
       </c>
       <c r="Q60">
-        <v>74.24965276000006</v>
+        <v>207.6327109600001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1243003850897717</v>
+        <v>0.119914835218407</v>
       </c>
       <c r="T60">
-        <v>1.811776358468127</v>
+        <v>1.711659011972448</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1813762993069657</v>
+        <v>0.2666281021147358</v>
       </c>
       <c r="W60">
-        <v>0.1766589946095568</v>
+        <v>0.1076589946095568</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.6045876643565525</v>
+        <v>0.8887603403824527</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1563683786112471</v>
+        <v>0.1138164476652739</v>
       </c>
       <c r="C61">
-        <v>-784.8708958252996</v>
+        <v>-33.29720684804988</v>
       </c>
       <c r="D61">
-        <v>1283.1961041747</v>
+        <v>2034.769793151949</v>
       </c>
       <c r="E61">
         <v>1453.367</v>
@@ -6289,45 +6289,45 @@
         <v>360.3</v>
       </c>
       <c r="M61">
-        <v>606.2182385999999</v>
+        <v>412.3857156</v>
       </c>
       <c r="N61">
-        <v>-245.9182385999999</v>
+        <v>-52.08571559999996</v>
       </c>
       <c r="O61">
-        <v>-73.77547157999997</v>
+        <v>-15.62571467999999</v>
       </c>
       <c r="P61">
-        <v>-172.14276702</v>
+        <v>-36.46000091999997</v>
       </c>
       <c r="Q61">
-        <v>67.05723298000004</v>
+        <v>202.73999908</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1262150286285466</v>
+        <v>0.121722514126173</v>
       </c>
       <c r="T61">
-        <v>1.855966025747838</v>
+        <v>1.753406792752263</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1783021247424409</v>
+        <v>0.2621089817399097</v>
       </c>
       <c r="W61">
-        <v>0.1773224014805813</v>
+        <v>0.1083224014805813</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5943404158081365</v>
+        <v>0.8736966057996991</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1580683786112471</v>
+        <v>0.1148264476652739</v>
       </c>
       <c r="C62">
-        <v>-851.1538090952204</v>
+        <v>-108.8249672009288</v>
       </c>
       <c r="D62">
-        <v>1264.526190904779</v>
+        <v>2006.855032799071</v>
       </c>
       <c r="E62">
         <v>1500.98</v>
@@ -6371,45 +6371,45 @@
         <v>360.3</v>
       </c>
       <c r="M62">
-        <v>616.4931239999999</v>
+        <v>419.3753039999999</v>
       </c>
       <c r="N62">
-        <v>-256.1931239999998</v>
+        <v>-59.0753039999999</v>
       </c>
       <c r="O62">
-        <v>-76.85793719999995</v>
+        <v>-17.72259119999997</v>
       </c>
       <c r="P62">
-        <v>-179.3351867999999</v>
+        <v>-41.35271279999994</v>
       </c>
       <c r="Q62">
-        <v>59.8648132000001</v>
+        <v>197.8472872</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1282254043442603</v>
+        <v>0.1236205769793273</v>
       </c>
       <c r="T62">
-        <v>1.902365176391534</v>
+        <v>1.79724196257107</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1753304226634002</v>
+        <v>0.2577404987109113</v>
       </c>
       <c r="W62">
-        <v>0.1779636947892382</v>
+        <v>0.1089636947892382</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5844347422113343</v>
+        <v>0.8591349957030376</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1597683786112471</v>
+        <v>0.1158364476652739</v>
       </c>
       <c r="C63">
-        <v>-916.9012361371642</v>
+        <v>-183.5971744623439</v>
       </c>
       <c r="D63">
-        <v>1246.391763862835</v>
+        <v>1979.695825537656</v>
       </c>
       <c r="E63">
         <v>1548.593</v>
@@ -6453,45 +6453,45 @@
         <v>360.3</v>
       </c>
       <c r="M63">
-        <v>626.7680094</v>
+        <v>426.3648924</v>
       </c>
       <c r="N63">
-        <v>-266.4680094</v>
+        <v>-66.06489239999996</v>
       </c>
       <c r="O63">
-        <v>-79.94040281999999</v>
+        <v>-19.81946771999999</v>
       </c>
       <c r="P63">
-        <v>-186.52760658</v>
+        <v>-46.24542467999997</v>
       </c>
       <c r="Q63">
-        <v>52.67239341999999</v>
+        <v>192.95457532</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1303388762505234</v>
+        <v>0.1256159763890537</v>
       </c>
       <c r="T63">
-        <v>1.951143770657984</v>
+        <v>1.843325089816482</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1724561534394101</v>
+        <v>0.2535152446336832</v>
       </c>
       <c r="W63">
-        <v>0.1785839620877753</v>
+        <v>0.1095839620877753</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5748538447980336</v>
+        <v>0.8450508154456107</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1614683786112471</v>
+        <v>0.1168464476652739</v>
       </c>
       <c r="C64">
-        <v>-982.1358892784547</v>
+        <v>-257.6440942360496</v>
       </c>
       <c r="D64">
-        <v>1228.770110721545</v>
+        <v>1953.26190576395</v>
       </c>
       <c r="E64">
         <v>1596.206</v>
@@ -6535,45 +6535,45 @@
         <v>360.3</v>
       </c>
       <c r="M64">
-        <v>637.0428947999999</v>
+        <v>433.3544808</v>
       </c>
       <c r="N64">
-        <v>-276.7428947999999</v>
+        <v>-73.05448079999996</v>
       </c>
       <c r="O64">
-        <v>-83.02286843999995</v>
+        <v>-21.91634423999999</v>
       </c>
       <c r="P64">
-        <v>-193.7200263599999</v>
+        <v>-51.13813655999998</v>
       </c>
       <c r="Q64">
-        <v>45.47997364000008</v>
+        <v>188.06186344</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.132563583520274</v>
+        <v>0.1277163968203446</v>
       </c>
       <c r="T64">
-        <v>2.002489659359509</v>
+        <v>1.891833644811653</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1696746025774841</v>
+        <v>0.2494262890750754</v>
       </c>
       <c r="W64">
-        <v>0.1791842207637789</v>
+        <v>0.1101842207637789</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5655820085916137</v>
+        <v>0.8314209635835846</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1631683786112471</v>
+        <v>0.1178564476652739</v>
       </c>
       <c r="C65">
-        <v>-1046.87921431317</v>
+        <v>-330.9943969377682</v>
       </c>
       <c r="D65">
-        <v>1211.63978568683</v>
+        <v>1927.524603062231</v>
       </c>
       <c r="E65">
         <v>1643.819</v>
@@ -6617,45 +6617,45 @@
         <v>360.3</v>
       </c>
       <c r="M65">
-        <v>647.3177802</v>
+        <v>440.3440692</v>
       </c>
       <c r="N65">
-        <v>-287.0177802</v>
+        <v>-80.04406919999997</v>
       </c>
       <c r="O65">
-        <v>-86.10533406</v>
+        <v>-24.01322075999999</v>
       </c>
       <c r="P65">
-        <v>-200.91244614</v>
+        <v>-56.03084843999998</v>
       </c>
       <c r="Q65">
-        <v>38.28755386</v>
+        <v>183.16915156</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1349085452370382</v>
+        <v>0.1299303534911647</v>
       </c>
       <c r="T65">
-        <v>2.056611001504361</v>
+        <v>1.942964283860616</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.166981354917524</v>
+        <v>0.2454671416294393</v>
       </c>
       <c r="W65">
-        <v>0.1797654236087984</v>
+        <v>0.1107654236087983</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.5566045163917468</v>
+        <v>0.8182238054314642</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1648683786112471</v>
+        <v>0.1188664476652739</v>
       </c>
       <c r="C66">
-        <v>-1111.151477572201</v>
+        <v>-403.6752615239725</v>
       </c>
       <c r="D66">
-        <v>1194.980522427798</v>
+        <v>1902.456738476027</v>
       </c>
       <c r="E66">
         <v>1691.432</v>
@@ -6699,45 +6699,45 @@
         <v>360.3</v>
       </c>
       <c r="M66">
-        <v>657.5926655999999</v>
+        <v>447.3336576</v>
       </c>
       <c r="N66">
-        <v>-297.2926655999999</v>
+        <v>-87.03365759999997</v>
       </c>
       <c r="O66">
-        <v>-89.18779967999997</v>
+        <v>-26.11009727999999</v>
       </c>
       <c r="P66">
-        <v>-208.10486592</v>
+        <v>-60.92356031999998</v>
       </c>
       <c r="Q66">
-        <v>31.09513408000004</v>
+        <v>178.27643968</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1373837826047337</v>
+        <v>0.1322673077548081</v>
       </c>
       <c r="T66">
-        <v>2.113739084879482</v>
+        <v>1.996935513967856</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1643722712469377</v>
+        <v>0.2416317175414793</v>
       </c>
       <c r="W66">
-        <v>0.1803284638649109</v>
+        <v>0.1113284638649109</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5479075708231258</v>
+        <v>0.8054390584715976</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1665683786112471</v>
+        <v>0.1565078133754237</v>
       </c>
       <c r="C67">
-        <v>-1174.971845907808</v>
+        <v>-1072.359303340069</v>
       </c>
       <c r="D67">
-        <v>1178.773154092192</v>
+        <v>1281.385696659931</v>
       </c>
       <c r="E67">
         <v>1739.045</v>
@@ -6781,37 +6781,37 @@
         <v>360.3</v>
       </c>
       <c r="M67">
-        <v>667.867551</v>
+        <v>621.444876</v>
       </c>
       <c r="N67">
-        <v>-307.567551</v>
+        <v>-261.144876</v>
       </c>
       <c r="O67">
-        <v>-92.27026530000001</v>
+        <v>-78.3434628</v>
       </c>
       <c r="P67">
-        <v>-215.2972857</v>
+        <v>-182.8014132</v>
       </c>
       <c r="Q67">
-        <v>23.90271429999996</v>
+        <v>56.39858679999998</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1400004621077261</v>
+        <v>0.1391131328625166</v>
       </c>
       <c r="T67">
-        <v>2.174131630161753</v>
+        <v>2.155037710450729</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1618434670739079</v>
+        <v>0.1739333675027357</v>
       </c>
       <c r="W67">
-        <v>0.1808741798054507</v>
+        <v>0.1658741798054507</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5394782235796929</v>
+        <v>0.5797778916757856</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1682683786112471</v>
+        <v>0.1580578133754237</v>
       </c>
       <c r="C68">
-        <v>-1238.358460256326</v>
+        <v>-1136.969347623513</v>
       </c>
       <c r="D68">
-        <v>1162.999539743674</v>
+        <v>1264.388652376486</v>
       </c>
       <c r="E68">
         <v>1786.658</v>
@@ -6863,37 +6863,37 @@
         <v>360.3</v>
       </c>
       <c r="M68">
-        <v>678.1424364</v>
+        <v>631.0055663999999</v>
       </c>
       <c r="N68">
-        <v>-317.8424363999999</v>
+        <v>-270.7055663999999</v>
       </c>
       <c r="O68">
-        <v>-95.35273091999998</v>
+        <v>-81.21166991999996</v>
       </c>
       <c r="P68">
-        <v>-222.4897054799999</v>
+        <v>-189.4938964799999</v>
       </c>
       <c r="Q68">
-        <v>16.71029452000005</v>
+        <v>49.70610352000006</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1427710639344239</v>
+        <v>0.1418576367702376</v>
       </c>
       <c r="T68">
-        <v>2.238076678107687</v>
+        <v>2.218421172522809</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1593912933303638</v>
+        <v>0.1712980134496639</v>
       </c>
       <c r="W68">
-        <v>0.1814033588993075</v>
+        <v>0.1664033588993075</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5313043111012128</v>
+        <v>0.5709933781655465</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1699683786112471</v>
+        <v>0.1596078133754237</v>
       </c>
       <c r="C69">
-        <v>-1301.328503372659</v>
+        <v>-1201.134377497473</v>
       </c>
       <c r="D69">
-        <v>1147.642496627341</v>
+        <v>1247.836622502527</v>
       </c>
       <c r="E69">
         <v>1834.271</v>
@@ -6945,37 +6945,37 @@
         <v>360.3</v>
       </c>
       <c r="M69">
-        <v>688.4173218000001</v>
+        <v>640.5662568</v>
       </c>
       <c r="N69">
-        <v>-328.1173218000001</v>
+        <v>-280.2662568</v>
       </c>
       <c r="O69">
-        <v>-98.43519654000002</v>
+        <v>-84.07987704</v>
       </c>
       <c r="P69">
-        <v>-229.68212526</v>
+        <v>-196.18637976</v>
       </c>
       <c r="Q69">
-        <v>9.517874739999939</v>
+        <v>43.01362023999997</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1457095810233458</v>
+        <v>0.1447684742481236</v>
       </c>
       <c r="T69">
-        <v>2.30589718350489</v>
+        <v>2.285646056538652</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.157012318803045</v>
+        <v>0.1687413266817585</v>
       </c>
       <c r="W69">
-        <v>0.1819167416023029</v>
+        <v>0.1669167416023029</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5233743960101498</v>
+        <v>0.562471088939195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1716683786112471</v>
+        <v>0.1611578133754238</v>
       </c>
       <c r="C70">
-        <v>-1363.898262268227</v>
+        <v>-1264.871644092859</v>
       </c>
       <c r="D70">
-        <v>1132.685737731773</v>
+        <v>1231.71235590714</v>
       </c>
       <c r="E70">
         <v>1881.884</v>
@@ -7027,37 +7027,37 @@
         <v>360.3</v>
       </c>
       <c r="M70">
-        <v>698.6922072</v>
+        <v>650.1269472</v>
       </c>
       <c r="N70">
-        <v>-338.3922072</v>
+        <v>-289.8269472</v>
       </c>
       <c r="O70">
-        <v>-101.51766216</v>
+        <v>-86.94808415999999</v>
       </c>
       <c r="P70">
-        <v>-236.87454504</v>
+        <v>-202.87886304</v>
       </c>
       <c r="Q70">
-        <v>2.325454960000002</v>
+        <v>36.32113695999999</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1488317554303254</v>
+        <v>0.1478612390683775</v>
       </c>
       <c r="T70">
-        <v>2.377956470489418</v>
+        <v>2.357072495805485</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1547033141147649</v>
+        <v>0.1662598365834973</v>
       </c>
       <c r="W70">
-        <v>0.1824150248140337</v>
+        <v>0.1674150248140338</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.515677713715883</v>
+        <v>0.5541994552783245</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.173368378611247</v>
+        <v>0.1627078133754238</v>
       </c>
       <c r="C71">
-        <v>-1426.083185829353</v>
+        <v>-1328.197518254379</v>
       </c>
       <c r="D71">
-        <v>1118.113814170647</v>
+        <v>1215.999481745621</v>
       </c>
       <c r="E71">
         <v>1929.497</v>
@@ -7109,37 +7109,37 @@
         <v>360.3</v>
       </c>
       <c r="M71">
-        <v>708.9670926</v>
+        <v>659.6876375999999</v>
       </c>
       <c r="N71">
-        <v>-348.6670926</v>
+        <v>-299.3876375999999</v>
       </c>
       <c r="O71">
-        <v>-104.60012778</v>
+        <v>-89.81629127999996</v>
       </c>
       <c r="P71">
-        <v>-244.06696482</v>
+        <v>-209.5713463199999</v>
       </c>
       <c r="Q71">
-        <v>-4.866964820000021</v>
+        <v>29.62865368000007</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1521553604442069</v>
+        <v>0.1511535371028413</v>
       </c>
       <c r="T71">
-        <v>2.454664743731012</v>
+        <v>2.433107092444372</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1524612370986089</v>
+        <v>0.1638502737344612</v>
       </c>
       <c r="W71">
-        <v>0.1828988650341202</v>
+        <v>0.1678988650341202</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5082041236620296</v>
+        <v>0.5461675791148706</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1750683786112471</v>
+        <v>0.1642578133754238</v>
       </c>
       <c r="C72">
-        <v>-1487.897938044608</v>
+        <v>-1391.127545982037</v>
       </c>
       <c r="D72">
-        <v>1103.912061955392</v>
+        <v>1200.682454017963</v>
       </c>
       <c r="E72">
         <v>1977.11</v>
@@ -7191,37 +7191,37 @@
         <v>360.3</v>
       </c>
       <c r="M72">
-        <v>719.241978</v>
+        <v>669.248328</v>
       </c>
       <c r="N72">
-        <v>-358.941978</v>
+        <v>-308.948328</v>
       </c>
       <c r="O72">
-        <v>-107.6825934</v>
+        <v>-92.6844984</v>
       </c>
       <c r="P72">
-        <v>-251.2593846</v>
+        <v>-216.2638296</v>
       </c>
       <c r="Q72">
-        <v>-12.05938460000002</v>
+        <v>22.93617039999998</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1557005391256804</v>
+        <v>0.154665321672936</v>
       </c>
       <c r="T72">
-        <v>2.536486901855379</v>
+        <v>2.514210662192518</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1502832194257716</v>
+        <v>0.1615095555382546</v>
       </c>
       <c r="W72">
-        <v>0.1833688812479185</v>
+        <v>0.1683688812479185</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.500944064752572</v>
+        <v>0.5383651851275152</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1985414668603452</v>
+        <v>0.1658078133754237</v>
       </c>
       <c r="C73">
-        <v>-1700.226197076246</v>
+        <v>-1453.676499734636</v>
       </c>
       <c r="D73">
-        <v>939.1968029237535</v>
+        <v>1185.746500265363</v>
       </c>
       <c r="E73">
         <v>2024.723</v>
@@ -7273,45 +7273,45 @@
         <v>360.3</v>
       </c>
       <c r="M73">
-        <v>830.9325533999998</v>
+        <v>678.8090183999999</v>
       </c>
       <c r="N73">
-        <v>-470.6325533999998</v>
+        <v>-318.5090183999999</v>
       </c>
       <c r="O73">
-        <v>-141.18976602</v>
+        <v>-95.55270551999996</v>
       </c>
       <c r="P73">
-        <v>-329.4427873799999</v>
+        <v>-222.9563128799999</v>
       </c>
       <c r="Q73">
-        <v>-90.24278737999992</v>
+        <v>16.24368712000006</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1611215516786286</v>
+        <v>0.1584192982823475</v>
       </c>
       <c r="T73">
-        <v>2.661603006332555</v>
+        <v>2.600907581578465</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1300827600961337</v>
+        <v>0.1592347730658848</v>
       </c>
       <c r="W73">
-        <v>0.2138256575683704</v>
+        <v>0.1688256575683703</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4336092003204457</v>
+        <v>0.5307825768862826</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2005414668603452</v>
+        <v>0.1673578133754237</v>
       </c>
       <c r="C74">
-        <v>-1759.629615031988</v>
+        <v>-1515.858425951171</v>
       </c>
       <c r="D74">
-        <v>927.4063849680117</v>
+        <v>1171.177574048828</v>
       </c>
       <c r="E74">
         <v>2072.336</v>
@@ -7355,45 +7355,45 @@
         <v>360.3</v>
       </c>
       <c r="M74">
-        <v>842.6358287999999</v>
+        <v>688.3697087999999</v>
       </c>
       <c r="N74">
-        <v>-482.3358287999999</v>
+        <v>-328.0697087999999</v>
       </c>
       <c r="O74">
-        <v>-144.70074864</v>
+        <v>-98.42091263999997</v>
       </c>
       <c r="P74">
-        <v>-337.6350801599999</v>
+        <v>-229.6487961599999</v>
       </c>
       <c r="Q74">
-        <v>-98.43508015999993</v>
+        <v>9.551203840000085</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1652401785242939</v>
+        <v>0.1624414160781457</v>
       </c>
       <c r="T74">
-        <v>2.756660256558717</v>
+        <v>2.693797138063411</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1282760550947985</v>
+        <v>0.1570231789955253</v>
       </c>
       <c r="W74">
-        <v>0.2142697456576985</v>
+        <v>0.1692697456576985</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4275868503159951</v>
+        <v>0.5234105966517509</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2025414668603452</v>
+        <v>0.1689078133754237</v>
       </c>
       <c r="C75">
-        <v>-1818.740675840296</v>
+        <v>-1577.686689111446</v>
       </c>
       <c r="D75">
-        <v>915.9083241597036</v>
+        <v>1156.962310888553</v>
       </c>
       <c r="E75">
         <v>2119.949</v>
@@ -7437,45 +7437,45 @@
         <v>360.3</v>
       </c>
       <c r="M75">
-        <v>854.3391042</v>
+        <v>697.9303991999999</v>
       </c>
       <c r="N75">
-        <v>-494.0391041999999</v>
+        <v>-337.6303991999999</v>
       </c>
       <c r="O75">
-        <v>-148.21173126</v>
+        <v>-101.28911976</v>
       </c>
       <c r="P75">
-        <v>-345.82737294</v>
+        <v>-236.3412794399999</v>
       </c>
       <c r="Q75">
-        <v>-106.62737294</v>
+        <v>2.858720560000052</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1696638888400085</v>
+        <v>0.1667614685254844</v>
       </c>
       <c r="T75">
-        <v>2.858758784579411</v>
+        <v>2.793567402436129</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1265188488606232</v>
+        <v>0.1548721765435318</v>
       </c>
       <c r="W75">
-        <v>0.2147016669500588</v>
+        <v>0.1697016669500588</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4217294962020773</v>
+        <v>0.5162405884784393</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2045414668603452</v>
+        <v>0.1704578133754237</v>
       </c>
       <c r="C76">
-        <v>-1877.570120339413</v>
+        <v>-1639.174012626444</v>
       </c>
       <c r="D76">
-        <v>904.691879660587</v>
+        <v>1143.087987373555</v>
       </c>
       <c r="E76">
         <v>2167.562</v>
@@ -7519,45 +7519,45 @@
         <v>360.3</v>
       </c>
       <c r="M76">
-        <v>866.0423796</v>
+        <v>707.4910895999999</v>
       </c>
       <c r="N76">
-        <v>-505.7423796</v>
+        <v>-347.1910895999999</v>
       </c>
       <c r="O76">
-        <v>-151.72271388</v>
+        <v>-104.15732688</v>
       </c>
       <c r="P76">
-        <v>-354.01966572</v>
+        <v>-243.0337627199999</v>
       </c>
       <c r="Q76">
-        <v>-114.81966572</v>
+        <v>-3.833762719999925</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1744278845646242</v>
+        <v>0.1714138326995415</v>
       </c>
       <c r="T76">
-        <v>2.968711045524773</v>
+        <v>2.901012302529827</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.124809134686831</v>
+        <v>0.1527793092929435</v>
       </c>
       <c r="W76">
-        <v>0.215121914693977</v>
+        <v>0.1701219146939769</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4160304489561033</v>
+        <v>0.5092643643098118</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2065414668603453</v>
+        <v>0.1720078133754238</v>
       </c>
       <c r="C77">
-        <v>-1936.12816959281</v>
+        <v>-1700.332516821407</v>
       </c>
       <c r="D77">
-        <v>893.7468304071899</v>
+        <v>1129.542483178593</v>
       </c>
       <c r="E77">
         <v>2215.175</v>
@@ -7601,45 +7601,45 @@
         <v>360.3</v>
       </c>
       <c r="M77">
-        <v>877.7456549999999</v>
+        <v>717.0517799999999</v>
       </c>
       <c r="N77">
-        <v>-517.445655</v>
+        <v>-356.7517799999999</v>
       </c>
       <c r="O77">
-        <v>-155.2336965</v>
+        <v>-107.025534</v>
       </c>
       <c r="P77">
-        <v>-362.2119585</v>
+        <v>-249.7262459999999</v>
       </c>
       <c r="Q77">
-        <v>-123.0119585</v>
+        <v>-10.52624599999993</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1795729999472092</v>
+        <v>0.1764383860075232</v>
       </c>
       <c r="T77">
-        <v>3.087459487345764</v>
+        <v>3.017052794631021</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1231450128910066</v>
+        <v>0.1507422518357043</v>
       </c>
       <c r="W77">
-        <v>0.2155309558313906</v>
+        <v>0.1705309558313906</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4104833763033552</v>
+        <v>0.502474172785681</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2085414668603452</v>
+        <v>0.2007757379363158</v>
       </c>
       <c r="C78">
-        <v>-1994.424555954776</v>
+        <v>-1951.583405830095</v>
       </c>
       <c r="D78">
-        <v>883.0634440452232</v>
+        <v>925.9045941699044</v>
       </c>
       <c r="E78">
         <v>2262.788</v>
@@ -7683,37 +7683,37 @@
         <v>360.3</v>
       </c>
       <c r="M78">
-        <v>889.4489303999999</v>
+        <v>853.2630503999999</v>
       </c>
       <c r="N78">
-        <v>-529.1489303999999</v>
+        <v>-492.9630503999999</v>
       </c>
       <c r="O78">
-        <v>-158.74467912</v>
+        <v>-147.88891512</v>
       </c>
       <c r="P78">
-        <v>-370.4042512799999</v>
+        <v>-345.07413528</v>
       </c>
       <c r="Q78">
-        <v>-131.2042512799999</v>
+        <v>-105.87413528</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1851468749450096</v>
+        <v>0.1844563377615533</v>
       </c>
       <c r="T78">
-        <v>3.216103632651838</v>
+        <v>3.202224890567051</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1215246837740196</v>
+        <v>0.1266784023394997</v>
       </c>
       <c r="W78">
-        <v>0.215929232728346</v>
+        <v>0.205929232728346</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4050822792467321</v>
+        <v>0.4222613411316657</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2105414668603453</v>
+        <v>0.2026757379363158</v>
       </c>
       <c r="C79">
-        <v>-2052.468551934286</v>
+        <v>-2010.091393422259</v>
       </c>
       <c r="D79">
-        <v>872.6324480657137</v>
+        <v>915.0096065777402</v>
       </c>
       <c r="E79">
         <v>2310.401</v>
@@ -7765,37 +7765,37 @@
         <v>360.3</v>
       </c>
       <c r="M79">
-        <v>901.1522057999999</v>
+        <v>864.4901957999999</v>
       </c>
       <c r="N79">
-        <v>-540.8522057999999</v>
+        <v>-504.1901957999999</v>
       </c>
       <c r="O79">
-        <v>-162.25566174</v>
+        <v>-151.25705874</v>
       </c>
       <c r="P79">
-        <v>-378.5965440599999</v>
+        <v>-352.9331370599999</v>
       </c>
       <c r="Q79">
-        <v>-139.3965440599999</v>
+        <v>-113.7331370599999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1912054347252274</v>
+        <v>0.1904848741859687</v>
       </c>
       <c r="T79">
-        <v>3.355934225375831</v>
+        <v>3.34145205972214</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1199464411276038</v>
+        <v>0.1250332282831426</v>
       </c>
       <c r="W79">
-        <v>0.216317164770835</v>
+        <v>0.206317164770835</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3998214704253461</v>
+        <v>0.4167774276104752</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2125414668603453</v>
+        <v>0.2045757379363158</v>
       </c>
       <c r="C80">
-        <v>-2110.268997037032</v>
+        <v>-2068.345963406336</v>
       </c>
       <c r="D80">
-        <v>862.4450029629674</v>
+        <v>904.368036593664</v>
       </c>
       <c r="E80">
         <v>2358.014</v>
@@ -7847,37 +7847,37 @@
         <v>360.3</v>
       </c>
       <c r="M80">
-        <v>912.8554811999999</v>
+        <v>875.7173411999999</v>
       </c>
       <c r="N80">
-        <v>-552.5554811999998</v>
+        <v>-515.4173411999998</v>
       </c>
       <c r="O80">
-        <v>-165.7666443599999</v>
+        <v>-154.6252023599999</v>
       </c>
       <c r="P80">
-        <v>-386.7888368399999</v>
+        <v>-360.7921388399999</v>
       </c>
       <c r="Q80">
-        <v>-147.5888368399999</v>
+        <v>-121.5921388399999</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1978147726672832</v>
+        <v>0.19706145937624</v>
       </c>
       <c r="T80">
-        <v>3.508476690165641</v>
+        <v>3.493336244254965</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1184086662413525</v>
+        <v>0.1234302381769484</v>
       </c>
       <c r="W80">
-        <v>0.2166951498378756</v>
+        <v>0.2066951498378756</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3946955541378416</v>
+        <v>0.4114341272564949</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2145414668603453</v>
+        <v>0.2064757379363157</v>
       </c>
       <c r="C81">
-        <v>-2167.834322749008</v>
+        <v>-2126.355855882097</v>
       </c>
       <c r="D81">
-        <v>852.4926772509916</v>
+        <v>893.9711441179026</v>
       </c>
       <c r="E81">
         <v>2405.627</v>
@@ -7929,37 +7929,37 @@
         <v>360.3</v>
       </c>
       <c r="M81">
-        <v>924.5587566</v>
+        <v>886.9444866</v>
       </c>
       <c r="N81">
-        <v>-564.2587566</v>
+        <v>-526.6444865999999</v>
       </c>
       <c r="O81">
-        <v>-169.27762698</v>
+        <v>-157.99334598</v>
       </c>
       <c r="P81">
-        <v>-394.98112962</v>
+        <v>-368.65114062</v>
       </c>
       <c r="Q81">
-        <v>-155.78112962</v>
+        <v>-129.45114062</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2050535713657252</v>
+        <v>0.2042643860132038</v>
       </c>
       <c r="T81">
-        <v>3.675547008744958</v>
+        <v>3.659685589219487</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1169098223648797</v>
+        <v>0.1218678300987592</v>
       </c>
       <c r="W81">
-        <v>0.2170635656627126</v>
+        <v>0.2070635656627126</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3896994078829322</v>
+        <v>0.4062261003291974</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2165414668603453</v>
+        <v>0.2083757379363158</v>
       </c>
       <c r="C82">
-        <v>-2225.172575809976</v>
+        <v>-2184.129413601861</v>
       </c>
       <c r="D82">
-        <v>842.7674241900239</v>
+        <v>883.8105863981383</v>
       </c>
       <c r="E82">
         <v>2453.24</v>
@@ -8011,37 +8011,37 @@
         <v>360.3</v>
       </c>
       <c r="M82">
-        <v>936.262032</v>
+        <v>898.1716319999999</v>
       </c>
       <c r="N82">
-        <v>-575.9620319999999</v>
+        <v>-537.8716319999999</v>
       </c>
       <c r="O82">
-        <v>-172.7886096</v>
+        <v>-161.3614895999999</v>
       </c>
       <c r="P82">
-        <v>-403.1734223999999</v>
+        <v>-376.5101423999999</v>
       </c>
       <c r="Q82">
-        <v>-163.9734223999999</v>
+        <v>-137.3101424</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2130162499340115</v>
+        <v>0.212187605313864</v>
       </c>
       <c r="T82">
-        <v>3.859324359182206</v>
+        <v>3.842669868680462</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1154484495853186</v>
+        <v>0.1203444822225247</v>
       </c>
       <c r="W82">
-        <v>0.2174227710919287</v>
+        <v>0.2074227710919287</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3848281652843956</v>
+        <v>0.4011482740750825</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2185414668603452</v>
+        <v>0.2102757379363157</v>
       </c>
       <c r="C83">
-        <v>-2282.291439911901</v>
+        <v>-2241.674604297292</v>
       </c>
       <c r="D83">
-        <v>833.2615600880991</v>
+        <v>873.8783957027076</v>
       </c>
       <c r="E83">
         <v>2500.853</v>
@@ -8093,37 +8093,37 @@
         <v>360.3</v>
       </c>
       <c r="M83">
-        <v>947.9653074</v>
+        <v>909.3987774</v>
       </c>
       <c r="N83">
-        <v>-587.6653074000001</v>
+        <v>-549.0987774</v>
       </c>
       <c r="O83">
-        <v>-176.29959222</v>
+        <v>-164.72963322</v>
       </c>
       <c r="P83">
-        <v>-411.3657151800001</v>
+        <v>-384.36914418</v>
       </c>
       <c r="Q83">
-        <v>-172.1657151800001</v>
+        <v>-145.16914418</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2218171051936963</v>
+        <v>0.2209448476988042</v>
       </c>
       <c r="T83">
-        <v>4.062446693876006</v>
+        <v>4.044915651242591</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1140231600842653</v>
+        <v>0.1188587478740985</v>
       </c>
       <c r="W83">
-        <v>0.2177731072512876</v>
+        <v>0.2077731072512876</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3800772002808844</v>
+        <v>0.3961958262469949</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2205414668603452</v>
+        <v>0.2121757379363158</v>
       </c>
       <c r="C84">
-        <v>-2339.198255945287</v>
+        <v>-2298.999041517477</v>
       </c>
       <c r="D84">
-        <v>823.967744054713</v>
+        <v>864.1669584825231</v>
       </c>
       <c r="E84">
         <v>2548.466</v>
@@ -8175,37 +8175,37 @@
         <v>360.3</v>
       </c>
       <c r="M84">
-        <v>959.6685828</v>
+        <v>920.6259227999999</v>
       </c>
       <c r="N84">
-        <v>-599.3685828</v>
+        <v>-560.3259227999999</v>
       </c>
       <c r="O84">
-        <v>-179.81057484</v>
+        <v>-168.09777684</v>
       </c>
       <c r="P84">
-        <v>-419.5580079600001</v>
+        <v>-392.22814596</v>
       </c>
       <c r="Q84">
-        <v>-180.3580079600001</v>
+        <v>-153.02814596</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2315958332600128</v>
+        <v>0.2306751170154045</v>
       </c>
       <c r="T84">
-        <v>4.288138176869118</v>
+        <v>4.269633187422736</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1126326337417743</v>
+        <v>0.1174092509488046</v>
       </c>
       <c r="W84">
-        <v>0.2181148986262719</v>
+        <v>0.2081148986262719</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.375442112472581</v>
+        <v>0.3913641698293486</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2225414668603453</v>
+        <v>0.2140757379363157</v>
       </c>
       <c r="C85">
-        <v>-2395.900040905558</v>
+        <v>-2356.110004092827</v>
       </c>
       <c r="D85">
-        <v>814.8789590944417</v>
+        <v>854.6689959071728</v>
       </c>
       <c r="E85">
         <v>2596.079</v>
@@ -8257,37 +8257,37 @@
         <v>360.3</v>
       </c>
       <c r="M85">
-        <v>971.3718582</v>
+        <v>931.8530682000001</v>
       </c>
       <c r="N85">
-        <v>-611.0718582</v>
+        <v>-571.5530682000001</v>
       </c>
       <c r="O85">
-        <v>-183.32155746</v>
+        <v>-171.46592046</v>
       </c>
       <c r="P85">
-        <v>-427.7503007399999</v>
+        <v>-400.0871477400001</v>
       </c>
       <c r="Q85">
-        <v>-188.55030074</v>
+        <v>-160.8871477400001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2425249999223665</v>
+        <v>0.2415501238986635</v>
       </c>
       <c r="T85">
-        <v>4.54038159903789</v>
+        <v>4.520788080800544</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1112756140581384</v>
+        <v>0.1159946816602648</v>
       </c>
       <c r="W85">
-        <v>0.2184484540645096</v>
+        <v>0.2084484540645096</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3709187135271282</v>
+        <v>0.3866489388675491</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2245414668603452</v>
+        <v>0.2159757379363157</v>
       </c>
       <c r="C86">
-        <v>-2452.403505561801</v>
+        <v>-2413.014454329385</v>
       </c>
       <c r="D86">
-        <v>805.9884944381989</v>
+        <v>845.3775456706137</v>
       </c>
       <c r="E86">
         <v>2643.692</v>
@@ -8339,37 +8339,37 @@
         <v>360.3</v>
       </c>
       <c r="M86">
-        <v>983.0751335999998</v>
+        <v>943.0802135999999</v>
       </c>
       <c r="N86">
-        <v>-622.7751335999999</v>
+        <v>-582.7802135999998</v>
       </c>
       <c r="O86">
-        <v>-186.83254008</v>
+        <v>-174.8340640799999</v>
       </c>
       <c r="P86">
-        <v>-435.9425935199999</v>
+        <v>-407.9461495199998</v>
       </c>
       <c r="Q86">
-        <v>-196.74259352</v>
+        <v>-168.7461495199998</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2548203124175143</v>
+        <v>0.2537845066423299</v>
       </c>
       <c r="T86">
-        <v>4.824155448977756</v>
+        <v>4.803337335850576</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1099509043669702</v>
+        <v>0.1146137925928807</v>
       </c>
       <c r="W86">
-        <v>0.2187740677065987</v>
+        <v>0.2087740677065987</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3665030145565672</v>
+        <v>0.3820459753096024</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2265414668603453</v>
+        <v>0.2178757379363157</v>
       </c>
       <c r="C87">
-        <v>-2508.715070981374</v>
+        <v>-2469.719055029122</v>
       </c>
       <c r="D87">
-        <v>797.2899290186249</v>
+        <v>836.2859449708775</v>
       </c>
       <c r="E87">
         <v>2691.304999999999</v>
@@ -8421,37 +8421,37 @@
         <v>360.3</v>
       </c>
       <c r="M87">
-        <v>994.7784089999999</v>
+        <v>954.3073589999998</v>
       </c>
       <c r="N87">
-        <v>-634.4784089999998</v>
+        <v>-594.0073589999997</v>
       </c>
       <c r="O87">
-        <v>-190.3435226999999</v>
+        <v>-178.2022076999999</v>
       </c>
       <c r="P87">
-        <v>-444.1348862999999</v>
+        <v>-415.8051512999998</v>
       </c>
       <c r="Q87">
-        <v>-204.9348862999999</v>
+        <v>-176.6051512999998</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2687549999120152</v>
+        <v>0.2676501404184852</v>
       </c>
       <c r="T87">
-        <v>5.145765812242939</v>
+        <v>5.12355982490728</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.108657364315594</v>
+        <v>0.1132653950329645</v>
       </c>
       <c r="W87">
-        <v>0.219092019851227</v>
+        <v>0.209092019851227</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3621912143853135</v>
+        <v>0.3775513167765483</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2285414668603452</v>
+        <v>0.2197757379363157</v>
       </c>
       <c r="C88">
-        <v>-2564.840883995917</v>
+        <v>-2526.230185423617</v>
       </c>
       <c r="D88">
-        <v>788.777116004082</v>
+        <v>827.3878145763824</v>
       </c>
       <c r="E88">
         <v>2738.918</v>
@@ -8503,37 +8503,37 @@
         <v>360.3</v>
       </c>
       <c r="M88">
-        <v>1006.4816844</v>
+        <v>965.5345043999999</v>
       </c>
       <c r="N88">
-        <v>-646.1816844</v>
+        <v>-605.2345043999999</v>
       </c>
       <c r="O88">
-        <v>-193.85450532</v>
+        <v>-181.57035132</v>
       </c>
       <c r="P88">
-        <v>-452.32717908</v>
+        <v>-423.6641530799999</v>
       </c>
       <c r="Q88">
-        <v>-213.12717908</v>
+        <v>-184.4641530799999</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2846803570485877</v>
+        <v>0.2834965790198056</v>
       </c>
       <c r="T88">
-        <v>5.513320513117435</v>
+        <v>5.48952838382923</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1073939065909941</v>
+        <v>0.1119483555558369</v>
       </c>
       <c r="W88">
-        <v>0.2194025777599337</v>
+        <v>0.2094025777599337</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.357979688636647</v>
+        <v>0.3731611851861232</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2305414668603452</v>
+        <v>0.2216757379363157</v>
       </c>
       <c r="C89">
-        <v>-2620.786831686999</v>
+        <v>-2582.553956101276</v>
       </c>
       <c r="D89">
-        <v>780.4441683130008</v>
+        <v>818.6770438987238</v>
       </c>
       <c r="E89">
         <v>2786.530999999999</v>
@@ -8585,37 +8585,37 @@
         <v>360.3</v>
       </c>
       <c r="M89">
-        <v>1018.1849598</v>
+        <v>976.7616497999999</v>
       </c>
       <c r="N89">
-        <v>-657.8849597999999</v>
+        <v>-616.4616497999998</v>
       </c>
       <c r="O89">
-        <v>-197.36548794</v>
+        <v>-184.9384949399999</v>
       </c>
       <c r="P89">
-        <v>-460.51947186</v>
+        <v>-431.5231548599999</v>
       </c>
       <c r="Q89">
-        <v>-221.31947186</v>
+        <v>-192.3231548599999</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3030557691292484</v>
+        <v>0.3017809312520984</v>
       </c>
       <c r="T89">
-        <v>5.937422091049545</v>
+        <v>5.911799797969939</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1061594938715574</v>
+        <v>0.1106615928482986</v>
       </c>
       <c r="W89">
-        <v>0.2197059964063712</v>
+        <v>0.2097059964063712</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3538649795718579</v>
+        <v>0.3688719761609954</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2325414668603452</v>
+        <v>0.2235757379363157</v>
       </c>
       <c r="C90">
-        <v>-2676.558554963199</v>
+        <v>-2638.696223001421</v>
       </c>
       <c r="D90">
-        <v>772.285445036801</v>
+        <v>810.147776998579</v>
       </c>
       <c r="E90">
         <v>2834.144</v>
@@ -8667,37 +8667,37 @@
         <v>360.3</v>
       </c>
       <c r="M90">
-        <v>1029.8882352</v>
+        <v>987.9887951999999</v>
       </c>
       <c r="N90">
-        <v>-669.5882352000001</v>
+        <v>-627.6887952</v>
       </c>
       <c r="O90">
-        <v>-200.87647056</v>
+        <v>-188.30663856</v>
       </c>
       <c r="P90">
-        <v>-468.7117646400001</v>
+        <v>-439.3821566399999</v>
       </c>
       <c r="Q90">
-        <v>-229.5117646400001</v>
+        <v>-200.18215664</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3244937498900191</v>
+        <v>0.3231126755231066</v>
       </c>
       <c r="T90">
-        <v>6.432207265303676</v>
+        <v>6.404449781134103</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1049531359866533</v>
+        <v>0.1094040747477497</v>
       </c>
       <c r="W90">
-        <v>0.2200025191744806</v>
+        <v>0.2100025191744806</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3498437866221776</v>
+        <v>0.3646802491591657</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2345414668603452</v>
+        <v>0.2254757379363157</v>
       </c>
       <c r="C91">
-        <v>-2732.161461294374</v>
+        <v>-2694.662600542636</v>
       </c>
       <c r="D91">
-        <v>764.2955387056262</v>
+        <v>801.7943994573636</v>
       </c>
       <c r="E91">
         <v>2881.757</v>
@@ -8749,37 +8749,37 @@
         <v>360.3</v>
       </c>
       <c r="M91">
-        <v>1041.5915106</v>
+        <v>999.2159406</v>
       </c>
       <c r="N91">
-        <v>-681.2915106</v>
+        <v>-638.9159405999999</v>
       </c>
       <c r="O91">
-        <v>-204.38745318</v>
+        <v>-191.67478218</v>
       </c>
       <c r="P91">
-        <v>-476.9040574200001</v>
+        <v>-447.2411584199999</v>
       </c>
       <c r="Q91">
-        <v>-237.7040574200001</v>
+        <v>-208.0411584199999</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3498295453345663</v>
+        <v>0.3483229187524799</v>
       </c>
       <c r="T91">
-        <v>7.016953380331283</v>
+        <v>6.986672488509929</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1037738872677022</v>
+        <v>0.1081748154809211</v>
       </c>
       <c r="W91">
-        <v>0.2202923785095988</v>
+        <v>0.2102923785095988</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3459129575590072</v>
+        <v>0.360582718269737</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2365414668603452</v>
+        <v>0.2273757379363157</v>
       </c>
       <c r="C92">
-        <v>-2787.600736663557</v>
+        <v>-2750.458473947214</v>
       </c>
       <c r="D92">
-        <v>756.4692633364421</v>
+        <v>793.6115260527848</v>
       </c>
       <c r="E92">
         <v>2929.369999999999</v>
@@ -8831,37 +8831,37 @@
         <v>360.3</v>
       </c>
       <c r="M92">
-        <v>1053.294786</v>
+        <v>1010.443086</v>
       </c>
       <c r="N92">
-        <v>-692.994786</v>
+        <v>-650.1430859999998</v>
       </c>
       <c r="O92">
-        <v>-207.8984358</v>
+        <v>-195.0429257999999</v>
       </c>
       <c r="P92">
-        <v>-485.0963502</v>
+        <v>-455.1001601999999</v>
       </c>
       <c r="Q92">
-        <v>-245.8963502</v>
+        <v>-215.9001601999999</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.380232499868023</v>
+        <v>0.3785752106277279</v>
       </c>
       <c r="T92">
-        <v>7.718648718364411</v>
+        <v>7.685339737360922</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1026208440758388</v>
+        <v>0.1069728730866886</v>
       </c>
       <c r="W92">
-        <v>0.2205757965261588</v>
+        <v>0.2105757965261588</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.342069480252796</v>
+        <v>0.3565762436222956</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2385414668603453</v>
+        <v>0.2292757379363157</v>
       </c>
       <c r="C93">
-        <v>-2842.881356791981</v>
+        <v>-2806.089010818539</v>
       </c>
       <c r="D93">
-        <v>748.8016432080187</v>
+        <v>785.5939891814609</v>
       </c>
       <c r="E93">
         <v>2976.983</v>
@@ -8913,37 +8913,37 @@
         <v>360.3</v>
       </c>
       <c r="M93">
-        <v>1064.9980614</v>
+        <v>1021.6702314</v>
       </c>
       <c r="N93">
-        <v>-704.6980613999999</v>
+        <v>-661.3702314</v>
       </c>
       <c r="O93">
-        <v>-211.40941842</v>
+        <v>-198.41106942</v>
       </c>
       <c r="P93">
-        <v>-493.28864298</v>
+        <v>-462.95916198</v>
       </c>
       <c r="Q93">
-        <v>-254.08864298</v>
+        <v>-223.75916198</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4173916665200256</v>
+        <v>0.4155502340308089</v>
       </c>
       <c r="T93">
-        <v>8.576276353738237</v>
+        <v>8.539266374845472</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1014931424925878</v>
+        <v>0.1057973470088129</v>
       </c>
       <c r="W93">
-        <v>0.2208529855753219</v>
+        <v>0.2108529855753219</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3383104749752928</v>
+        <v>0.3526578233627098</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2405414668603452</v>
+        <v>0.2311757379363157</v>
       </c>
       <c r="C94">
-        <v>-2898.008097688278</v>
+        <v>-2861.559172023718</v>
       </c>
       <c r="D94">
-        <v>741.2879023117218</v>
+        <v>777.7368279762811</v>
       </c>
       <c r="E94">
         <v>3024.596</v>
@@ -8995,37 +8995,37 @@
         <v>360.3</v>
       </c>
       <c r="M94">
-        <v>1076.7013368</v>
+        <v>1032.8973768</v>
       </c>
       <c r="N94">
-        <v>-716.4013368000001</v>
+        <v>-672.5973768000001</v>
       </c>
       <c r="O94">
-        <v>-214.92040104</v>
+        <v>-201.77921304</v>
       </c>
       <c r="P94">
-        <v>-501.4809357600001</v>
+        <v>-470.8181637600001</v>
       </c>
       <c r="Q94">
-        <v>-262.2809357600001</v>
+        <v>-231.6181637600001</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4638406248350289</v>
+        <v>0.4617690132846601</v>
       </c>
       <c r="T94">
-        <v>9.648310897955518</v>
+        <v>9.606674671701159</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1003899561611467</v>
+        <v>0.1046473758456736</v>
       </c>
       <c r="W94">
-        <v>0.2211241487755902</v>
+        <v>0.2111241487755902</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3346331872038222</v>
+        <v>0.3488245861522454</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2425414668603453</v>
+        <v>0.2330757379363157</v>
       </c>
       <c r="C95">
-        <v>-2952.985545568873</v>
+        <v>-2916.87372192964</v>
       </c>
       <c r="D95">
-        <v>733.9234544311258</v>
+        <v>770.0352780703588</v>
       </c>
       <c r="E95">
         <v>3072.208999999999</v>
@@ -9077,37 +9077,37 @@
         <v>360.3</v>
       </c>
       <c r="M95">
-        <v>1088.4046122</v>
+        <v>1044.1245222</v>
       </c>
       <c r="N95">
-        <v>-728.1046122</v>
+        <v>-683.8245221999998</v>
       </c>
       <c r="O95">
-        <v>-218.43138366</v>
+        <v>-205.1473566599999</v>
       </c>
       <c r="P95">
-        <v>-509.67322854</v>
+        <v>-478.6771655399999</v>
       </c>
       <c r="Q95">
-        <v>-270.47322854</v>
+        <v>-239.4771655399999</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5235607140971759</v>
+        <v>0.5211931580396115</v>
       </c>
       <c r="T95">
-        <v>11.02664102623488</v>
+        <v>10.97905676765847</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09931049426694077</v>
+        <v>0.1035221352451826</v>
       </c>
       <c r="W95">
-        <v>0.221389480509186</v>
+        <v>0.211389480509186</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3310349808898025</v>
+        <v>0.3450737841506085</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2445414668603453</v>
+        <v>0.2349757379363157</v>
       </c>
       <c r="C96">
-        <v>-3007.818106192863</v>
+        <v>-2972.037238036799</v>
       </c>
       <c r="D96">
-        <v>726.7038938071365</v>
+        <v>762.4847619631998</v>
       </c>
       <c r="E96">
         <v>3119.822</v>
@@ -9159,37 +9159,37 @@
         <v>360.3</v>
       </c>
       <c r="M96">
-        <v>1100.1078876</v>
+        <v>1055.3516676</v>
       </c>
       <c r="N96">
-        <v>-739.8078876</v>
+        <v>-695.0516676</v>
       </c>
       <c r="O96">
-        <v>-221.94236628</v>
+        <v>-208.51550028</v>
       </c>
       <c r="P96">
-        <v>-517.86552132</v>
+        <v>-486.53616732</v>
       </c>
       <c r="Q96">
-        <v>-278.66552132</v>
+        <v>-247.33616732</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6031874997800387</v>
+        <v>0.6004253510462136</v>
       </c>
       <c r="T96">
-        <v>12.86441453060736</v>
+        <v>12.80889956226822</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09825399964707972</v>
+        <v>0.1024208359340636</v>
       </c>
       <c r="W96">
-        <v>0.2216491668867478</v>
+        <v>0.2116491668867478</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3275133321569323</v>
+        <v>0.3414027864468786</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2465414668603453</v>
+        <v>0.2368757379363158</v>
       </c>
       <c r="C97">
-        <v>-3062.510013651283</v>
+        <v>-3027.054120051847</v>
       </c>
       <c r="D97">
-        <v>719.624986348717</v>
+        <v>755.0808799481522</v>
       </c>
       <c r="E97">
         <v>3167.435</v>
@@ -9241,37 +9241,37 @@
         <v>360.3</v>
       </c>
       <c r="M97">
-        <v>1111.811163</v>
+        <v>1066.578813</v>
       </c>
       <c r="N97">
-        <v>-751.5111630000001</v>
+        <v>-706.2788129999999</v>
       </c>
       <c r="O97">
-        <v>-225.4533489</v>
+        <v>-211.8836439</v>
       </c>
       <c r="P97">
-        <v>-526.0578141000001</v>
+        <v>-494.3951691</v>
       </c>
       <c r="Q97">
-        <v>-286.8578141000001</v>
+        <v>-255.1951691</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7146649997360468</v>
+        <v>0.7113504212554568</v>
       </c>
       <c r="T97">
-        <v>15.43729743672884</v>
+        <v>15.37067947472187</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09721974701921569</v>
+        <v>0.1013427218715998</v>
       </c>
       <c r="W97">
-        <v>0.2219033861826768</v>
+        <v>0.2119033861826768</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3240658233973857</v>
+        <v>0.3378090729053325</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2485414668603452</v>
+        <v>0.2387757379363157</v>
       </c>
       <c r="C98">
-        <v>-3117.065338647648</v>
+        <v>-3081.928598436648</v>
       </c>
       <c r="D98">
-        <v>712.6826613523513</v>
+        <v>747.8194015633507</v>
       </c>
       <c r="E98">
         <v>3215.047999999999</v>
@@ -9323,37 +9323,37 @@
         <v>360.3</v>
       </c>
       <c r="M98">
-        <v>1123.5144384</v>
+        <v>1077.8059584</v>
       </c>
       <c r="N98">
-        <v>-763.2144383999998</v>
+        <v>-717.5059583999998</v>
       </c>
       <c r="O98">
-        <v>-228.9643315199999</v>
+        <v>-215.2517875199999</v>
       </c>
       <c r="P98">
-        <v>-534.2501068799999</v>
+        <v>-502.2541708799999</v>
       </c>
       <c r="Q98">
-        <v>-295.0501068799999</v>
+        <v>-263.0541708799999</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8818812496700564</v>
+        <v>0.8777380265693189</v>
       </c>
       <c r="T98">
-        <v>19.29662179591101</v>
+        <v>19.21334934340229</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0962070413210989</v>
+        <v>0.1002870685187706</v>
       </c>
       <c r="W98">
-        <v>0.2221523092432739</v>
+        <v>0.2121523092432739</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3206901377369963</v>
+        <v>0.3342902283959019</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2505414668603453</v>
+        <v>0.2406757379363157</v>
       </c>
       <c r="C99">
-        <v>-3171.487996303762</v>
+        <v>-3136.664742468766</v>
       </c>
       <c r="D99">
-        <v>705.8730036962374</v>
+        <v>740.6962575312332</v>
       </c>
       <c r="E99">
         <v>3262.661</v>
@@ -9405,37 +9405,37 @@
         <v>360.3</v>
       </c>
       <c r="M99">
-        <v>1135.2177138</v>
+        <v>1089.0331038</v>
       </c>
       <c r="N99">
-        <v>-774.9177138</v>
+        <v>-728.7331038</v>
       </c>
       <c r="O99">
-        <v>-232.47531414</v>
+        <v>-218.61993114</v>
       </c>
       <c r="P99">
-        <v>-542.44239966</v>
+        <v>-510.11317266</v>
       </c>
       <c r="Q99">
-        <v>-303.24239966</v>
+        <v>-270.91317266</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.160574999560076</v>
+        <v>1.155050702092425</v>
       </c>
       <c r="T99">
-        <v>25.72882906121468</v>
+        <v>25.61779912453639</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09521521615284013</v>
+        <v>0.09925318121445337</v>
       </c>
       <c r="W99">
-        <v>0.2223960998696319</v>
+        <v>0.2123960998696319</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3173840538428004</v>
+        <v>0.3308439373815112</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2525414668603452</v>
+        <v>0.2425757379363158</v>
       </c>
       <c r="C100">
-        <v>-3225.781753522252</v>
+        <v>-3191.266467845587</v>
       </c>
       <c r="D100">
-        <v>699.1922464777476</v>
+        <v>733.7075321544131</v>
       </c>
       <c r="E100">
         <v>3310.274</v>
@@ -9487,37 +9487,37 @@
         <v>360.3</v>
       </c>
       <c r="M100">
-        <v>1146.9209892</v>
+        <v>1100.2602492</v>
       </c>
       <c r="N100">
-        <v>-786.6209891999999</v>
+        <v>-739.9602491999999</v>
       </c>
       <c r="O100">
-        <v>-235.98629676</v>
+        <v>-221.98807476</v>
       </c>
       <c r="P100">
-        <v>-550.63469244</v>
+        <v>-517.9721744399999</v>
       </c>
       <c r="Q100">
-        <v>-311.43469244</v>
+        <v>-278.7721744399999</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.717962499340113</v>
+        <v>1.709676053138638</v>
       </c>
       <c r="T100">
-        <v>38.59324359182202</v>
+        <v>38.42669868680458</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09424363231454586</v>
+        <v>0.09824039365104058</v>
       </c>
       <c r="W100">
-        <v>0.2226349151770846</v>
+        <v>0.2126349151770847</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3141454410484861</v>
+        <v>0.3274679788368019</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2545414668603452</v>
+        <v>0.2444757379363157</v>
       </c>
       <c r="C101">
-        <v>-3279.950235934936</v>
+        <v>-3245.737543862023</v>
       </c>
       <c r="D101">
-        <v>692.6367640650632</v>
+        <v>726.8494561379763</v>
       </c>
       <c r="E101">
         <v>3357.886999999999</v>
@@ -9569,37 +9569,37 @@
         <v>360.3</v>
       </c>
       <c r="M101">
-        <v>1158.6242646</v>
+        <v>1111.4873946</v>
       </c>
       <c r="N101">
-        <v>-798.3242645999999</v>
+        <v>-751.1873945999998</v>
       </c>
       <c r="O101">
-        <v>-239.49727938</v>
+        <v>-225.3562183799999</v>
       </c>
       <c r="P101">
-        <v>-558.8269852199999</v>
+        <v>-525.8311762199999</v>
       </c>
       <c r="Q101">
-        <v>-319.6269852199999</v>
+        <v>-286.6311762199999</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.390124998680226</v>
+        <v>3.373552106277276</v>
       </c>
       <c r="T101">
-        <v>77.18648718364403</v>
+        <v>76.85339737360916</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.09329167643258074</v>
+        <v>0.09724806644244423</v>
       </c>
       <c r="W101">
-        <v>0.2228689059328717</v>
+        <v>0.2128689059328717</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3109722547752691</v>
+        <v>0.324160221474814</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/australia/australia_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_chemical_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08262264254354745</v>
+        <v>0.08240627461591679</v>
       </c>
       <c r="C2">
-        <v>4308.37199480726</v>
+        <v>4279.492598103548</v>
       </c>
       <c r="D2">
-        <v>3567.27199480726</v>
+        <v>3586.005598103548</v>
       </c>
       <c r="E2">
-        <v>-1355.8</v>
+        <v>-1308.187</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>47.61299999999999</v>
       </c>
       <c r="G2">
         <v>741.1</v>
@@ -1451,28 +1451,28 @@
         <v>360.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.3949339</v>
       </c>
       <c r="N2">
-        <v>360.3</v>
+        <v>357.9050661</v>
       </c>
       <c r="O2">
-        <v>108.09</v>
+        <v>107.37151983</v>
       </c>
       <c r="P2">
-        <v>252.21</v>
+        <v>250.53354627</v>
       </c>
       <c r="Q2">
-        <v>491.41</v>
+        <v>489.73354627</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08262264254354745</v>
+        <v>0.08288300466254223</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426664</v>
+        <v>0.8564204310055943</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.442565450345</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08240627461591679</v>
+        <v>0.08218990668828616</v>
       </c>
       <c r="C3">
-        <v>4279.492598103548</v>
+        <v>4250.810999960111</v>
       </c>
       <c r="D3">
-        <v>3586.005598103548</v>
+        <v>3604.93699996011</v>
       </c>
       <c r="E3">
-        <v>-1308.187</v>
+        <v>-1260.574</v>
       </c>
       <c r="F3">
-        <v>47.61299999999999</v>
+        <v>95.22599999999998</v>
       </c>
       <c r="G3">
         <v>741.1</v>
@@ -1533,28 +1533,28 @@
         <v>360.3</v>
       </c>
       <c r="M3">
-        <v>2.3949339</v>
+        <v>4.7898678</v>
       </c>
       <c r="N3">
-        <v>357.9050661</v>
+        <v>355.5101322</v>
       </c>
       <c r="O3">
-        <v>107.37151983</v>
+        <v>106.65303966</v>
       </c>
       <c r="P3">
-        <v>250.53354627</v>
+        <v>248.85709254</v>
       </c>
       <c r="Q3">
-        <v>489.73354627</v>
+        <v>488.05709254</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08288300466254223</v>
+        <v>0.08314868029416955</v>
       </c>
       <c r="T3">
-        <v>0.8564204310055943</v>
+        <v>0.862556126886133</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.442565450345</v>
+        <v>75.2212827251725</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08218990668828616</v>
+        <v>0.08197353876065552</v>
       </c>
       <c r="C4">
-        <v>4250.810999960111</v>
+        <v>4222.330349684049</v>
       </c>
       <c r="D4">
-        <v>3604.93699996011</v>
+        <v>3624.069349684049</v>
       </c>
       <c r="E4">
-        <v>-1260.574</v>
+        <v>-1212.961</v>
       </c>
       <c r="F4">
-        <v>95.22599999999998</v>
+        <v>142.839</v>
       </c>
       <c r="G4">
         <v>741.1</v>
@@ -1615,28 +1615,28 @@
         <v>360.3</v>
       </c>
       <c r="M4">
-        <v>4.7898678</v>
+        <v>7.1848017</v>
       </c>
       <c r="N4">
-        <v>355.5101322</v>
+        <v>353.1151983</v>
       </c>
       <c r="O4">
-        <v>106.65303966</v>
+        <v>105.93455949</v>
       </c>
       <c r="P4">
-        <v>248.85709254</v>
+        <v>247.18063881</v>
       </c>
       <c r="Q4">
-        <v>488.05709254</v>
+        <v>486.38063881</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08314868029416955</v>
+        <v>0.08341983377387167</v>
       </c>
       <c r="T4">
-        <v>0.862556126886133</v>
+        <v>0.8688183319600848</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.2212827251725</v>
+        <v>50.14752181678168</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08197353876065552</v>
+        <v>0.08175717083302488</v>
       </c>
       <c r="C5">
-        <v>4222.330349684049</v>
+        <v>4194.053863795993</v>
       </c>
       <c r="D5">
-        <v>3624.069349684049</v>
+        <v>3643.405863795992</v>
       </c>
       <c r="E5">
-        <v>-1212.961</v>
+        <v>-1165.348</v>
       </c>
       <c r="F5">
-        <v>142.839</v>
+        <v>190.452</v>
       </c>
       <c r="G5">
         <v>741.1</v>
@@ -1697,28 +1697,28 @@
         <v>360.3</v>
       </c>
       <c r="M5">
-        <v>7.1848017</v>
+        <v>9.579735599999999</v>
       </c>
       <c r="N5">
-        <v>353.1151983</v>
+        <v>350.7202644</v>
       </c>
       <c r="O5">
-        <v>105.93455949</v>
+        <v>105.21607932</v>
       </c>
       <c r="P5">
-        <v>247.18063881</v>
+        <v>245.50418508</v>
       </c>
       <c r="Q5">
-        <v>486.38063881</v>
+        <v>484.70418508</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08341983377387167</v>
+        <v>0.08369663628440091</v>
       </c>
       <c r="T5">
-        <v>0.8688183319600848</v>
+        <v>0.8752109996397441</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.14752181678168</v>
+        <v>37.61064136258626</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08175717083302488</v>
+        <v>0.08154080290539424</v>
       </c>
       <c r="C6">
-        <v>4194.053863795993</v>
+        <v>4165.98482783283</v>
       </c>
       <c r="D6">
-        <v>3643.405863795992</v>
+        <v>3662.94982783283</v>
       </c>
       <c r="E6">
-        <v>-1165.348</v>
+        <v>-1117.735</v>
       </c>
       <c r="F6">
-        <v>190.452</v>
+        <v>238.065</v>
       </c>
       <c r="G6">
         <v>741.1</v>
@@ -1779,28 +1779,28 @@
         <v>360.3</v>
       </c>
       <c r="M6">
-        <v>9.579735599999999</v>
+        <v>11.9746695</v>
       </c>
       <c r="N6">
-        <v>350.7202644</v>
+        <v>348.3253305</v>
       </c>
       <c r="O6">
-        <v>105.21607932</v>
+        <v>104.49759915</v>
       </c>
       <c r="P6">
-        <v>245.50418508</v>
+        <v>243.82773135</v>
       </c>
       <c r="Q6">
-        <v>484.70418508</v>
+        <v>483.02773135</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08369663628440091</v>
+        <v>0.08397926621620447</v>
       </c>
       <c r="T6">
-        <v>0.8752109996397441</v>
+        <v>0.8817382497968698</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.61064136258626</v>
+        <v>30.088513090069</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08154080290539424</v>
+        <v>0.08132443497776361</v>
       </c>
       <c r="C7">
-        <v>4165.98482783283</v>
+        <v>4138.126598208782</v>
       </c>
       <c r="D7">
-        <v>3662.94982783283</v>
+        <v>3682.704598208781</v>
       </c>
       <c r="E7">
-        <v>-1117.735</v>
+        <v>-1070.122</v>
       </c>
       <c r="F7">
-        <v>238.065</v>
+        <v>285.678</v>
       </c>
       <c r="G7">
         <v>741.1</v>
@@ -1861,28 +1861,28 @@
         <v>360.3</v>
       </c>
       <c r="M7">
-        <v>11.9746695</v>
+        <v>14.3696034</v>
       </c>
       <c r="N7">
-        <v>348.3253305</v>
+        <v>345.9303966</v>
       </c>
       <c r="O7">
-        <v>104.49759915</v>
+        <v>103.77911898</v>
       </c>
       <c r="P7">
-        <v>243.82773135</v>
+        <v>242.15127762</v>
       </c>
       <c r="Q7">
-        <v>483.02773135</v>
+        <v>481.35127762</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08397926621620447</v>
+        <v>0.08426790955081234</v>
       </c>
       <c r="T7">
-        <v>0.8817382497968698</v>
+        <v>0.8884043776169132</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.088513090069</v>
+        <v>25.07376090839083</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08132443497776361</v>
+        <v>0.08110806705013297</v>
       </c>
       <c r="C8">
-        <v>4138.126598208782</v>
+        <v>4110.482604137017</v>
       </c>
       <c r="D8">
-        <v>3682.704598208781</v>
+        <v>3702.673604137017</v>
       </c>
       <c r="E8">
-        <v>-1070.122</v>
+        <v>-1022.509</v>
       </c>
       <c r="F8">
-        <v>285.6779999999999</v>
+        <v>333.2909999999999</v>
       </c>
       <c r="G8">
         <v>741.1</v>
@@ -1943,28 +1943,28 @@
         <v>360.3</v>
       </c>
       <c r="M8">
-        <v>14.3696034</v>
+        <v>16.7645373</v>
       </c>
       <c r="N8">
-        <v>345.9303966</v>
+        <v>343.5354627</v>
       </c>
       <c r="O8">
-        <v>103.77911898</v>
+        <v>103.06063881</v>
       </c>
       <c r="P8">
-        <v>242.15127762</v>
+        <v>240.47482389</v>
       </c>
       <c r="Q8">
-        <v>481.35127762</v>
+        <v>479.67482389</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08426790955081234</v>
+        <v>0.08456276026896017</v>
       </c>
       <c r="T8">
-        <v>0.8884043776169132</v>
+        <v>0.8952138630244844</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.07376090839083</v>
+        <v>21.491795064335</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08110806705013296</v>
+        <v>0.08089169912250231</v>
       </c>
       <c r="C9">
-        <v>4110.482604137019</v>
+        <v>4083.056349614134</v>
       </c>
       <c r="D9">
-        <v>3702.673604137019</v>
+        <v>3722.860349614134</v>
       </c>
       <c r="E9">
-        <v>-1022.509</v>
+        <v>-974.8959999999997</v>
       </c>
       <c r="F9">
-        <v>333.291</v>
+        <v>380.9039999999999</v>
       </c>
       <c r="G9">
         <v>741.1</v>
@@ -2025,28 +2025,28 @@
         <v>360.3</v>
       </c>
       <c r="M9">
-        <v>16.7645373</v>
+        <v>19.1594712</v>
       </c>
       <c r="N9">
-        <v>343.5354627</v>
+        <v>341.1405288</v>
       </c>
       <c r="O9">
-        <v>103.06063881</v>
+        <v>102.34215864</v>
       </c>
       <c r="P9">
-        <v>240.47482389</v>
+        <v>238.79837016</v>
       </c>
       <c r="Q9">
-        <v>479.67482389</v>
+        <v>477.99837016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08456276026896017</v>
+        <v>0.08486402078532861</v>
       </c>
       <c r="T9">
-        <v>0.8952138630244844</v>
+        <v>0.9021713807235244</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.491795064335</v>
+        <v>18.80532068129313</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08089169912250231</v>
+        <v>0.08067533119487168</v>
       </c>
       <c r="C10">
-        <v>4083.056349614134</v>
+        <v>4055.851415469894</v>
       </c>
       <c r="D10">
-        <v>3722.860349614134</v>
+        <v>3743.268415469894</v>
       </c>
       <c r="E10">
-        <v>-974.8959999999997</v>
+        <v>-927.2829999999998</v>
       </c>
       <c r="F10">
-        <v>380.9039999999999</v>
+        <v>428.5169999999999</v>
       </c>
       <c r="G10">
         <v>741.1</v>
@@ -2107,28 +2107,28 @@
         <v>360.3</v>
       </c>
       <c r="M10">
-        <v>19.1594712</v>
+        <v>21.5544051</v>
       </c>
       <c r="N10">
-        <v>341.1405288</v>
+        <v>338.7455949</v>
       </c>
       <c r="O10">
-        <v>102.34215864</v>
+        <v>101.62367847</v>
       </c>
       <c r="P10">
-        <v>238.79837016</v>
+        <v>237.12191643</v>
       </c>
       <c r="Q10">
-        <v>477.99837016</v>
+        <v>476.32191643</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08486402078532861</v>
+        <v>0.08517190241194689</v>
       </c>
       <c r="T10">
-        <v>0.9021713807235244</v>
+        <v>0.9092818108994664</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.80532068129313</v>
+        <v>16.71584060559389</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08067533119487168</v>
+        <v>0.08045896326724103</v>
       </c>
       <c r="C11">
-        <v>4055.851415469894</v>
+        <v>4028.871461484778</v>
       </c>
       <c r="D11">
-        <v>3743.268415469894</v>
+        <v>3763.901461484778</v>
       </c>
       <c r="E11">
-        <v>-927.2829999999998</v>
+        <v>-879.6699999999998</v>
       </c>
       <c r="F11">
-        <v>428.5169999999999</v>
+        <v>476.1299999999999</v>
       </c>
       <c r="G11">
         <v>741.1</v>
@@ -2189,28 +2189,28 @@
         <v>360.3</v>
       </c>
       <c r="M11">
-        <v>21.5544051</v>
+        <v>23.94933899999999</v>
       </c>
       <c r="N11">
-        <v>338.7455949</v>
+        <v>336.350661</v>
       </c>
       <c r="O11">
-        <v>101.62367847</v>
+        <v>100.9051983</v>
       </c>
       <c r="P11">
-        <v>237.12191643</v>
+        <v>235.4454627</v>
       </c>
       <c r="Q11">
-        <v>476.32191643</v>
+        <v>474.6454627</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08517190241194689</v>
+        <v>0.08548662585249003</v>
       </c>
       <c r="T11">
-        <v>0.9092818108994664</v>
+        <v>0.9165502506348737</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.71584060559389</v>
+        <v>15.0442565450345</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08045896326724103</v>
+        <v>0.08024259533961038</v>
       </c>
       <c r="C12">
-        <v>4028.871461484778</v>
+        <v>4002.120228577931</v>
       </c>
       <c r="D12">
-        <v>3763.901461484778</v>
+        <v>3784.763228577931</v>
       </c>
       <c r="E12">
-        <v>-879.6699999999998</v>
+        <v>-832.0569999999998</v>
       </c>
       <c r="F12">
-        <v>476.1299999999999</v>
+        <v>523.7429999999999</v>
       </c>
       <c r="G12">
         <v>741.1</v>
@@ -2271,28 +2271,28 @@
         <v>360.3</v>
       </c>
       <c r="M12">
-        <v>23.949339</v>
+        <v>26.3442729</v>
       </c>
       <c r="N12">
-        <v>336.350661</v>
+        <v>333.9557271</v>
       </c>
       <c r="O12">
-        <v>100.9051983</v>
+        <v>100.18671813</v>
       </c>
       <c r="P12">
-        <v>235.4454627</v>
+        <v>233.76900897</v>
       </c>
       <c r="Q12">
-        <v>474.6454627</v>
+        <v>472.96900897</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08548662585249003</v>
+        <v>0.0858084217298993</v>
       </c>
       <c r="T12">
-        <v>0.9165502506348737</v>
+        <v>0.9239820260946724</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.0442565450345</v>
+        <v>13.67659685912227</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08024259533961038</v>
+        <v>0.08015222741197975</v>
       </c>
       <c r="C13">
-        <v>4002.120228577931</v>
+        <v>3963.288947227009</v>
       </c>
       <c r="D13">
-        <v>3784.763228577931</v>
+        <v>3793.544947227009</v>
       </c>
       <c r="E13">
-        <v>-832.0569999999998</v>
+        <v>-784.4439999999998</v>
       </c>
       <c r="F13">
-        <v>523.7429999999999</v>
+        <v>571.3559999999999</v>
       </c>
       <c r="G13">
         <v>741.1</v>
@@ -2353,45 +2353,45 @@
         <v>360.3</v>
       </c>
       <c r="M13">
-        <v>26.3442729</v>
+        <v>29.5962408</v>
       </c>
       <c r="N13">
-        <v>333.9557271</v>
+        <v>330.7037592</v>
       </c>
       <c r="O13">
-        <v>100.18671813</v>
+        <v>99.21112776000001</v>
       </c>
       <c r="P13">
-        <v>233.76900897</v>
+        <v>231.49263144</v>
       </c>
       <c r="Q13">
-        <v>472.96900897</v>
+        <v>470.69263144</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0858084217298993</v>
+        <v>0.08613753114997699</v>
       </c>
       <c r="T13">
-        <v>0.9239820260946724</v>
+        <v>0.9315827055421937</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03521</v>
+        <v>0.03626</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.67659685912227</v>
+        <v>12.17384337540598</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08015222741197975</v>
+        <v>0.07994635948434911</v>
       </c>
       <c r="C14">
-        <v>3963.288947227009</v>
+        <v>3935.834628260126</v>
       </c>
       <c r="D14">
-        <v>3793.544947227009</v>
+        <v>3813.703628260126</v>
       </c>
       <c r="E14">
-        <v>-784.4439999999998</v>
+        <v>-736.8309999999998</v>
       </c>
       <c r="F14">
-        <v>571.3559999999999</v>
+        <v>618.9689999999999</v>
       </c>
       <c r="G14">
         <v>741.1</v>
@@ -2435,28 +2435,28 @@
         <v>360.3</v>
       </c>
       <c r="M14">
-        <v>29.5962408</v>
+        <v>32.0625942</v>
       </c>
       <c r="N14">
-        <v>330.7037592</v>
+        <v>328.2374058</v>
       </c>
       <c r="O14">
-        <v>99.21112776000001</v>
+        <v>98.47122174</v>
       </c>
       <c r="P14">
-        <v>231.49263144</v>
+        <v>229.76618406</v>
       </c>
       <c r="Q14">
-        <v>470.69263144</v>
+        <v>468.96618406</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08613753114997699</v>
+        <v>0.08647420630384954</v>
       </c>
       <c r="T14">
-        <v>0.9315827055421937</v>
+        <v>0.9393581132528763</v>
       </c>
       <c r="U14">
         <v>0.05180000000000001</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.17384337540598</v>
+        <v>11.23739388499013</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07994635948434911</v>
+        <v>0.07974049155671845</v>
       </c>
       <c r="C15">
-        <v>3935.834628260126</v>
+        <v>3908.59569801432</v>
       </c>
       <c r="D15">
-        <v>3813.703628260126</v>
+        <v>3834.077698014319</v>
       </c>
       <c r="E15">
-        <v>-736.8309999999998</v>
+        <v>-689.2179999999997</v>
       </c>
       <c r="F15">
-        <v>618.9689999999999</v>
+        <v>666.582</v>
       </c>
       <c r="G15">
         <v>741.1</v>
@@ -2517,28 +2517,28 @@
         <v>360.3</v>
       </c>
       <c r="M15">
-        <v>32.0625942</v>
+        <v>34.5289476</v>
       </c>
       <c r="N15">
-        <v>328.2374058</v>
+        <v>325.7710524</v>
       </c>
       <c r="O15">
-        <v>98.47122174</v>
+        <v>97.73131572000001</v>
       </c>
       <c r="P15">
-        <v>229.76618406</v>
+        <v>228.03973668</v>
       </c>
       <c r="Q15">
-        <v>468.96618406</v>
+        <v>467.23973668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08647420630384954</v>
+        <v>0.08681871111246332</v>
       </c>
       <c r="T15">
-        <v>0.9393581132528763</v>
+        <v>0.9473143443986911</v>
       </c>
       <c r="U15">
         <v>0.05180000000000001</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.23739388499013</v>
+        <v>10.43472289320512</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07974049155671845</v>
+        <v>0.07971312362908781</v>
       </c>
       <c r="C16">
-        <v>3908.59569801432</v>
+        <v>3863.707616570362</v>
       </c>
       <c r="D16">
-        <v>3834.077698014319</v>
+        <v>3836.802616570362</v>
       </c>
       <c r="E16">
-        <v>-689.2179999999997</v>
+        <v>-641.6049999999997</v>
       </c>
       <c r="F16">
-        <v>666.582</v>
+        <v>714.1950000000001</v>
       </c>
       <c r="G16">
         <v>741.1</v>
@@ -2599,45 +2599,45 @@
         <v>360.3</v>
       </c>
       <c r="M16">
-        <v>34.5289476</v>
+        <v>38.20943250000001</v>
       </c>
       <c r="N16">
-        <v>325.7710524</v>
+        <v>322.0905675</v>
       </c>
       <c r="O16">
-        <v>97.73131572000001</v>
+        <v>96.62717025000001</v>
       </c>
       <c r="P16">
-        <v>228.03973668</v>
+        <v>225.46339725</v>
       </c>
       <c r="Q16">
-        <v>467.23973668</v>
+        <v>464.66339725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08681871111246332</v>
+        <v>0.0871713219165739</v>
       </c>
       <c r="T16">
-        <v>0.9473143443986911</v>
+        <v>0.9554577809832311</v>
       </c>
       <c r="U16">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03626</v>
+        <v>0.03745</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.43472289320512</v>
+        <v>9.429608775267729</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07971312362908781</v>
+        <v>0.07951915570145716</v>
       </c>
       <c r="C17">
-        <v>3863.707616570362</v>
+        <v>3835.51881922453</v>
       </c>
       <c r="D17">
-        <v>3836.802616570362</v>
+        <v>3856.22681922453</v>
       </c>
       <c r="E17">
-        <v>-641.6049999999999</v>
+        <v>-593.9919999999998</v>
       </c>
       <c r="F17">
-        <v>714.1949999999998</v>
+        <v>761.8079999999999</v>
       </c>
       <c r="G17">
         <v>741.1</v>
@@ -2681,28 +2681,28 @@
         <v>360.3</v>
       </c>
       <c r="M17">
-        <v>38.20943249999999</v>
+        <v>40.756728</v>
       </c>
       <c r="N17">
-        <v>322.0905675</v>
+        <v>319.543272</v>
       </c>
       <c r="O17">
-        <v>96.62717025000001</v>
+        <v>95.8629816</v>
       </c>
       <c r="P17">
-        <v>225.46339725</v>
+        <v>223.6802904</v>
       </c>
       <c r="Q17">
-        <v>464.66339725</v>
+        <v>462.8802904</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0871713219165739</v>
+        <v>0.08753232821602044</v>
       </c>
       <c r="T17">
-        <v>0.9554577809832311</v>
+        <v>0.963795108915022</v>
       </c>
       <c r="U17">
         <v>0.05350000000000001</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.429608775267733</v>
+        <v>8.840258226813498</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07951915570145716</v>
+        <v>0.07932518777382652</v>
       </c>
       <c r="C18">
-        <v>3835.51881922453</v>
+        <v>3807.527696621855</v>
       </c>
       <c r="D18">
-        <v>3856.22681922453</v>
+        <v>3875.848696621854</v>
       </c>
       <c r="E18">
-        <v>-593.9919999999998</v>
+        <v>-546.3789999999998</v>
       </c>
       <c r="F18">
-        <v>761.8079999999999</v>
+        <v>809.4209999999999</v>
       </c>
       <c r="G18">
         <v>741.1</v>
@@ -2763,28 +2763,28 @@
         <v>360.3</v>
       </c>
       <c r="M18">
-        <v>40.756728</v>
+        <v>43.3040235</v>
       </c>
       <c r="N18">
-        <v>319.543272</v>
+        <v>316.9959765</v>
       </c>
       <c r="O18">
-        <v>95.8629816</v>
+        <v>95.09879294999999</v>
       </c>
       <c r="P18">
-        <v>223.6802904</v>
+        <v>221.89718355</v>
       </c>
       <c r="Q18">
-        <v>462.8802904</v>
+        <v>461.09718355</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08753232821602044</v>
+        <v>0.0879020334624416</v>
       </c>
       <c r="T18">
-        <v>0.963795108915022</v>
+        <v>0.9723333363150488</v>
       </c>
       <c r="U18">
         <v>0.05350000000000001</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.840258226813498</v>
+        <v>8.320243037000939</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07932518777382652</v>
+        <v>0.07913121984619588</v>
       </c>
       <c r="C19">
-        <v>3807.527696621855</v>
+        <v>3779.737281716966</v>
       </c>
       <c r="D19">
-        <v>3875.848696621854</v>
+        <v>3895.671281716965</v>
       </c>
       <c r="E19">
-        <v>-546.3789999999998</v>
+        <v>-498.7659999999997</v>
       </c>
       <c r="F19">
-        <v>809.4209999999999</v>
+        <v>857.034</v>
       </c>
       <c r="G19">
         <v>741.1</v>
@@ -2845,28 +2845,28 @@
         <v>360.3</v>
       </c>
       <c r="M19">
-        <v>43.3040235</v>
+        <v>45.851319</v>
       </c>
       <c r="N19">
-        <v>316.9959765</v>
+        <v>314.448681</v>
       </c>
       <c r="O19">
-        <v>95.09879294999999</v>
+        <v>94.33460430000001</v>
       </c>
       <c r="P19">
-        <v>221.89718355</v>
+        <v>220.1140767</v>
       </c>
       <c r="Q19">
-        <v>461.09718355</v>
+        <v>459.3140767</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0879020334624416</v>
+        <v>0.08828075590999498</v>
       </c>
       <c r="T19">
-        <v>0.9723333363150488</v>
+        <v>0.9810798131638565</v>
       </c>
       <c r="U19">
         <v>0.05350000000000001</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.320243037000939</v>
+        <v>7.858007312723108</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07913121984619589</v>
+        <v>0.07904365191856526</v>
       </c>
       <c r="C20">
-        <v>3779.737281716964</v>
+        <v>3741.139885889275</v>
       </c>
       <c r="D20">
-        <v>3895.671281716964</v>
+        <v>3904.686885889275</v>
       </c>
       <c r="E20">
-        <v>-498.7659999999998</v>
+        <v>-451.1529999999999</v>
       </c>
       <c r="F20">
-        <v>857.0339999999999</v>
+        <v>904.6469999999998</v>
       </c>
       <c r="G20">
         <v>741.1</v>
@@ -2927,45 +2927,45 @@
         <v>360.3</v>
       </c>
       <c r="M20">
-        <v>45.851319</v>
+        <v>49.12233209999999</v>
       </c>
       <c r="N20">
-        <v>314.448681</v>
+        <v>311.1776679</v>
       </c>
       <c r="O20">
-        <v>94.33460430000001</v>
+        <v>93.35330037</v>
       </c>
       <c r="P20">
-        <v>220.1140767</v>
+        <v>217.82436753</v>
       </c>
       <c r="Q20">
-        <v>459.3140767</v>
+        <v>457.02436753</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08828075590999498</v>
+        <v>0.0886688295290929</v>
       </c>
       <c r="T20">
-        <v>0.9810798131638565</v>
+        <v>0.990042252403993</v>
       </c>
       <c r="U20">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.858007312723109</v>
+        <v>7.334749483524624</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07904365191856526</v>
+        <v>0.0788552839909346</v>
       </c>
       <c r="C21">
-        <v>3741.139885889275</v>
+        <v>3713.062544100439</v>
       </c>
       <c r="D21">
-        <v>3904.686885889275</v>
+        <v>3924.222544100438</v>
       </c>
       <c r="E21">
-        <v>-451.1529999999999</v>
+        <v>-403.5399999999998</v>
       </c>
       <c r="F21">
-        <v>904.6469999999998</v>
+        <v>952.2599999999999</v>
       </c>
       <c r="G21">
         <v>741.1</v>
@@ -3009,28 +3009,28 @@
         <v>360.3</v>
       </c>
       <c r="M21">
-        <v>49.12233209999999</v>
+        <v>51.707718</v>
       </c>
       <c r="N21">
-        <v>311.1776679</v>
+        <v>308.592282</v>
       </c>
       <c r="O21">
-        <v>93.35330037</v>
+        <v>92.5776846</v>
       </c>
       <c r="P21">
-        <v>217.82436753</v>
+        <v>216.0145974</v>
       </c>
       <c r="Q21">
-        <v>457.02436753</v>
+        <v>455.2145974</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0886688295290929</v>
+        <v>0.08906660498866825</v>
       </c>
       <c r="T21">
-        <v>0.990042252403993</v>
+        <v>0.9992287526251331</v>
       </c>
       <c r="U21">
         <v>0.05430000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.334749483524624</v>
+        <v>6.968012009348392</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0788552839909346</v>
+        <v>0.07866691606330398</v>
       </c>
       <c r="C22">
-        <v>3713.062544100439</v>
+        <v>3685.181664132195</v>
       </c>
       <c r="D22">
-        <v>3924.222544100438</v>
+        <v>3943.954664132195</v>
       </c>
       <c r="E22">
-        <v>-403.5399999999998</v>
+        <v>-355.9269999999998</v>
       </c>
       <c r="F22">
-        <v>952.2599999999999</v>
+        <v>999.8729999999999</v>
       </c>
       <c r="G22">
         <v>741.1</v>
@@ -3091,28 +3091,28 @@
         <v>360.3</v>
       </c>
       <c r="M22">
-        <v>51.707718</v>
+        <v>54.29310390000001</v>
       </c>
       <c r="N22">
-        <v>308.592282</v>
+        <v>306.0068961</v>
       </c>
       <c r="O22">
-        <v>92.5776846</v>
+        <v>91.80206883</v>
       </c>
       <c r="P22">
-        <v>216.0145974</v>
+        <v>214.20482727</v>
       </c>
       <c r="Q22">
-        <v>455.2145974</v>
+        <v>453.40482727</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08906660498866825</v>
+        <v>0.089474450713043</v>
       </c>
       <c r="T22">
-        <v>0.9992287526251331</v>
+        <v>1.008647822472125</v>
       </c>
       <c r="U22">
         <v>0.05430000000000001</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.968012009348392</v>
+        <v>6.636201913665134</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07866691606330398</v>
+        <v>0.07847854813567333</v>
       </c>
       <c r="C23">
-        <v>3685.181664132196</v>
+        <v>3657.500224561374</v>
       </c>
       <c r="D23">
-        <v>3943.954664132195</v>
+        <v>3963.886224561374</v>
       </c>
       <c r="E23">
-        <v>-355.9269999999999</v>
+        <v>-308.3139999999999</v>
       </c>
       <c r="F23">
-        <v>999.8729999999998</v>
+        <v>1047.486</v>
       </c>
       <c r="G23">
         <v>741.1</v>
@@ -3173,28 +3173,28 @@
         <v>360.3</v>
       </c>
       <c r="M23">
-        <v>54.2931039</v>
+        <v>56.8784898</v>
       </c>
       <c r="N23">
-        <v>306.0068961</v>
+        <v>303.4215102</v>
       </c>
       <c r="O23">
-        <v>91.80206883</v>
+        <v>91.02645305999999</v>
       </c>
       <c r="P23">
-        <v>214.20482727</v>
+        <v>212.39505714</v>
       </c>
       <c r="Q23">
-        <v>453.40482727</v>
+        <v>451.59505714</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.089474450713043</v>
+        <v>0.089892754020094</v>
       </c>
       <c r="T23">
-        <v>1.008647822472124</v>
+        <v>1.018308406930577</v>
       </c>
       <c r="U23">
         <v>0.05430000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.636201913665135</v>
+        <v>6.334556372134901</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07847854813567333</v>
+        <v>0.07845118020804269</v>
       </c>
       <c r="C24">
-        <v>3657.500224561374</v>
+        <v>3612.799849194063</v>
       </c>
       <c r="D24">
-        <v>3963.886224561374</v>
+        <v>3966.798849194063</v>
       </c>
       <c r="E24">
-        <v>-308.3139999999999</v>
+        <v>-260.7009999999998</v>
       </c>
       <c r="F24">
-        <v>1047.486</v>
+        <v>1095.099</v>
       </c>
       <c r="G24">
         <v>741.1</v>
@@ -3255,45 +3255,45 @@
         <v>360.3</v>
       </c>
       <c r="M24">
-        <v>56.8784898</v>
+        <v>60.55897470000001</v>
       </c>
       <c r="N24">
-        <v>303.4215102</v>
+        <v>299.7410253</v>
       </c>
       <c r="O24">
-        <v>91.02645305999999</v>
+        <v>89.92230758999999</v>
       </c>
       <c r="P24">
-        <v>212.39505714</v>
+        <v>209.81871771</v>
       </c>
       <c r="Q24">
-        <v>451.59505714</v>
+        <v>449.01871771</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.089892754020094</v>
+        <v>0.09032192234810738</v>
       </c>
       <c r="T24">
-        <v>1.018308406930577</v>
+        <v>1.028219915660678</v>
       </c>
       <c r="U24">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.334556372134901</v>
+        <v>5.949572326560541</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07845118020804269</v>
+        <v>0.07826981228041203</v>
       </c>
       <c r="C25">
-        <v>3612.799849194063</v>
+        <v>3584.597587068911</v>
       </c>
       <c r="D25">
-        <v>3966.798849194063</v>
+        <v>3986.209587068911</v>
       </c>
       <c r="E25">
-        <v>-260.7009999999998</v>
+        <v>-213.0879999999997</v>
       </c>
       <c r="F25">
-        <v>1095.099</v>
+        <v>1142.712</v>
       </c>
       <c r="G25">
         <v>741.1</v>
@@ -3337,28 +3337,28 @@
         <v>360.3</v>
       </c>
       <c r="M25">
-        <v>60.55897470000001</v>
+        <v>63.19197360000001</v>
       </c>
       <c r="N25">
-        <v>299.7410253</v>
+        <v>297.1080264</v>
       </c>
       <c r="O25">
-        <v>89.92230758999999</v>
+        <v>89.13240791999999</v>
       </c>
       <c r="P25">
-        <v>209.81871771</v>
+        <v>207.97561848</v>
       </c>
       <c r="Q25">
-        <v>449.01871771</v>
+        <v>447.17561848</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09032192234810738</v>
+        <v>0.09076238457948951</v>
       </c>
       <c r="T25">
-        <v>1.028219915660678</v>
+        <v>1.038392253567887</v>
       </c>
       <c r="U25">
         <v>0.05530000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.949572326560541</v>
+        <v>5.701673479620518</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07826981228041203</v>
+        <v>0.07808844435278139</v>
       </c>
       <c r="C26">
-        <v>3584.597587068912</v>
+        <v>3556.586224208903</v>
       </c>
       <c r="D26">
-        <v>3986.209587068911</v>
+        <v>4005.811224208903</v>
       </c>
       <c r="E26">
-        <v>-213.088</v>
+        <v>-165.4749999999999</v>
       </c>
       <c r="F26">
-        <v>1142.712</v>
+        <v>1190.325</v>
       </c>
       <c r="G26">
         <v>741.1</v>
@@ -3419,28 +3419,28 @@
         <v>360.3</v>
       </c>
       <c r="M26">
-        <v>63.1919736</v>
+        <v>65.8249725</v>
       </c>
       <c r="N26">
-        <v>297.1080264</v>
+        <v>294.4750275</v>
       </c>
       <c r="O26">
-        <v>89.13240792000001</v>
+        <v>88.34250824999999</v>
       </c>
       <c r="P26">
-        <v>207.97561848</v>
+        <v>206.13251925</v>
       </c>
       <c r="Q26">
-        <v>447.17561848</v>
+        <v>445.33251925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09076238457948951</v>
+        <v>0.09121459247037519</v>
       </c>
       <c r="T26">
-        <v>1.038392253567887</v>
+        <v>1.048835853819289</v>
       </c>
       <c r="U26">
         <v>0.05530000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.70167347962052</v>
+        <v>5.473606540435699</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07808844435278139</v>
+        <v>0.07790707642515074</v>
       </c>
       <c r="C27">
-        <v>3556.586224208903</v>
+        <v>3528.768590693171</v>
       </c>
       <c r="D27">
-        <v>4005.811224208903</v>
+        <v>4025.606590693171</v>
       </c>
       <c r="E27">
-        <v>-165.4749999999999</v>
+        <v>-117.8619999999999</v>
       </c>
       <c r="F27">
-        <v>1190.325</v>
+        <v>1237.938</v>
       </c>
       <c r="G27">
         <v>741.1</v>
@@ -3501,28 +3501,28 @@
         <v>360.3</v>
       </c>
       <c r="M27">
-        <v>65.8249725</v>
+        <v>68.45797140000001</v>
       </c>
       <c r="N27">
-        <v>294.4750275</v>
+        <v>291.8420286</v>
       </c>
       <c r="O27">
-        <v>88.34250824999999</v>
+        <v>87.55260858</v>
       </c>
       <c r="P27">
-        <v>206.13251925</v>
+        <v>204.28942002</v>
       </c>
       <c r="Q27">
-        <v>445.33251925</v>
+        <v>443.48942002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09121459247037519</v>
+        <v>0.09167902219614966</v>
       </c>
       <c r="T27">
-        <v>1.048835853819289</v>
+        <v>1.059561713536944</v>
       </c>
       <c r="U27">
         <v>0.05530000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.473606540435699</v>
+        <v>5.263083211957402</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07790707642515074</v>
+        <v>0.07772570849752011</v>
       </c>
       <c r="C28">
-        <v>3528.768590693171</v>
+        <v>3501.147572819838</v>
       </c>
       <c r="D28">
-        <v>4025.606590693171</v>
+        <v>4045.598572819837</v>
       </c>
       <c r="E28">
-        <v>-117.8619999999999</v>
+        <v>-70.2489999999998</v>
       </c>
       <c r="F28">
-        <v>1237.938</v>
+        <v>1285.551</v>
       </c>
       <c r="G28">
         <v>741.1</v>
@@ -3583,28 +3583,28 @@
         <v>360.3</v>
       </c>
       <c r="M28">
-        <v>68.45797140000001</v>
+        <v>71.09097030000001</v>
       </c>
       <c r="N28">
-        <v>291.8420286</v>
+        <v>289.2090297</v>
       </c>
       <c r="O28">
-        <v>87.55260858</v>
+        <v>86.76270890999999</v>
       </c>
       <c r="P28">
-        <v>204.28942002</v>
+        <v>202.44632079</v>
       </c>
       <c r="Q28">
-        <v>443.48942002</v>
+        <v>441.64632079</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09167902219614966</v>
+        <v>0.09215617602400016</v>
       </c>
       <c r="T28">
-        <v>1.059561713536944</v>
+        <v>1.070581432424946</v>
       </c>
       <c r="U28">
         <v>0.05530000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.263083211957402</v>
+        <v>5.068154204107127</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07772570849752011</v>
+        <v>0.07754434056988946</v>
       </c>
       <c r="C29">
-        <v>3501.147572819838</v>
+        <v>3473.726114508978</v>
       </c>
       <c r="D29">
-        <v>4045.598572819837</v>
+        <v>4065.790114508977</v>
       </c>
       <c r="E29">
-        <v>-70.2489999999998</v>
+        <v>-22.63599999999974</v>
       </c>
       <c r="F29">
-        <v>1285.551</v>
+        <v>1333.164</v>
       </c>
       <c r="G29">
         <v>741.1</v>
@@ -3665,28 +3665,28 @@
         <v>360.3</v>
       </c>
       <c r="M29">
-        <v>71.09097030000001</v>
+        <v>73.72396920000001</v>
       </c>
       <c r="N29">
-        <v>289.2090297</v>
+        <v>286.5760308</v>
       </c>
       <c r="O29">
-        <v>86.76270890999999</v>
+        <v>85.97280924</v>
       </c>
       <c r="P29">
-        <v>202.44632079</v>
+        <v>200.60322156</v>
       </c>
       <c r="Q29">
-        <v>441.64632079</v>
+        <v>439.80322156</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09215617602400016</v>
+        <v>0.09264658412484648</v>
       </c>
       <c r="T29">
-        <v>1.070581432424946</v>
+        <v>1.081907254615392</v>
       </c>
       <c r="U29">
         <v>0.05530000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.068154204107127</v>
+        <v>4.887148696817587</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07754434056988946</v>
+        <v>0.07736297264225883</v>
       </c>
       <c r="C30">
-        <v>3473.726114508978</v>
+        <v>3446.507218747754</v>
       </c>
       <c r="D30">
-        <v>4065.790114508977</v>
+        <v>4086.184218747755</v>
       </c>
       <c r="E30">
-        <v>-22.63599999999974</v>
+        <v>24.97700000000032</v>
       </c>
       <c r="F30">
-        <v>1333.164</v>
+        <v>1380.777</v>
       </c>
       <c r="G30">
         <v>741.1</v>
@@ -3747,28 +3747,28 @@
         <v>360.3</v>
       </c>
       <c r="M30">
-        <v>73.72396920000001</v>
+        <v>76.35696810000002</v>
       </c>
       <c r="N30">
-        <v>286.5760308</v>
+        <v>283.9430319</v>
       </c>
       <c r="O30">
-        <v>85.97280924</v>
+        <v>85.18290956999999</v>
       </c>
       <c r="P30">
-        <v>200.60322156</v>
+        <v>198.76012233</v>
       </c>
       <c r="Q30">
-        <v>439.80322156</v>
+        <v>437.96012233</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09264658412484648</v>
+        <v>0.09315080653839272</v>
       </c>
       <c r="T30">
-        <v>1.081907254615392</v>
+        <v>1.09355211405064</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.887148696817587</v>
+        <v>4.718626327961808</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07736297264225883</v>
+        <v>0.07718160471462819</v>
       </c>
       <c r="C31">
-        <v>3446.507218747755</v>
+        <v>3419.49394907933</v>
       </c>
       <c r="D31">
-        <v>4086.184218747755</v>
+        <v>4106.783949079329</v>
       </c>
       <c r="E31">
-        <v>24.97699999999986</v>
+        <v>72.58999999999992</v>
       </c>
       <c r="F31">
-        <v>1380.777</v>
+        <v>1428.39</v>
       </c>
       <c r="G31">
         <v>741.1</v>
@@ -3829,28 +3829,28 @@
         <v>360.3</v>
       </c>
       <c r="M31">
-        <v>76.35696809999999</v>
+        <v>78.98996699999999</v>
       </c>
       <c r="N31">
-        <v>283.9430319000001</v>
+        <v>281.310033</v>
       </c>
       <c r="O31">
-        <v>85.18290957000001</v>
+        <v>84.39300990000001</v>
       </c>
       <c r="P31">
-        <v>198.7601223300001</v>
+        <v>196.9170231</v>
       </c>
       <c r="Q31">
-        <v>437.96012233</v>
+        <v>436.1170231</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09315080653839272</v>
+        <v>0.0936694353066117</v>
       </c>
       <c r="T31">
-        <v>1.09355211405064</v>
+        <v>1.105529683755466</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.718626327961811</v>
+        <v>4.561338783696416</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07718160471462819</v>
+        <v>0.07754273678699754</v>
       </c>
       <c r="C32">
-        <v>3419.49394907933</v>
+        <v>3331.066561384714</v>
       </c>
       <c r="D32">
-        <v>4106.783949079329</v>
+        <v>4065.969561384713</v>
       </c>
       <c r="E32">
-        <v>72.58999999999992</v>
+        <v>120.203</v>
       </c>
       <c r="F32">
-        <v>1428.39</v>
+        <v>1476.003</v>
       </c>
       <c r="G32">
         <v>741.1</v>
@@ -3911,45 +3911,45 @@
         <v>360.3</v>
       </c>
       <c r="M32">
-        <v>78.98996699999999</v>
+        <v>85.31297339999999</v>
       </c>
       <c r="N32">
-        <v>281.310033</v>
+        <v>274.9870266</v>
       </c>
       <c r="O32">
-        <v>84.39300990000001</v>
+        <v>82.49610798</v>
       </c>
       <c r="P32">
-        <v>196.9170231</v>
+        <v>192.49091862</v>
       </c>
       <c r="Q32">
-        <v>436.1170231</v>
+        <v>431.69091862</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0936694353066117</v>
+        <v>0.09420309679275006</v>
       </c>
       <c r="T32">
-        <v>1.105529683755466</v>
+        <v>1.117854429393766</v>
       </c>
       <c r="U32">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.561338783696416</v>
+        <v>4.223273268306929</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07754273678699754</v>
+        <v>0.0773788688593669</v>
       </c>
       <c r="C33">
-        <v>3331.066561384714</v>
+        <v>3301.872575623271</v>
       </c>
       <c r="D33">
-        <v>4065.969561384713</v>
+        <v>4084.388575623271</v>
       </c>
       <c r="E33">
-        <v>120.203</v>
+        <v>167.816</v>
       </c>
       <c r="F33">
-        <v>1476.003</v>
+        <v>1523.616</v>
       </c>
       <c r="G33">
         <v>741.1</v>
@@ -3993,28 +3993,28 @@
         <v>360.3</v>
       </c>
       <c r="M33">
-        <v>85.31297339999999</v>
+        <v>88.0650048</v>
       </c>
       <c r="N33">
-        <v>274.9870266</v>
+        <v>272.2349952</v>
       </c>
       <c r="O33">
-        <v>82.49610798</v>
+        <v>81.67049856</v>
       </c>
       <c r="P33">
-        <v>192.49091862</v>
+        <v>190.56449664</v>
       </c>
       <c r="Q33">
-        <v>431.69091862</v>
+        <v>429.76449664</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09420309679275006</v>
+        <v>0.09475245420495132</v>
       </c>
       <c r="T33">
-        <v>1.117854429393766</v>
+        <v>1.130541667550839</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.223273268306929</v>
+        <v>4.091295978672337</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0773788688593669</v>
+        <v>0.07802350093173625</v>
       </c>
       <c r="C34">
-        <v>3301.872575623271</v>
+        <v>3182.748046998006</v>
       </c>
       <c r="D34">
-        <v>4084.388575623271</v>
+        <v>4012.877046998005</v>
       </c>
       <c r="E34">
-        <v>167.816</v>
+        <v>215.4290000000001</v>
       </c>
       <c r="F34">
-        <v>1523.616</v>
+        <v>1571.229</v>
       </c>
       <c r="G34">
         <v>741.1</v>
@@ -4075,45 +4075,45 @@
         <v>360.3</v>
       </c>
       <c r="M34">
-        <v>88.0650048</v>
+        <v>96.31633770000001</v>
       </c>
       <c r="N34">
-        <v>272.2349952</v>
+        <v>263.9836623</v>
       </c>
       <c r="O34">
-        <v>81.67049856</v>
+        <v>79.19509868999999</v>
       </c>
       <c r="P34">
-        <v>190.56449664</v>
+        <v>184.78856361</v>
       </c>
       <c r="Q34">
-        <v>429.76449664</v>
+        <v>423.98856361</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09475245420495132</v>
+        <v>0.09531821034587501</v>
       </c>
       <c r="T34">
-        <v>1.130541667550839</v>
+        <v>1.143607629234989</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.091295978672337</v>
+        <v>3.74079837962942</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07802350093173625</v>
+        <v>0.07788413300410561</v>
       </c>
       <c r="C35">
-        <v>3182.748046998006</v>
+        <v>3150.382694664956</v>
       </c>
       <c r="D35">
-        <v>4012.877046998005</v>
+        <v>4028.124694664956</v>
       </c>
       <c r="E35">
-        <v>215.4290000000001</v>
+        <v>263.0420000000001</v>
       </c>
       <c r="F35">
-        <v>1571.229</v>
+        <v>1618.842</v>
       </c>
       <c r="G35">
         <v>741.1</v>
@@ -4157,28 +4157,28 @@
         <v>360.3</v>
       </c>
       <c r="M35">
-        <v>96.31633770000001</v>
+        <v>99.2350146</v>
       </c>
       <c r="N35">
-        <v>263.9836623</v>
+        <v>261.0649854</v>
       </c>
       <c r="O35">
-        <v>79.19509868999999</v>
+        <v>78.31949562</v>
       </c>
       <c r="P35">
-        <v>184.78856361</v>
+        <v>182.74548978</v>
       </c>
       <c r="Q35">
-        <v>423.98856361</v>
+        <v>421.94548978</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09531821034587501</v>
+        <v>0.09590111061228124</v>
       </c>
       <c r="T35">
-        <v>1.143607629234989</v>
+        <v>1.157069529151991</v>
       </c>
       <c r="U35">
         <v>0.06130000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.74079837962942</v>
+        <v>3.630774897875614</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07788413300410561</v>
+        <v>0.07774476507647497</v>
       </c>
       <c r="C36">
-        <v>3150.382694664956</v>
+        <v>3118.133656645291</v>
       </c>
       <c r="D36">
-        <v>4028.124694664956</v>
+        <v>4043.488656645291</v>
       </c>
       <c r="E36">
-        <v>263.0420000000001</v>
+        <v>310.6550000000002</v>
       </c>
       <c r="F36">
-        <v>1618.842</v>
+        <v>1666.455</v>
       </c>
       <c r="G36">
         <v>741.1</v>
@@ -4239,28 +4239,28 @@
         <v>360.3</v>
       </c>
       <c r="M36">
-        <v>99.2350146</v>
+        <v>102.1536915</v>
       </c>
       <c r="N36">
-        <v>261.0649854</v>
+        <v>258.1463085</v>
       </c>
       <c r="O36">
-        <v>78.31949562</v>
+        <v>77.44389255</v>
       </c>
       <c r="P36">
-        <v>182.74548978</v>
+        <v>180.70241595</v>
       </c>
       <c r="Q36">
-        <v>421.94548978</v>
+        <v>419.90241595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09590111061228124</v>
+        <v>0.09650194627149997</v>
       </c>
       <c r="T36">
-        <v>1.157069529151991</v>
+        <v>1.170945641374133</v>
       </c>
       <c r="U36">
         <v>0.06130000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.630774897875614</v>
+        <v>3.527038472222025</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07774476507647497</v>
+        <v>0.07831099714884432</v>
       </c>
       <c r="C37">
-        <v>3118.133656645291</v>
+        <v>3008.817161612375</v>
       </c>
       <c r="D37">
-        <v>4043.488656645291</v>
+        <v>3981.785161612375</v>
       </c>
       <c r="E37">
-        <v>310.6550000000002</v>
+        <v>358.2680000000003</v>
       </c>
       <c r="F37">
-        <v>1666.455</v>
+        <v>1714.068</v>
       </c>
       <c r="G37">
         <v>741.1</v>
@@ -4321,45 +4321,45 @@
         <v>360.3</v>
       </c>
       <c r="M37">
-        <v>102.1536915</v>
+        <v>109.8717588</v>
       </c>
       <c r="N37">
-        <v>258.1463085</v>
+        <v>250.4282412</v>
       </c>
       <c r="O37">
-        <v>77.44389255</v>
+        <v>75.12847236</v>
       </c>
       <c r="P37">
-        <v>180.70241595</v>
+        <v>175.29976884</v>
       </c>
       <c r="Q37">
-        <v>419.90241595</v>
+        <v>414.49976884</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09650194627149997</v>
+        <v>0.09712155804506926</v>
       </c>
       <c r="T37">
-        <v>1.170945641374133</v>
+        <v>1.185255382103216</v>
       </c>
       <c r="U37">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.527038472222025</v>
+        <v>3.279277622704261</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07831099714884433</v>
+        <v>0.07819122922121369</v>
       </c>
       <c r="C38">
-        <v>3008.817161612374</v>
+        <v>2974.097978232277</v>
       </c>
       <c r="D38">
-        <v>3981.785161612373</v>
+        <v>3994.678978232276</v>
       </c>
       <c r="E38">
-        <v>358.268</v>
+        <v>405.8810000000001</v>
       </c>
       <c r="F38">
-        <v>1714.068</v>
+        <v>1761.681</v>
       </c>
       <c r="G38">
         <v>741.1</v>
@@ -4403,28 +4403,28 @@
         <v>360.3</v>
       </c>
       <c r="M38">
-        <v>109.8717588</v>
+        <v>112.9237521</v>
       </c>
       <c r="N38">
-        <v>250.4282412</v>
+        <v>247.3762479</v>
       </c>
       <c r="O38">
-        <v>75.12847236</v>
+        <v>74.21287436999999</v>
       </c>
       <c r="P38">
-        <v>175.29976884</v>
+        <v>173.16337353</v>
       </c>
       <c r="Q38">
-        <v>414.49976884</v>
+        <v>412.36337353</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09712155804506926</v>
+        <v>0.09776084003367251</v>
       </c>
       <c r="T38">
-        <v>1.185255382103216</v>
+        <v>1.200019400315762</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.279277622704261</v>
+        <v>3.190648497766309</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07819122922121369</v>
+        <v>0.07807146129358304</v>
       </c>
       <c r="C39">
-        <v>2974.097978232277</v>
+        <v>2939.46257165158</v>
       </c>
       <c r="D39">
-        <v>3994.678978232276</v>
+        <v>4007.65657165158</v>
       </c>
       <c r="E39">
-        <v>405.8810000000001</v>
+        <v>453.4939999999999</v>
       </c>
       <c r="F39">
-        <v>1761.681</v>
+        <v>1809.294</v>
       </c>
       <c r="G39">
         <v>741.1</v>
@@ -4485,28 +4485,28 @@
         <v>360.3</v>
       </c>
       <c r="M39">
-        <v>112.9237521</v>
+        <v>115.9757454</v>
       </c>
       <c r="N39">
-        <v>247.3762479</v>
+        <v>244.3242546</v>
       </c>
       <c r="O39">
-        <v>74.21287436999999</v>
+        <v>73.29727638</v>
       </c>
       <c r="P39">
-        <v>173.16337353</v>
+        <v>171.02697822</v>
       </c>
       <c r="Q39">
-        <v>412.36337353</v>
+        <v>410.22697822</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09776084003367251</v>
+        <v>0.09842074402190813</v>
       </c>
       <c r="T39">
-        <v>1.200019400315762</v>
+        <v>1.215259677180326</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.190648497766309</v>
+        <v>3.106684063614564</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07807146129358304</v>
+        <v>0.0779516933659524</v>
       </c>
       <c r="C40">
-        <v>2939.46257165158</v>
+        <v>2904.911761033605</v>
       </c>
       <c r="D40">
-        <v>4007.65657165158</v>
+        <v>4020.718761033605</v>
       </c>
       <c r="E40">
-        <v>453.4939999999999</v>
+        <v>501.107</v>
       </c>
       <c r="F40">
-        <v>1809.294</v>
+        <v>1856.907</v>
       </c>
       <c r="G40">
         <v>741.1</v>
@@ -4567,28 +4567,28 @@
         <v>360.3</v>
       </c>
       <c r="M40">
-        <v>115.9757454</v>
+        <v>119.0277387</v>
       </c>
       <c r="N40">
-        <v>244.3242546</v>
+        <v>241.2722613</v>
       </c>
       <c r="O40">
-        <v>73.29727638</v>
+        <v>72.38167839</v>
       </c>
       <c r="P40">
-        <v>171.02697822</v>
+        <v>168.89058291</v>
       </c>
       <c r="Q40">
-        <v>410.22697822</v>
+        <v>408.09058291</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09842074402190813</v>
+        <v>0.09910228420647935</v>
       </c>
       <c r="T40">
-        <v>1.215259677180326</v>
+        <v>1.230999635253565</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.106684063614564</v>
+        <v>3.027025497880857</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0779516933659524</v>
+        <v>0.08001592543832176</v>
       </c>
       <c r="C41">
-        <v>2904.911761033605</v>
+        <v>2643.447775117453</v>
       </c>
       <c r="D41">
-        <v>4020.718761033605</v>
+        <v>3806.867775117452</v>
       </c>
       <c r="E41">
-        <v>501.107</v>
+        <v>548.72</v>
       </c>
       <c r="F41">
-        <v>1856.907</v>
+        <v>1904.52</v>
       </c>
       <c r="G41">
         <v>741.1</v>
@@ -4649,45 +4649,45 @@
         <v>360.3</v>
       </c>
       <c r="M41">
-        <v>119.0277387</v>
+        <v>136.934988</v>
       </c>
       <c r="N41">
-        <v>241.2722613</v>
+        <v>223.365012</v>
       </c>
       <c r="O41">
-        <v>72.38167839</v>
+        <v>67.0095036</v>
       </c>
       <c r="P41">
-        <v>168.89058291</v>
+        <v>156.3555084</v>
       </c>
       <c r="Q41">
-        <v>408.09058291</v>
+        <v>395.5555084</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09910228420647935</v>
+        <v>0.09980654239720294</v>
       </c>
       <c r="T41">
-        <v>1.230999635253565</v>
+        <v>1.247264258595911</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.027025497880857</v>
+        <v>2.631175605755338</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08001592543832176</v>
+        <v>0.07995075751069111</v>
       </c>
       <c r="C42">
-        <v>2643.447775117453</v>
+        <v>2602.237732180586</v>
       </c>
       <c r="D42">
-        <v>3806.867775117452</v>
+        <v>3813.270732180586</v>
       </c>
       <c r="E42">
-        <v>548.72</v>
+        <v>596.3330000000001</v>
       </c>
       <c r="F42">
-        <v>1904.52</v>
+        <v>1952.133</v>
       </c>
       <c r="G42">
         <v>741.1</v>
@@ -4731,28 +4731,28 @@
         <v>360.3</v>
       </c>
       <c r="M42">
-        <v>136.934988</v>
+        <v>140.3583627</v>
       </c>
       <c r="N42">
-        <v>223.365012</v>
+        <v>219.9416373</v>
       </c>
       <c r="O42">
-        <v>67.0095036</v>
+        <v>65.98249119</v>
       </c>
       <c r="P42">
-        <v>156.3555084</v>
+        <v>153.95914611</v>
       </c>
       <c r="Q42">
-        <v>395.5555084</v>
+        <v>393.15914611</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09980654239720294</v>
+        <v>0.1005346737469341</v>
       </c>
       <c r="T42">
-        <v>1.247264258595911</v>
+        <v>1.264080225102404</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.631175605755338</v>
+        <v>2.567000590980818</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07995075751069111</v>
+        <v>0.07988558958306047</v>
       </c>
       <c r="C43">
-        <v>2602.237732180586</v>
+        <v>2561.049264425239</v>
       </c>
       <c r="D43">
-        <v>3813.270732180586</v>
+        <v>3819.695264425239</v>
       </c>
       <c r="E43">
-        <v>596.3330000000001</v>
+        <v>643.9460000000001</v>
       </c>
       <c r="F43">
-        <v>1952.133</v>
+        <v>1999.746</v>
       </c>
       <c r="G43">
         <v>741.1</v>
@@ -4813,28 +4813,28 @@
         <v>360.3</v>
       </c>
       <c r="M43">
-        <v>140.3583627</v>
+        <v>143.7817374</v>
       </c>
       <c r="N43">
-        <v>219.9416373</v>
+        <v>216.5182626</v>
       </c>
       <c r="O43">
-        <v>65.98249119</v>
+        <v>64.95547878000001</v>
       </c>
       <c r="P43">
-        <v>153.95914611</v>
+        <v>151.56278382</v>
       </c>
       <c r="Q43">
-        <v>393.15914611</v>
+        <v>390.76278382</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1005346737469341</v>
+        <v>0.1012879130742422</v>
       </c>
       <c r="T43">
-        <v>1.264080225102404</v>
+        <v>1.281476052522915</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.567000590980818</v>
+        <v>2.505881529290798</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07988558958306047</v>
+        <v>0.08099432165542984</v>
       </c>
       <c r="C44">
-        <v>2561.049264425239</v>
+        <v>2406.999477822945</v>
       </c>
       <c r="D44">
-        <v>3819.695264425239</v>
+        <v>3713.258477822944</v>
       </c>
       <c r="E44">
-        <v>643.9459999999999</v>
+        <v>691.559</v>
       </c>
       <c r="F44">
-        <v>1999.746</v>
+        <v>2047.359</v>
       </c>
       <c r="G44">
         <v>741.1</v>
@@ -4895,45 +4895,45 @@
         <v>360.3</v>
       </c>
       <c r="M44">
-        <v>143.7817374</v>
+        <v>155.1898122</v>
       </c>
       <c r="N44">
-        <v>216.5182626</v>
+        <v>205.1101878</v>
       </c>
       <c r="O44">
-        <v>64.95547878000001</v>
+        <v>61.53305634000001</v>
       </c>
       <c r="P44">
-        <v>151.56278382</v>
+        <v>143.57713146</v>
       </c>
       <c r="Q44">
-        <v>390.76278382</v>
+        <v>382.77713146</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1012879130742422</v>
+        <v>0.1020675818516313</v>
       </c>
       <c r="T44">
-        <v>1.281476052522914</v>
+        <v>1.299482259852917</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.505881529290798</v>
+        <v>2.321673020234508</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08099432165542984</v>
+        <v>0.08095645372779919</v>
       </c>
       <c r="C45">
-        <v>2406.999477822945</v>
+        <v>2362.923816720491</v>
       </c>
       <c r="D45">
-        <v>3713.258477822944</v>
+        <v>3716.795816720491</v>
       </c>
       <c r="E45">
-        <v>691.559</v>
+        <v>739.172</v>
       </c>
       <c r="F45">
-        <v>2047.359</v>
+        <v>2094.972</v>
       </c>
       <c r="G45">
         <v>741.1</v>
@@ -4977,28 +4977,28 @@
         <v>360.3</v>
       </c>
       <c r="M45">
-        <v>155.1898122</v>
+        <v>158.7988776</v>
       </c>
       <c r="N45">
-        <v>205.1101878</v>
+        <v>201.5011224</v>
       </c>
       <c r="O45">
-        <v>61.53305634000001</v>
+        <v>60.45033672</v>
       </c>
       <c r="P45">
-        <v>143.57713146</v>
+        <v>141.05078568</v>
       </c>
       <c r="Q45">
-        <v>382.77713146</v>
+        <v>380.25078568</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1020675818516313</v>
+        <v>0.1028750959424986</v>
       </c>
       <c r="T45">
-        <v>1.299482259852917</v>
+        <v>1.318131546016133</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.321673020234508</v>
+        <v>2.268907724320087</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08095645372779919</v>
+        <v>0.08091858580016856</v>
       </c>
       <c r="C46">
-        <v>2362.923816720491</v>
+        <v>2318.854901551765</v>
       </c>
       <c r="D46">
-        <v>3716.795816720491</v>
+        <v>3720.339901551764</v>
       </c>
       <c r="E46">
-        <v>739.172</v>
+        <v>786.7849999999999</v>
       </c>
       <c r="F46">
-        <v>2094.972</v>
+        <v>2142.585</v>
       </c>
       <c r="G46">
         <v>741.1</v>
@@ -5059,28 +5059,28 @@
         <v>360.3</v>
       </c>
       <c r="M46">
-        <v>158.7988776</v>
+        <v>162.407943</v>
       </c>
       <c r="N46">
-        <v>201.5011224</v>
+        <v>197.892057</v>
       </c>
       <c r="O46">
-        <v>60.45033672</v>
+        <v>59.3676171</v>
       </c>
       <c r="P46">
-        <v>141.05078568</v>
+        <v>138.5244399</v>
       </c>
       <c r="Q46">
-        <v>380.25078568</v>
+        <v>377.7244399</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1028750959424986</v>
+        <v>0.1037119741821246</v>
       </c>
       <c r="T46">
-        <v>1.318131546016133</v>
+        <v>1.33745898803983</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.268907724320087</v>
+        <v>2.218487552668529</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08091858580016856</v>
+        <v>0.08088071787253791</v>
       </c>
       <c r="C47">
-        <v>2318.854901551765</v>
+        <v>2274.792751632582</v>
       </c>
       <c r="D47">
-        <v>3720.339901551764</v>
+        <v>3723.890751632582</v>
       </c>
       <c r="E47">
-        <v>786.7849999999999</v>
+        <v>834.3980000000001</v>
       </c>
       <c r="F47">
-        <v>2142.585</v>
+        <v>2190.198</v>
       </c>
       <c r="G47">
         <v>741.1</v>
@@ -5141,28 +5141,28 @@
         <v>360.3</v>
       </c>
       <c r="M47">
-        <v>162.407943</v>
+        <v>166.0170084</v>
       </c>
       <c r="N47">
-        <v>197.892057</v>
+        <v>194.2829916</v>
       </c>
       <c r="O47">
-        <v>59.3676171</v>
+        <v>58.28489748</v>
       </c>
       <c r="P47">
-        <v>138.5244399</v>
+        <v>135.99809412</v>
       </c>
       <c r="Q47">
-        <v>377.7244399</v>
+        <v>375.19809412</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1037119741821246</v>
+        <v>0.1045798479121072</v>
       </c>
       <c r="T47">
-        <v>1.33745898803983</v>
+        <v>1.35750226124959</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.218487552668529</v>
+        <v>2.170259562393126</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08088071787253791</v>
+        <v>0.08084284994490727</v>
       </c>
       <c r="C48">
-        <v>2274.792751632582</v>
+        <v>2230.737386352571</v>
       </c>
       <c r="D48">
-        <v>3723.890751632582</v>
+        <v>3727.448386352571</v>
       </c>
       <c r="E48">
-        <v>834.3980000000001</v>
+        <v>882.011</v>
       </c>
       <c r="F48">
-        <v>2190.198</v>
+        <v>2237.811</v>
       </c>
       <c r="G48">
         <v>741.1</v>
@@ -5223,28 +5223,28 @@
         <v>360.3</v>
       </c>
       <c r="M48">
-        <v>166.0170084</v>
+        <v>169.6260738</v>
       </c>
       <c r="N48">
-        <v>194.2829916</v>
+        <v>190.6739262</v>
       </c>
       <c r="O48">
-        <v>58.28489748</v>
+        <v>57.20217786</v>
       </c>
       <c r="P48">
-        <v>135.99809412</v>
+        <v>133.47174834</v>
       </c>
       <c r="Q48">
-        <v>375.19809412</v>
+        <v>372.67174834</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1045798479121072</v>
+        <v>0.1054804715941647</v>
       </c>
       <c r="T48">
-        <v>1.35750226124959</v>
+        <v>1.378301884391793</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.170259562393126</v>
+        <v>2.12408382702306</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08084284994490727</v>
+        <v>0.08080498201727662</v>
       </c>
       <c r="C49">
-        <v>2230.737386352571</v>
+        <v>2186.688825175529</v>
       </c>
       <c r="D49">
-        <v>3727.448386352571</v>
+        <v>3731.012825175529</v>
       </c>
       <c r="E49">
-        <v>882.011</v>
+        <v>929.6240000000003</v>
       </c>
       <c r="F49">
-        <v>2237.811</v>
+        <v>2285.424</v>
       </c>
       <c r="G49">
         <v>741.1</v>
@@ -5305,28 +5305,28 @@
         <v>360.3</v>
       </c>
       <c r="M49">
-        <v>169.6260738</v>
+        <v>173.2351392</v>
       </c>
       <c r="N49">
-        <v>190.6739262</v>
+        <v>187.0648608</v>
       </c>
       <c r="O49">
-        <v>57.20217786</v>
+        <v>56.11945823999999</v>
       </c>
       <c r="P49">
-        <v>133.47174834</v>
+        <v>130.94540256</v>
       </c>
       <c r="Q49">
-        <v>372.67174834</v>
+        <v>370.14540256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1054804715941647</v>
+        <v>0.1064157346486089</v>
       </c>
       <c r="T49">
-        <v>1.378301884391793</v>
+        <v>1.399901493039466</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.12408382702306</v>
+        <v>2.079832080626746</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08080498201727662</v>
+        <v>0.08076711408964599</v>
       </c>
       <c r="C50">
-        <v>2186.688825175529</v>
+        <v>2142.64708763977</v>
       </c>
       <c r="D50">
-        <v>3731.012825175529</v>
+        <v>3734.58408763977</v>
       </c>
       <c r="E50">
-        <v>929.6239999999998</v>
+        <v>977.2370000000001</v>
       </c>
       <c r="F50">
-        <v>2285.424</v>
+        <v>2333.037</v>
       </c>
       <c r="G50">
         <v>741.1</v>
@@ -5387,28 +5387,28 @@
         <v>360.3</v>
       </c>
       <c r="M50">
-        <v>173.2351392</v>
+        <v>176.8442046</v>
       </c>
       <c r="N50">
-        <v>187.0648608</v>
+        <v>183.4557954</v>
       </c>
       <c r="O50">
-        <v>56.11945824000001</v>
+        <v>55.03673862</v>
       </c>
       <c r="P50">
-        <v>130.94540256</v>
+        <v>128.41905678</v>
       </c>
       <c r="Q50">
-        <v>370.14540256</v>
+        <v>367.61905678</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1064157346486089</v>
+        <v>0.1073876746855803</v>
       </c>
       <c r="T50">
-        <v>1.399901493039466</v>
+        <v>1.422348145163518</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.079832080626746</v>
+        <v>2.037386527960894</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08076711408964599</v>
+        <v>0.08569924616201534</v>
       </c>
       <c r="C51">
-        <v>2142.64708763977</v>
+        <v>1681.057541988464</v>
       </c>
       <c r="D51">
-        <v>3734.58408763977</v>
+        <v>3320.607541988464</v>
       </c>
       <c r="E51">
-        <v>977.2370000000001</v>
+        <v>1024.85</v>
       </c>
       <c r="F51">
-        <v>2333.037</v>
+        <v>2380.65</v>
       </c>
       <c r="G51">
         <v>741.1</v>
@@ -5469,45 +5469,45 @@
         <v>360.3</v>
       </c>
       <c r="M51">
-        <v>176.8442046</v>
+        <v>214.2585</v>
       </c>
       <c r="N51">
-        <v>183.4557954</v>
+        <v>146.0415</v>
       </c>
       <c r="O51">
-        <v>55.03673862</v>
+        <v>43.81245000000001</v>
       </c>
       <c r="P51">
-        <v>128.41905678</v>
+        <v>102.22905</v>
       </c>
       <c r="Q51">
-        <v>367.61905678</v>
+        <v>341.42905</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1073876746855803</v>
+        <v>0.1083984923240307</v>
       </c>
       <c r="T51">
-        <v>1.422348145163518</v>
+        <v>1.445692663372533</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.037386527960894</v>
+        <v>1.681613564922745</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08569924616201534</v>
+        <v>0.0857607782343847</v>
       </c>
       <c r="C52">
-        <v>1681.057541988464</v>
+        <v>1628.858714594554</v>
       </c>
       <c r="D52">
-        <v>3320.607541988464</v>
+        <v>3316.021714594553</v>
       </c>
       <c r="E52">
-        <v>1024.85</v>
+        <v>1072.463</v>
       </c>
       <c r="F52">
-        <v>2380.65</v>
+        <v>2428.262999999999</v>
       </c>
       <c r="G52">
         <v>741.1</v>
@@ -5551,28 +5551,28 @@
         <v>360.3</v>
       </c>
       <c r="M52">
-        <v>214.2585</v>
+        <v>218.54367</v>
       </c>
       <c r="N52">
-        <v>146.0415</v>
+        <v>141.75633</v>
       </c>
       <c r="O52">
-        <v>43.81245000000001</v>
+        <v>42.52689900000001</v>
       </c>
       <c r="P52">
-        <v>102.22905</v>
+        <v>99.22943100000001</v>
       </c>
       <c r="Q52">
-        <v>341.42905</v>
+        <v>338.429431</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1083984923240307</v>
+        <v>0.1094505678252749</v>
       </c>
       <c r="T52">
-        <v>1.445692663372533</v>
+        <v>1.469990019059466</v>
       </c>
       <c r="U52">
         <v>0.09000000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.681613564922745</v>
+        <v>1.64864074992426</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0857607782343847</v>
+        <v>0.08582231030675405</v>
       </c>
       <c r="C53">
-        <v>1628.858714594554</v>
+        <v>1576.672535976551</v>
       </c>
       <c r="D53">
-        <v>3316.021714594553</v>
+        <v>3311.44853597655</v>
       </c>
       <c r="E53">
-        <v>1072.463</v>
+        <v>1120.076</v>
       </c>
       <c r="F53">
-        <v>2428.262999999999</v>
+        <v>2475.876</v>
       </c>
       <c r="G53">
         <v>741.1</v>
@@ -5633,28 +5633,28 @@
         <v>360.3</v>
       </c>
       <c r="M53">
-        <v>218.54367</v>
+        <v>222.82884</v>
       </c>
       <c r="N53">
-        <v>141.75633</v>
+        <v>137.47116</v>
       </c>
       <c r="O53">
-        <v>42.52689900000001</v>
+        <v>41.241348</v>
       </c>
       <c r="P53">
-        <v>99.22943100000001</v>
+        <v>96.22981200000001</v>
       </c>
       <c r="Q53">
-        <v>338.429431</v>
+        <v>335.429812</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1094505678252749</v>
+        <v>0.1105464798057376</v>
       </c>
       <c r="T53">
-        <v>1.469990019059466</v>
+        <v>1.495299764566688</v>
       </c>
       <c r="U53">
         <v>0.09000000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.64864074992426</v>
+        <v>1.616936120118024</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08582231030675405</v>
+        <v>0.0858838423791234</v>
       </c>
       <c r="C54">
-        <v>1576.672535976551</v>
+        <v>1524.498953874139</v>
       </c>
       <c r="D54">
-        <v>3311.44853597655</v>
+        <v>3306.887953874138</v>
       </c>
       <c r="E54">
-        <v>1120.076</v>
+        <v>1167.689</v>
       </c>
       <c r="F54">
-        <v>2475.876</v>
+        <v>2523.489</v>
       </c>
       <c r="G54">
         <v>741.1</v>
@@ -5715,28 +5715,28 @@
         <v>360.3</v>
       </c>
       <c r="M54">
-        <v>222.82884</v>
+        <v>227.11401</v>
       </c>
       <c r="N54">
-        <v>137.47116</v>
+        <v>133.18599</v>
       </c>
       <c r="O54">
-        <v>41.241348</v>
+        <v>39.95579700000001</v>
       </c>
       <c r="P54">
-        <v>96.22981200000001</v>
+        <v>93.23019300000001</v>
       </c>
       <c r="Q54">
-        <v>335.429812</v>
+        <v>332.430193</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1105464798057376</v>
+        <v>0.1116890263385604</v>
       </c>
       <c r="T54">
-        <v>1.495299764566688</v>
+        <v>1.521686520521026</v>
       </c>
       <c r="U54">
         <v>0.09000000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.616936120118024</v>
+        <v>1.586427891436552</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0858838423791234</v>
+        <v>0.08594537445149275</v>
       </c>
       <c r="C55">
-        <v>1524.498953874139</v>
+        <v>1472.337916314502</v>
       </c>
       <c r="D55">
-        <v>3306.887953874138</v>
+        <v>3302.339916314502</v>
       </c>
       <c r="E55">
-        <v>1167.689</v>
+        <v>1215.302</v>
       </c>
       <c r="F55">
-        <v>2523.489</v>
+        <v>2571.102</v>
       </c>
       <c r="G55">
         <v>741.1</v>
@@ -5797,28 +5797,28 @@
         <v>360.3</v>
       </c>
       <c r="M55">
-        <v>227.11401</v>
+        <v>231.39918</v>
       </c>
       <c r="N55">
-        <v>133.18599</v>
+        <v>128.90082</v>
       </c>
       <c r="O55">
-        <v>39.95579700000001</v>
+        <v>38.670246</v>
       </c>
       <c r="P55">
-        <v>93.23019300000001</v>
+        <v>90.23057400000002</v>
       </c>
       <c r="Q55">
-        <v>332.430193</v>
+        <v>329.430574</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1116890263385604</v>
+        <v>0.112881248807593</v>
       </c>
       <c r="T55">
-        <v>1.521686520521026</v>
+        <v>1.549220526734249</v>
       </c>
       <c r="U55">
         <v>0.09000000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.586427891436552</v>
+        <v>1.55704959715069</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08594537445149275</v>
+        <v>0.08600690652386211</v>
       </c>
       <c r="C56">
-        <v>1472.337916314502</v>
+        <v>1420.18937161035</v>
       </c>
       <c r="D56">
-        <v>3302.339916314502</v>
+        <v>3297.804371610349</v>
       </c>
       <c r="E56">
-        <v>1215.302</v>
+        <v>1262.915</v>
       </c>
       <c r="F56">
-        <v>2571.102</v>
+        <v>2618.715</v>
       </c>
       <c r="G56">
         <v>741.1</v>
@@ -5879,28 +5879,28 @@
         <v>360.3</v>
       </c>
       <c r="M56">
-        <v>231.39918</v>
+        <v>235.68435</v>
       </c>
       <c r="N56">
-        <v>128.90082</v>
+        <v>124.61565</v>
       </c>
       <c r="O56">
-        <v>38.670246</v>
+        <v>37.384695</v>
       </c>
       <c r="P56">
-        <v>90.23057400000002</v>
+        <v>87.23095500000002</v>
       </c>
       <c r="Q56">
-        <v>329.430574</v>
+        <v>326.430955</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.112881248807593</v>
+        <v>0.1141264589419158</v>
       </c>
       <c r="T56">
-        <v>1.549220526734249</v>
+        <v>1.577978266556948</v>
       </c>
       <c r="U56">
         <v>0.09000000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.55704959715069</v>
+        <v>1.528739604475223</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08600690652386211</v>
+        <v>0.08606843859623148</v>
       </c>
       <c r="C57">
-        <v>1420.18937161035</v>
+        <v>1368.053268357957</v>
       </c>
       <c r="D57">
-        <v>3297.804371610349</v>
+        <v>3293.281268357957</v>
       </c>
       <c r="E57">
-        <v>1262.915</v>
+        <v>1310.528</v>
       </c>
       <c r="F57">
-        <v>2618.715</v>
+        <v>2666.328</v>
       </c>
       <c r="G57">
         <v>741.1</v>
@@ -5961,28 +5961,28 @@
         <v>360.3</v>
       </c>
       <c r="M57">
-        <v>235.68435</v>
+        <v>239.96952</v>
       </c>
       <c r="N57">
-        <v>124.61565</v>
+        <v>120.33048</v>
       </c>
       <c r="O57">
-        <v>37.384695</v>
+        <v>36.099144</v>
       </c>
       <c r="P57">
-        <v>87.23095500000002</v>
+        <v>84.231336</v>
       </c>
       <c r="Q57">
-        <v>326.430955</v>
+        <v>323.431336</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1141264589419158</v>
+        <v>0.1154282695368897</v>
       </c>
       <c r="T57">
-        <v>1.577978266556948</v>
+        <v>1.608043176371587</v>
       </c>
       <c r="U57">
         <v>0.09000000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.528739604475223</v>
+        <v>1.501440682966737</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08606843859623148</v>
+        <v>0.1117964476652739</v>
       </c>
       <c r="C58">
-        <v>1368.053268357957</v>
+        <v>120.1546961932399</v>
       </c>
       <c r="D58">
-        <v>3293.281268357957</v>
+        <v>2092.99569619324</v>
       </c>
       <c r="E58">
-        <v>1310.528</v>
+        <v>1358.141</v>
       </c>
       <c r="F58">
-        <v>2666.328</v>
+        <v>2713.941</v>
       </c>
       <c r="G58">
         <v>741.1</v>
@@ -6043,45 +6043,45 @@
         <v>360.3</v>
       </c>
       <c r="M58">
-        <v>239.96952</v>
+        <v>398.4065388</v>
       </c>
       <c r="N58">
-        <v>120.33048</v>
+        <v>-38.10653880000001</v>
       </c>
       <c r="O58">
-        <v>36.099144</v>
+        <v>-11.43196164</v>
       </c>
       <c r="P58">
-        <v>84.231336</v>
+        <v>-26.67457716000001</v>
       </c>
       <c r="Q58">
-        <v>323.431336</v>
+        <v>212.52542284</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1154282695368897</v>
+        <v>0.1181912343993743</v>
       </c>
       <c r="T58">
-        <v>1.608043176371587</v>
+        <v>1.671852988438205</v>
       </c>
       <c r="U58">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.3</v>
+        <v>0.2713057881167487</v>
       </c>
       <c r="W58">
-        <v>0.063</v>
+        <v>0.1069723103044613</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.501440682966737</v>
+        <v>0.9043526270558289</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1117964476652739</v>
+        <v>0.1128064476652739</v>
       </c>
       <c r="C59">
-        <v>120.1546961932399</v>
+        <v>43.01807989600638</v>
       </c>
       <c r="D59">
-        <v>2092.99569619324</v>
+        <v>2063.472079896007</v>
       </c>
       <c r="E59">
-        <v>1358.141</v>
+        <v>1405.754</v>
       </c>
       <c r="F59">
-        <v>2713.941</v>
+        <v>2761.554</v>
       </c>
       <c r="G59">
         <v>741.1</v>
@@ -6125,37 +6125,37 @@
         <v>360.3</v>
       </c>
       <c r="M59">
-        <v>398.4065388</v>
+        <v>405.3961272</v>
       </c>
       <c r="N59">
-        <v>-38.10653880000001</v>
+        <v>-45.09612720000001</v>
       </c>
       <c r="O59">
-        <v>-11.43196164</v>
+        <v>-13.52883816</v>
       </c>
       <c r="P59">
-        <v>-26.67457716000001</v>
+        <v>-31.56728904000001</v>
       </c>
       <c r="Q59">
-        <v>212.52542284</v>
+        <v>207.63271096</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1181912343993743</v>
+        <v>0.119914835218407</v>
       </c>
       <c r="T59">
-        <v>1.671852988438205</v>
+        <v>1.711659011972448</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2713057881167487</v>
+        <v>0.2666281021147357</v>
       </c>
       <c r="W59">
-        <v>0.1069723103044613</v>
+        <v>0.1076589946095568</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9043526270558289</v>
+        <v>0.8887603403824524</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1128064476652739</v>
+        <v>0.1138164476652739</v>
       </c>
       <c r="C60">
-        <v>43.0180798960082</v>
+        <v>-33.29720684804988</v>
       </c>
       <c r="D60">
-        <v>2063.472079896007</v>
+        <v>2034.769793151949</v>
       </c>
       <c r="E60">
-        <v>1405.753999999999</v>
+        <v>1453.367</v>
       </c>
       <c r="F60">
-        <v>2761.553999999999</v>
+        <v>2809.166999999999</v>
       </c>
       <c r="G60">
         <v>741.1</v>
@@ -6207,37 +6207,37 @@
         <v>360.3</v>
       </c>
       <c r="M60">
-        <v>405.3961271999999</v>
+        <v>412.3857156</v>
       </c>
       <c r="N60">
-        <v>-45.0961271999999</v>
+        <v>-52.08571559999996</v>
       </c>
       <c r="O60">
-        <v>-13.52883815999997</v>
+        <v>-15.62571467999999</v>
       </c>
       <c r="P60">
-        <v>-31.56728903999993</v>
+        <v>-36.46000091999997</v>
       </c>
       <c r="Q60">
-        <v>207.6327109600001</v>
+        <v>202.73999908</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.119914835218407</v>
+        <v>0.121722514126173</v>
       </c>
       <c r="T60">
-        <v>1.711659011972448</v>
+        <v>1.753406792752263</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2666281021147358</v>
+        <v>0.2621089817399097</v>
       </c>
       <c r="W60">
-        <v>0.1076589946095568</v>
+        <v>0.1083224014805813</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8887603403824527</v>
+        <v>0.8736966057996991</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1138164476652739</v>
+        <v>0.1148264476652739</v>
       </c>
       <c r="C61">
-        <v>-33.29720684804988</v>
+        <v>-108.8249672009288</v>
       </c>
       <c r="D61">
-        <v>2034.769793151949</v>
+        <v>2006.855032799071</v>
       </c>
       <c r="E61">
-        <v>1453.367</v>
+        <v>1500.98</v>
       </c>
       <c r="F61">
-        <v>2809.166999999999</v>
+        <v>2856.779999999999</v>
       </c>
       <c r="G61">
         <v>741.1</v>
@@ -6289,37 +6289,37 @@
         <v>360.3</v>
       </c>
       <c r="M61">
-        <v>412.3857156</v>
+        <v>419.3753039999999</v>
       </c>
       <c r="N61">
-        <v>-52.08571559999996</v>
+        <v>-59.0753039999999</v>
       </c>
       <c r="O61">
-        <v>-15.62571467999999</v>
+        <v>-17.72259119999997</v>
       </c>
       <c r="P61">
-        <v>-36.46000091999997</v>
+        <v>-41.35271279999994</v>
       </c>
       <c r="Q61">
-        <v>202.73999908</v>
+        <v>197.8472872</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.121722514126173</v>
+        <v>0.1236205769793273</v>
       </c>
       <c r="T61">
-        <v>1.753406792752263</v>
+        <v>1.79724196257107</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2621089817399097</v>
+        <v>0.2577404987109113</v>
       </c>
       <c r="W61">
-        <v>0.1083224014805813</v>
+        <v>0.1089636947892382</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8736966057996991</v>
+        <v>0.8591349957030376</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1148264476652739</v>
+        <v>0.1158364476652739</v>
       </c>
       <c r="C62">
-        <v>-108.8249672009288</v>
+        <v>-183.5971744623439</v>
       </c>
       <c r="D62">
-        <v>2006.855032799071</v>
+        <v>1979.695825537656</v>
       </c>
       <c r="E62">
-        <v>1500.98</v>
+        <v>1548.593</v>
       </c>
       <c r="F62">
-        <v>2856.779999999999</v>
+        <v>2904.393</v>
       </c>
       <c r="G62">
         <v>741.1</v>
@@ -6371,37 +6371,37 @@
         <v>360.3</v>
       </c>
       <c r="M62">
-        <v>419.3753039999999</v>
+        <v>426.3648924</v>
       </c>
       <c r="N62">
-        <v>-59.0753039999999</v>
+        <v>-66.06489239999996</v>
       </c>
       <c r="O62">
-        <v>-17.72259119999997</v>
+        <v>-19.81946771999999</v>
       </c>
       <c r="P62">
-        <v>-41.35271279999994</v>
+        <v>-46.24542467999997</v>
       </c>
       <c r="Q62">
-        <v>197.8472872</v>
+        <v>192.95457532</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1236205769793273</v>
+        <v>0.1256159763890537</v>
       </c>
       <c r="T62">
-        <v>1.79724196257107</v>
+        <v>1.843325089816482</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2577404987109113</v>
+        <v>0.2535152446336832</v>
       </c>
       <c r="W62">
-        <v>0.1089636947892382</v>
+        <v>0.1095839620877753</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8591349957030376</v>
+        <v>0.8450508154456107</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1158364476652739</v>
+        <v>0.1168464476652739</v>
       </c>
       <c r="C63">
-        <v>-183.5971744623439</v>
+        <v>-257.6440942360496</v>
       </c>
       <c r="D63">
-        <v>1979.695825537656</v>
+        <v>1953.26190576395</v>
       </c>
       <c r="E63">
-        <v>1548.593</v>
+        <v>1596.206</v>
       </c>
       <c r="F63">
-        <v>2904.393</v>
+        <v>2952.005999999999</v>
       </c>
       <c r="G63">
         <v>741.1</v>
@@ -6453,37 +6453,37 @@
         <v>360.3</v>
       </c>
       <c r="M63">
-        <v>426.3648924</v>
+        <v>433.3544808</v>
       </c>
       <c r="N63">
-        <v>-66.06489239999996</v>
+        <v>-73.05448079999996</v>
       </c>
       <c r="O63">
-        <v>-19.81946771999999</v>
+        <v>-21.91634423999999</v>
       </c>
       <c r="P63">
-        <v>-46.24542467999997</v>
+        <v>-51.13813655999998</v>
       </c>
       <c r="Q63">
-        <v>192.95457532</v>
+        <v>188.06186344</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1256159763890537</v>
+        <v>0.1277163968203446</v>
       </c>
       <c r="T63">
-        <v>1.843325089816482</v>
+        <v>1.891833644811653</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2535152446336832</v>
+        <v>0.2494262890750754</v>
       </c>
       <c r="W63">
-        <v>0.1095839620877753</v>
+        <v>0.1101842207637789</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8450508154456107</v>
+        <v>0.8314209635835846</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1168464476652739</v>
+        <v>0.1178564476652739</v>
       </c>
       <c r="C64">
-        <v>-257.6440942360496</v>
+        <v>-330.9943969377682</v>
       </c>
       <c r="D64">
-        <v>1953.26190576395</v>
+        <v>1927.524603062231</v>
       </c>
       <c r="E64">
-        <v>1596.206</v>
+        <v>1643.819</v>
       </c>
       <c r="F64">
-        <v>2952.005999999999</v>
+        <v>2999.619</v>
       </c>
       <c r="G64">
         <v>741.1</v>
@@ -6535,37 +6535,37 @@
         <v>360.3</v>
       </c>
       <c r="M64">
-        <v>433.3544808</v>
+        <v>440.3440692</v>
       </c>
       <c r="N64">
-        <v>-73.05448079999996</v>
+        <v>-80.04406919999997</v>
       </c>
       <c r="O64">
-        <v>-21.91634423999999</v>
+        <v>-24.01322075999999</v>
       </c>
       <c r="P64">
-        <v>-51.13813655999998</v>
+        <v>-56.03084843999998</v>
       </c>
       <c r="Q64">
-        <v>188.06186344</v>
+        <v>183.16915156</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1277163968203446</v>
+        <v>0.1299303534911647</v>
       </c>
       <c r="T64">
-        <v>1.891833644811653</v>
+        <v>1.942964283860616</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2494262890750754</v>
+        <v>0.2454671416294393</v>
       </c>
       <c r="W64">
-        <v>0.1101842207637789</v>
+        <v>0.1107654236087983</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8314209635835846</v>
+        <v>0.8182238054314642</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1178564476652739</v>
+        <v>0.1188664476652739</v>
       </c>
       <c r="C65">
-        <v>-330.9943969377682</v>
+        <v>-403.6752615239725</v>
       </c>
       <c r="D65">
-        <v>1927.524603062231</v>
+        <v>1902.456738476027</v>
       </c>
       <c r="E65">
-        <v>1643.819</v>
+        <v>1691.432</v>
       </c>
       <c r="F65">
-        <v>2999.619</v>
+        <v>3047.232</v>
       </c>
       <c r="G65">
         <v>741.1</v>
@@ -6617,37 +6617,37 @@
         <v>360.3</v>
       </c>
       <c r="M65">
-        <v>440.3440692</v>
+        <v>447.3336576</v>
       </c>
       <c r="N65">
-        <v>-80.04406919999997</v>
+        <v>-87.03365759999997</v>
       </c>
       <c r="O65">
-        <v>-24.01322075999999</v>
+        <v>-26.11009727999999</v>
       </c>
       <c r="P65">
-        <v>-56.03084843999998</v>
+        <v>-60.92356031999998</v>
       </c>
       <c r="Q65">
-        <v>183.16915156</v>
+        <v>178.27643968</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1299303534911647</v>
+        <v>0.1322673077548081</v>
       </c>
       <c r="T65">
-        <v>1.942964283860616</v>
+        <v>1.996935513967856</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2454671416294393</v>
+        <v>0.2416317175414793</v>
       </c>
       <c r="W65">
-        <v>0.1107654236087983</v>
+        <v>0.1113284638649109</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8182238054314642</v>
+        <v>0.8054390584715976</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1188664476652739</v>
+        <v>0.1565078133754237</v>
       </c>
       <c r="C66">
-        <v>-403.6752615239725</v>
+        <v>-1072.359303340069</v>
       </c>
       <c r="D66">
-        <v>1902.456738476027</v>
+        <v>1281.385696659931</v>
       </c>
       <c r="E66">
-        <v>1691.432</v>
+        <v>1739.045</v>
       </c>
       <c r="F66">
-        <v>3047.232</v>
+        <v>3094.845</v>
       </c>
       <c r="G66">
         <v>741.1</v>
@@ -6699,45 +6699,45 @@
         <v>360.3</v>
       </c>
       <c r="M66">
-        <v>447.3336576</v>
+        <v>621.444876</v>
       </c>
       <c r="N66">
-        <v>-87.03365759999997</v>
+        <v>-261.144876</v>
       </c>
       <c r="O66">
-        <v>-26.11009727999999</v>
+        <v>-78.3434628</v>
       </c>
       <c r="P66">
-        <v>-60.92356031999998</v>
+        <v>-182.8014132</v>
       </c>
       <c r="Q66">
-        <v>178.27643968</v>
+        <v>56.39858679999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1322673077548081</v>
+        <v>0.1391131328625166</v>
       </c>
       <c r="T66">
-        <v>1.996935513967856</v>
+        <v>2.155037710450729</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.2416317175414793</v>
+        <v>0.1739333675027357</v>
       </c>
       <c r="W66">
-        <v>0.1113284638649109</v>
+        <v>0.1658741798054507</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8054390584715976</v>
+        <v>0.5797778916757856</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1565078133754237</v>
+        <v>0.1580578133754237</v>
       </c>
       <c r="C67">
-        <v>-1072.359303340069</v>
+        <v>-1136.969347623513</v>
       </c>
       <c r="D67">
-        <v>1281.385696659931</v>
+        <v>1264.388652376486</v>
       </c>
       <c r="E67">
-        <v>1739.045</v>
+        <v>1786.658</v>
       </c>
       <c r="F67">
-        <v>3094.845</v>
+        <v>3142.458</v>
       </c>
       <c r="G67">
         <v>741.1</v>
@@ -6781,37 +6781,37 @@
         <v>360.3</v>
       </c>
       <c r="M67">
-        <v>621.444876</v>
+        <v>631.0055663999999</v>
       </c>
       <c r="N67">
-        <v>-261.144876</v>
+        <v>-270.7055663999999</v>
       </c>
       <c r="O67">
-        <v>-78.3434628</v>
+        <v>-81.21166991999996</v>
       </c>
       <c r="P67">
-        <v>-182.8014132</v>
+        <v>-189.4938964799999</v>
       </c>
       <c r="Q67">
-        <v>56.39858679999998</v>
+        <v>49.70610352000006</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1391131328625166</v>
+        <v>0.1418576367702376</v>
       </c>
       <c r="T67">
-        <v>2.155037710450729</v>
+        <v>2.218421172522809</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1739333675027357</v>
+        <v>0.1712980134496639</v>
       </c>
       <c r="W67">
-        <v>0.1658741798054507</v>
+        <v>0.1664033588993075</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5797778916757856</v>
+        <v>0.5709933781655465</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1580578133754237</v>
+        <v>0.1596078133754237</v>
       </c>
       <c r="C68">
-        <v>-1136.969347623513</v>
+        <v>-1201.134377497473</v>
       </c>
       <c r="D68">
-        <v>1264.388652376486</v>
+        <v>1247.836622502527</v>
       </c>
       <c r="E68">
-        <v>1786.658</v>
+        <v>1834.271</v>
       </c>
       <c r="F68">
-        <v>3142.458</v>
+        <v>3190.071</v>
       </c>
       <c r="G68">
         <v>741.1</v>
@@ -6863,37 +6863,37 @@
         <v>360.3</v>
       </c>
       <c r="M68">
-        <v>631.0055663999999</v>
+        <v>640.5662568</v>
       </c>
       <c r="N68">
-        <v>-270.7055663999999</v>
+        <v>-280.2662568</v>
       </c>
       <c r="O68">
-        <v>-81.21166991999996</v>
+        <v>-84.07987704</v>
       </c>
       <c r="P68">
-        <v>-189.4938964799999</v>
+        <v>-196.18637976</v>
       </c>
       <c r="Q68">
-        <v>49.70610352000006</v>
+        <v>43.01362023999997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1418576367702376</v>
+        <v>0.1447684742481236</v>
       </c>
       <c r="T68">
-        <v>2.218421172522809</v>
+        <v>2.285646056538652</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1712980134496639</v>
+        <v>0.1687413266817585</v>
       </c>
       <c r="W68">
-        <v>0.1664033588993075</v>
+        <v>0.1669167416023029</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5709933781655465</v>
+        <v>0.562471088939195</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1596078133754237</v>
+        <v>0.1611578133754238</v>
       </c>
       <c r="C69">
-        <v>-1201.134377497473</v>
+        <v>-1264.871644092859</v>
       </c>
       <c r="D69">
-        <v>1247.836622502527</v>
+        <v>1231.71235590714</v>
       </c>
       <c r="E69">
-        <v>1834.271</v>
+        <v>1881.884</v>
       </c>
       <c r="F69">
-        <v>3190.071</v>
+        <v>3237.684</v>
       </c>
       <c r="G69">
         <v>741.1</v>
@@ -6945,37 +6945,37 @@
         <v>360.3</v>
       </c>
       <c r="M69">
-        <v>640.5662568</v>
+        <v>650.1269472</v>
       </c>
       <c r="N69">
-        <v>-280.2662568</v>
+        <v>-289.8269472</v>
       </c>
       <c r="O69">
-        <v>-84.07987704</v>
+        <v>-86.94808415999999</v>
       </c>
       <c r="P69">
-        <v>-196.18637976</v>
+        <v>-202.87886304</v>
       </c>
       <c r="Q69">
-        <v>43.01362023999997</v>
+        <v>36.32113695999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1447684742481236</v>
+        <v>0.1478612390683775</v>
       </c>
       <c r="T69">
-        <v>2.285646056538652</v>
+        <v>2.357072495805485</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1687413266817585</v>
+        <v>0.1662598365834973</v>
       </c>
       <c r="W69">
-        <v>0.1669167416023029</v>
+        <v>0.1674150248140338</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.562471088939195</v>
+        <v>0.5541994552783245</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1611578133754238</v>
+        <v>0.1627078133754238</v>
       </c>
       <c r="C70">
-        <v>-1264.871644092859</v>
+        <v>-1328.197518254379</v>
       </c>
       <c r="D70">
-        <v>1231.71235590714</v>
+        <v>1215.999481745621</v>
       </c>
       <c r="E70">
-        <v>1881.884</v>
+        <v>1929.497</v>
       </c>
       <c r="F70">
-        <v>3237.684</v>
+        <v>3285.297</v>
       </c>
       <c r="G70">
         <v>741.1</v>
@@ -7027,37 +7027,37 @@
         <v>360.3</v>
       </c>
       <c r="M70">
-        <v>650.1269472</v>
+        <v>659.6876375999999</v>
       </c>
       <c r="N70">
-        <v>-289.8269472</v>
+        <v>-299.3876375999999</v>
       </c>
       <c r="O70">
-        <v>-86.94808415999999</v>
+        <v>-89.81629127999996</v>
       </c>
       <c r="P70">
-        <v>-202.87886304</v>
+        <v>-209.5713463199999</v>
       </c>
       <c r="Q70">
-        <v>36.32113695999999</v>
+        <v>29.62865368000007</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1478612390683775</v>
+        <v>0.1511535371028413</v>
       </c>
       <c r="T70">
-        <v>2.357072495805485</v>
+        <v>2.433107092444372</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1662598365834973</v>
+        <v>0.1638502737344612</v>
       </c>
       <c r="W70">
-        <v>0.1674150248140338</v>
+        <v>0.1678988650341202</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5541994552783245</v>
+        <v>0.5461675791148706</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1627078133754238</v>
+        <v>0.1642578133754238</v>
       </c>
       <c r="C71">
-        <v>-1328.197518254379</v>
+        <v>-1391.127545982037</v>
       </c>
       <c r="D71">
-        <v>1215.999481745621</v>
+        <v>1200.682454017963</v>
       </c>
       <c r="E71">
-        <v>1929.497</v>
+        <v>1977.11</v>
       </c>
       <c r="F71">
-        <v>3285.297</v>
+        <v>3332.91</v>
       </c>
       <c r="G71">
         <v>741.1</v>
@@ -7109,37 +7109,37 @@
         <v>360.3</v>
       </c>
       <c r="M71">
-        <v>659.6876375999999</v>
+        <v>669.248328</v>
       </c>
       <c r="N71">
-        <v>-299.3876375999999</v>
+        <v>-308.948328</v>
       </c>
       <c r="O71">
-        <v>-89.81629127999996</v>
+        <v>-92.6844984</v>
       </c>
       <c r="P71">
-        <v>-209.5713463199999</v>
+        <v>-216.2638296</v>
       </c>
       <c r="Q71">
-        <v>29.62865368000007</v>
+        <v>22.93617039999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1511535371028413</v>
+        <v>0.154665321672936</v>
       </c>
       <c r="T71">
-        <v>2.433107092444372</v>
+        <v>2.514210662192518</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1638502737344612</v>
+        <v>0.1615095555382546</v>
       </c>
       <c r="W71">
-        <v>0.1678988650341202</v>
+        <v>0.1683688812479185</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5461675791148706</v>
+        <v>0.5383651851275152</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1642578133754238</v>
+        <v>0.1658078133754238</v>
       </c>
       <c r="C72">
-        <v>-1391.127545982037</v>
+        <v>-1453.676499734637</v>
       </c>
       <c r="D72">
-        <v>1200.682454017963</v>
+        <v>1185.746500265362</v>
       </c>
       <c r="E72">
-        <v>1977.11</v>
+        <v>2024.723</v>
       </c>
       <c r="F72">
-        <v>3332.91</v>
+        <v>3380.523</v>
       </c>
       <c r="G72">
         <v>741.1</v>
@@ -7191,37 +7191,37 @@
         <v>360.3</v>
       </c>
       <c r="M72">
-        <v>669.248328</v>
+        <v>678.8090184</v>
       </c>
       <c r="N72">
-        <v>-308.948328</v>
+        <v>-318.5090184</v>
       </c>
       <c r="O72">
-        <v>-92.6844984</v>
+        <v>-95.55270552</v>
       </c>
       <c r="P72">
-        <v>-216.2638296</v>
+        <v>-222.95631288</v>
       </c>
       <c r="Q72">
-        <v>22.93617039999998</v>
+        <v>16.24368712</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.154665321672936</v>
+        <v>0.1584192982823476</v>
       </c>
       <c r="T72">
-        <v>2.514210662192518</v>
+        <v>2.600907581578467</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1615095555382546</v>
+        <v>0.1592347730658848</v>
       </c>
       <c r="W72">
-        <v>0.1683688812479185</v>
+        <v>0.1688256575683703</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5383651851275152</v>
+        <v>0.5307825768862826</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1658078133754237</v>
+        <v>0.1673578133754237</v>
       </c>
       <c r="C73">
-        <v>-1453.676499734636</v>
+        <v>-1515.858425951171</v>
       </c>
       <c r="D73">
-        <v>1185.746500265363</v>
+        <v>1171.177574048828</v>
       </c>
       <c r="E73">
-        <v>2024.723</v>
+        <v>2072.336</v>
       </c>
       <c r="F73">
-        <v>3380.522999999999</v>
+        <v>3428.136</v>
       </c>
       <c r="G73">
         <v>741.1</v>
@@ -7273,37 +7273,37 @@
         <v>360.3</v>
       </c>
       <c r="M73">
-        <v>678.8090183999999</v>
+        <v>688.3697087999999</v>
       </c>
       <c r="N73">
-        <v>-318.5090183999999</v>
+        <v>-328.0697087999999</v>
       </c>
       <c r="O73">
-        <v>-95.55270551999996</v>
+        <v>-98.42091263999997</v>
       </c>
       <c r="P73">
-        <v>-222.9563128799999</v>
+        <v>-229.6487961599999</v>
       </c>
       <c r="Q73">
-        <v>16.24368712000006</v>
+        <v>9.551203840000085</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1584192982823475</v>
+        <v>0.1624414160781457</v>
       </c>
       <c r="T73">
-        <v>2.600907581578465</v>
+        <v>2.693797138063411</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1592347730658848</v>
+        <v>0.1570231789955253</v>
       </c>
       <c r="W73">
-        <v>0.1688256575683703</v>
+        <v>0.1692697456576985</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5307825768862826</v>
+        <v>0.5234105966517509</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1673578133754237</v>
+        <v>0.1689078133754237</v>
       </c>
       <c r="C74">
-        <v>-1515.858425951171</v>
+        <v>-1577.686689111446</v>
       </c>
       <c r="D74">
-        <v>1171.177574048828</v>
+        <v>1156.962310888553</v>
       </c>
       <c r="E74">
-        <v>2072.336</v>
+        <v>2119.949</v>
       </c>
       <c r="F74">
-        <v>3428.136</v>
+        <v>3475.748999999999</v>
       </c>
       <c r="G74">
         <v>741.1</v>
@@ -7355,37 +7355,37 @@
         <v>360.3</v>
       </c>
       <c r="M74">
-        <v>688.3697087999999</v>
+        <v>697.9303991999999</v>
       </c>
       <c r="N74">
-        <v>-328.0697087999999</v>
+        <v>-337.6303991999999</v>
       </c>
       <c r="O74">
-        <v>-98.42091263999997</v>
+        <v>-101.28911976</v>
       </c>
       <c r="P74">
-        <v>-229.6487961599999</v>
+        <v>-236.3412794399999</v>
       </c>
       <c r="Q74">
-        <v>9.551203840000085</v>
+        <v>2.858720560000052</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1624414160781457</v>
+        <v>0.1667614685254844</v>
       </c>
       <c r="T74">
-        <v>2.693797138063411</v>
+        <v>2.793567402436129</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1570231789955253</v>
+        <v>0.1548721765435318</v>
       </c>
       <c r="W74">
-        <v>0.1692697456576985</v>
+        <v>0.1697016669500588</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5234105966517509</v>
+        <v>0.5162405884784393</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1689078133754237</v>
+        <v>0.1704578133754237</v>
       </c>
       <c r="C75">
-        <v>-1577.686689111446</v>
+        <v>-1639.174012626444</v>
       </c>
       <c r="D75">
-        <v>1156.962310888553</v>
+        <v>1143.087987373555</v>
       </c>
       <c r="E75">
-        <v>2119.949</v>
+        <v>2167.562</v>
       </c>
       <c r="F75">
-        <v>3475.748999999999</v>
+        <v>3523.362</v>
       </c>
       <c r="G75">
         <v>741.1</v>
@@ -7437,37 +7437,37 @@
         <v>360.3</v>
       </c>
       <c r="M75">
-        <v>697.9303991999999</v>
+        <v>707.4910895999999</v>
       </c>
       <c r="N75">
-        <v>-337.6303991999999</v>
+        <v>-347.1910895999999</v>
       </c>
       <c r="O75">
-        <v>-101.28911976</v>
+        <v>-104.15732688</v>
       </c>
       <c r="P75">
-        <v>-236.3412794399999</v>
+        <v>-243.0337627199999</v>
       </c>
       <c r="Q75">
-        <v>2.858720560000052</v>
+        <v>-3.833762719999925</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1667614685254844</v>
+        <v>0.1714138326995415</v>
       </c>
       <c r="T75">
-        <v>2.793567402436129</v>
+        <v>2.901012302529827</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1548721765435318</v>
+        <v>0.1527793092929435</v>
       </c>
       <c r="W75">
-        <v>0.1697016669500588</v>
+        <v>0.1701219146939769</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5162405884784393</v>
+        <v>0.5092643643098118</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1704578133754237</v>
+        <v>0.1720078133754238</v>
       </c>
       <c r="C76">
-        <v>-1639.174012626444</v>
+        <v>-1700.332516821407</v>
       </c>
       <c r="D76">
-        <v>1143.087987373555</v>
+        <v>1129.542483178593</v>
       </c>
       <c r="E76">
-        <v>2167.562</v>
+        <v>2215.175</v>
       </c>
       <c r="F76">
-        <v>3523.362</v>
+        <v>3570.974999999999</v>
       </c>
       <c r="G76">
         <v>741.1</v>
@@ -7519,37 +7519,37 @@
         <v>360.3</v>
       </c>
       <c r="M76">
-        <v>707.4910895999999</v>
+        <v>717.0517799999999</v>
       </c>
       <c r="N76">
-        <v>-347.1910895999999</v>
+        <v>-356.7517799999999</v>
       </c>
       <c r="O76">
-        <v>-104.15732688</v>
+        <v>-107.025534</v>
       </c>
       <c r="P76">
-        <v>-243.0337627199999</v>
+        <v>-249.7262459999999</v>
       </c>
       <c r="Q76">
-        <v>-3.833762719999925</v>
+        <v>-10.52624599999993</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1714138326995415</v>
+        <v>0.1764383860075232</v>
       </c>
       <c r="T76">
-        <v>2.901012302529827</v>
+        <v>3.017052794631021</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1527793092929435</v>
+        <v>0.1507422518357043</v>
       </c>
       <c r="W76">
-        <v>0.1701219146939769</v>
+        <v>0.1705309558313906</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5092643643098118</v>
+        <v>0.502474172785681</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1720078133754238</v>
+        <v>0.2007757379363158</v>
       </c>
       <c r="C77">
-        <v>-1700.332516821407</v>
+        <v>-1951.583405830095</v>
       </c>
       <c r="D77">
-        <v>1129.542483178593</v>
+        <v>925.9045941699044</v>
       </c>
       <c r="E77">
-        <v>2215.175</v>
+        <v>2262.788</v>
       </c>
       <c r="F77">
-        <v>3570.974999999999</v>
+        <v>3618.587999999999</v>
       </c>
       <c r="G77">
         <v>741.1</v>
@@ -7601,45 +7601,45 @@
         <v>360.3</v>
       </c>
       <c r="M77">
-        <v>717.0517799999999</v>
+        <v>853.2630503999999</v>
       </c>
       <c r="N77">
-        <v>-356.7517799999999</v>
+        <v>-492.9630503999999</v>
       </c>
       <c r="O77">
-        <v>-107.025534</v>
+        <v>-147.88891512</v>
       </c>
       <c r="P77">
-        <v>-249.7262459999999</v>
+        <v>-345.07413528</v>
       </c>
       <c r="Q77">
-        <v>-10.52624599999993</v>
+        <v>-105.87413528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1764383860075232</v>
+        <v>0.1844563377615533</v>
       </c>
       <c r="T77">
-        <v>3.017052794631021</v>
+        <v>3.202224890567051</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1507422518357043</v>
+        <v>0.1266784023394997</v>
       </c>
       <c r="W77">
-        <v>0.1705309558313906</v>
+        <v>0.205929232728346</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.502474172785681</v>
+        <v>0.4222613411316657</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2007757379363158</v>
+        <v>0.2026757379363158</v>
       </c>
       <c r="C78">
-        <v>-1951.583405830095</v>
+        <v>-2010.091393422259</v>
       </c>
       <c r="D78">
-        <v>925.9045941699044</v>
+        <v>915.0096065777402</v>
       </c>
       <c r="E78">
-        <v>2262.788</v>
+        <v>2310.401</v>
       </c>
       <c r="F78">
-        <v>3618.587999999999</v>
+        <v>3666.201</v>
       </c>
       <c r="G78">
         <v>741.1</v>
@@ -7683,37 +7683,37 @@
         <v>360.3</v>
       </c>
       <c r="M78">
-        <v>853.2630503999999</v>
+        <v>864.4901957999999</v>
       </c>
       <c r="N78">
-        <v>-492.9630503999999</v>
+        <v>-504.1901957999999</v>
       </c>
       <c r="O78">
-        <v>-147.88891512</v>
+        <v>-151.25705874</v>
       </c>
       <c r="P78">
-        <v>-345.07413528</v>
+        <v>-352.9331370599999</v>
       </c>
       <c r="Q78">
-        <v>-105.87413528</v>
+        <v>-113.7331370599999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1844563377615533</v>
+        <v>0.1904848741859687</v>
       </c>
       <c r="T78">
-        <v>3.202224890567051</v>
+        <v>3.34145205972214</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1266784023394997</v>
+        <v>0.1250332282831426</v>
       </c>
       <c r="W78">
-        <v>0.205929232728346</v>
+        <v>0.206317164770835</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4222613411316657</v>
+        <v>0.4167774276104752</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2026757379363158</v>
+        <v>0.2045757379363158</v>
       </c>
       <c r="C79">
-        <v>-2010.091393422259</v>
+        <v>-2068.345963406336</v>
       </c>
       <c r="D79">
-        <v>915.0096065777402</v>
+        <v>904.368036593664</v>
       </c>
       <c r="E79">
-        <v>2310.401</v>
+        <v>2358.014</v>
       </c>
       <c r="F79">
-        <v>3666.201</v>
+        <v>3713.813999999999</v>
       </c>
       <c r="G79">
         <v>741.1</v>
@@ -7765,37 +7765,37 @@
         <v>360.3</v>
       </c>
       <c r="M79">
-        <v>864.4901957999999</v>
+        <v>875.7173411999999</v>
       </c>
       <c r="N79">
-        <v>-504.1901957999999</v>
+        <v>-515.4173411999998</v>
       </c>
       <c r="O79">
-        <v>-151.25705874</v>
+        <v>-154.6252023599999</v>
       </c>
       <c r="P79">
-        <v>-352.9331370599999</v>
+        <v>-360.7921388399999</v>
       </c>
       <c r="Q79">
-        <v>-113.7331370599999</v>
+        <v>-121.5921388399999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1904848741859687</v>
+        <v>0.19706145937624</v>
       </c>
       <c r="T79">
-        <v>3.34145205972214</v>
+        <v>3.493336244254965</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1250332282831426</v>
+        <v>0.1234302381769484</v>
       </c>
       <c r="W79">
-        <v>0.206317164770835</v>
+        <v>0.2066951498378756</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4167774276104752</v>
+        <v>0.4114341272564949</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2045757379363158</v>
+        <v>0.2064757379363157</v>
       </c>
       <c r="C80">
-        <v>-2068.345963406336</v>
+        <v>-2126.355855882097</v>
       </c>
       <c r="D80">
-        <v>904.368036593664</v>
+        <v>893.9711441179026</v>
       </c>
       <c r="E80">
-        <v>2358.014</v>
+        <v>2405.627</v>
       </c>
       <c r="F80">
-        <v>3713.813999999999</v>
+        <v>3761.427</v>
       </c>
       <c r="G80">
         <v>741.1</v>
@@ -7847,37 +7847,37 @@
         <v>360.3</v>
       </c>
       <c r="M80">
-        <v>875.7173411999999</v>
+        <v>886.9444866</v>
       </c>
       <c r="N80">
-        <v>-515.4173411999998</v>
+        <v>-526.6444865999999</v>
       </c>
       <c r="O80">
-        <v>-154.6252023599999</v>
+        <v>-157.99334598</v>
       </c>
       <c r="P80">
-        <v>-360.7921388399999</v>
+        <v>-368.65114062</v>
       </c>
       <c r="Q80">
-        <v>-121.5921388399999</v>
+        <v>-129.45114062</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.19706145937624</v>
+        <v>0.2042643860132038</v>
       </c>
       <c r="T80">
-        <v>3.493336244254965</v>
+        <v>3.659685589219487</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1234302381769484</v>
+        <v>0.1218678300987592</v>
       </c>
       <c r="W80">
-        <v>0.2066951498378756</v>
+        <v>0.2070635656627126</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4114341272564949</v>
+        <v>0.4062261003291974</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2064757379363157</v>
+        <v>0.2083757379363158</v>
       </c>
       <c r="C81">
-        <v>-2126.355855882097</v>
+        <v>-2184.129413601861</v>
       </c>
       <c r="D81">
-        <v>893.9711441179026</v>
+        <v>883.8105863981383</v>
       </c>
       <c r="E81">
-        <v>2405.627</v>
+        <v>2453.24</v>
       </c>
       <c r="F81">
-        <v>3761.427</v>
+        <v>3809.04</v>
       </c>
       <c r="G81">
         <v>741.1</v>
@@ -7929,37 +7929,37 @@
         <v>360.3</v>
       </c>
       <c r="M81">
-        <v>886.9444866</v>
+        <v>898.1716319999999</v>
       </c>
       <c r="N81">
-        <v>-526.6444865999999</v>
+        <v>-537.8716319999999</v>
       </c>
       <c r="O81">
-        <v>-157.99334598</v>
+        <v>-161.3614895999999</v>
       </c>
       <c r="P81">
-        <v>-368.65114062</v>
+        <v>-376.5101423999999</v>
       </c>
       <c r="Q81">
-        <v>-129.45114062</v>
+        <v>-137.3101424</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2042643860132038</v>
+        <v>0.212187605313864</v>
       </c>
       <c r="T81">
-        <v>3.659685589219487</v>
+        <v>3.842669868680462</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1218678300987592</v>
+        <v>0.1203444822225247</v>
       </c>
       <c r="W81">
-        <v>0.2070635656627126</v>
+        <v>0.2074227710919287</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4062261003291974</v>
+        <v>0.4011482740750825</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2083757379363158</v>
+        <v>0.2102757379363157</v>
       </c>
       <c r="C82">
-        <v>-2184.129413601861</v>
+        <v>-2241.674604297292</v>
       </c>
       <c r="D82">
-        <v>883.8105863981383</v>
+        <v>873.8783957027076</v>
       </c>
       <c r="E82">
-        <v>2453.24</v>
+        <v>2500.853</v>
       </c>
       <c r="F82">
-        <v>3809.04</v>
+        <v>3856.653</v>
       </c>
       <c r="G82">
         <v>741.1</v>
@@ -8011,37 +8011,37 @@
         <v>360.3</v>
       </c>
       <c r="M82">
-        <v>898.1716319999999</v>
+        <v>909.3987774</v>
       </c>
       <c r="N82">
-        <v>-537.8716319999999</v>
+        <v>-549.0987774</v>
       </c>
       <c r="O82">
-        <v>-161.3614895999999</v>
+        <v>-164.72963322</v>
       </c>
       <c r="P82">
-        <v>-376.5101423999999</v>
+        <v>-384.36914418</v>
       </c>
       <c r="Q82">
-        <v>-137.3101424</v>
+        <v>-145.16914418</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.212187605313864</v>
+        <v>0.2209448476988042</v>
       </c>
       <c r="T82">
-        <v>3.842669868680462</v>
+        <v>4.044915651242591</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1203444822225247</v>
+        <v>0.1188587478740985</v>
       </c>
       <c r="W82">
-        <v>0.2074227710919287</v>
+        <v>0.2077731072512876</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4011482740750825</v>
+        <v>0.3961958262469949</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2102757379363157</v>
+        <v>0.2121757379363158</v>
       </c>
       <c r="C83">
-        <v>-2241.674604297292</v>
+        <v>-2298.999041517477</v>
       </c>
       <c r="D83">
-        <v>873.8783957027076</v>
+        <v>864.1669584825231</v>
       </c>
       <c r="E83">
-        <v>2500.853</v>
+        <v>2548.466</v>
       </c>
       <c r="F83">
-        <v>3856.653</v>
+        <v>3904.266</v>
       </c>
       <c r="G83">
         <v>741.1</v>
@@ -8093,37 +8093,37 @@
         <v>360.3</v>
       </c>
       <c r="M83">
-        <v>909.3987774</v>
+        <v>920.6259227999999</v>
       </c>
       <c r="N83">
-        <v>-549.0987774</v>
+        <v>-560.3259227999999</v>
       </c>
       <c r="O83">
-        <v>-164.72963322</v>
+        <v>-168.09777684</v>
       </c>
       <c r="P83">
-        <v>-384.36914418</v>
+        <v>-392.22814596</v>
       </c>
       <c r="Q83">
-        <v>-145.16914418</v>
+        <v>-153.02814596</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2209448476988042</v>
+        <v>0.2306751170154045</v>
       </c>
       <c r="T83">
-        <v>4.044915651242591</v>
+        <v>4.269633187422736</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1188587478740985</v>
+        <v>0.1174092509488046</v>
       </c>
       <c r="W83">
-        <v>0.2077731072512876</v>
+        <v>0.2081148986262719</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3961958262469949</v>
+        <v>0.3913641698293486</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2121757379363158</v>
+        <v>0.2140757379363157</v>
       </c>
       <c r="C84">
-        <v>-2298.999041517477</v>
+        <v>-2356.110004092827</v>
       </c>
       <c r="D84">
-        <v>864.1669584825231</v>
+        <v>854.6689959071728</v>
       </c>
       <c r="E84">
-        <v>2548.466</v>
+        <v>2596.079</v>
       </c>
       <c r="F84">
-        <v>3904.266</v>
+        <v>3951.879</v>
       </c>
       <c r="G84">
         <v>741.1</v>
@@ -8175,37 +8175,37 @@
         <v>360.3</v>
       </c>
       <c r="M84">
-        <v>920.6259227999999</v>
+        <v>931.8530682000001</v>
       </c>
       <c r="N84">
-        <v>-560.3259227999999</v>
+        <v>-571.5530682000001</v>
       </c>
       <c r="O84">
-        <v>-168.09777684</v>
+        <v>-171.46592046</v>
       </c>
       <c r="P84">
-        <v>-392.22814596</v>
+        <v>-400.0871477400001</v>
       </c>
       <c r="Q84">
-        <v>-153.02814596</v>
+        <v>-160.8871477400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2306751170154045</v>
+        <v>0.2415501238986635</v>
       </c>
       <c r="T84">
-        <v>4.269633187422736</v>
+        <v>4.520788080800544</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1174092509488046</v>
+        <v>0.1159946816602648</v>
       </c>
       <c r="W84">
-        <v>0.2081148986262719</v>
+        <v>0.2084484540645096</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3913641698293486</v>
+        <v>0.3866489388675491</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2140757379363157</v>
+        <v>0.2159757379363157</v>
       </c>
       <c r="C85">
-        <v>-2356.110004092827</v>
+        <v>-2413.014454329387</v>
       </c>
       <c r="D85">
-        <v>854.6689959071728</v>
+        <v>845.3775456706123</v>
       </c>
       <c r="E85">
-        <v>2596.079</v>
+        <v>2643.692</v>
       </c>
       <c r="F85">
-        <v>3951.879</v>
+        <v>3999.492</v>
       </c>
       <c r="G85">
         <v>741.1</v>
@@ -8257,37 +8257,37 @@
         <v>360.3</v>
       </c>
       <c r="M85">
-        <v>931.8530682000001</v>
+        <v>943.0802136</v>
       </c>
       <c r="N85">
-        <v>-571.5530682000001</v>
+        <v>-582.7802136</v>
       </c>
       <c r="O85">
-        <v>-171.46592046</v>
+        <v>-174.83406408</v>
       </c>
       <c r="P85">
-        <v>-400.0871477400001</v>
+        <v>-407.9461495200001</v>
       </c>
       <c r="Q85">
-        <v>-160.8871477400001</v>
+        <v>-168.7461495200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2415501238986635</v>
+        <v>0.25378450664233</v>
       </c>
       <c r="T85">
-        <v>4.520788080800544</v>
+        <v>4.803337335850578</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1159946816602648</v>
+        <v>0.1146137925928807</v>
       </c>
       <c r="W85">
-        <v>0.2084484540645096</v>
+        <v>0.2087740677065987</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3866489388675491</v>
+        <v>0.3820459753096022</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2159757379363157</v>
+        <v>0.2178757379363157</v>
       </c>
       <c r="C86">
-        <v>-2413.014454329385</v>
+        <v>-2469.719055029122</v>
       </c>
       <c r="D86">
-        <v>845.3775456706137</v>
+        <v>836.2859449708775</v>
       </c>
       <c r="E86">
-        <v>2643.692</v>
+        <v>2691.304999999999</v>
       </c>
       <c r="F86">
-        <v>3999.491999999999</v>
+        <v>4047.104999999999</v>
       </c>
       <c r="G86">
         <v>741.1</v>
@@ -8339,37 +8339,37 @@
         <v>360.3</v>
       </c>
       <c r="M86">
-        <v>943.0802135999999</v>
+        <v>954.3073589999998</v>
       </c>
       <c r="N86">
-        <v>-582.7802135999998</v>
+        <v>-594.0073589999997</v>
       </c>
       <c r="O86">
-        <v>-174.8340640799999</v>
+        <v>-178.2022076999999</v>
       </c>
       <c r="P86">
-        <v>-407.9461495199998</v>
+        <v>-415.8051512999998</v>
       </c>
       <c r="Q86">
-        <v>-168.7461495199998</v>
+        <v>-176.6051512999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2537845066423299</v>
+        <v>0.2676501404184852</v>
       </c>
       <c r="T86">
-        <v>4.803337335850576</v>
+        <v>5.12355982490728</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1146137925928807</v>
+        <v>0.1132653950329645</v>
       </c>
       <c r="W86">
-        <v>0.2087740677065987</v>
+        <v>0.209092019851227</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3820459753096024</v>
+        <v>0.3775513167765483</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2178757379363157</v>
+        <v>0.2197757379363157</v>
       </c>
       <c r="C87">
-        <v>-2469.719055029122</v>
+        <v>-2526.230185423617</v>
       </c>
       <c r="D87">
-        <v>836.2859449708775</v>
+        <v>827.3878145763824</v>
       </c>
       <c r="E87">
-        <v>2691.304999999999</v>
+        <v>2738.918</v>
       </c>
       <c r="F87">
-        <v>4047.104999999999</v>
+        <v>4094.717999999999</v>
       </c>
       <c r="G87">
         <v>741.1</v>
@@ -8421,37 +8421,37 @@
         <v>360.3</v>
       </c>
       <c r="M87">
-        <v>954.3073589999998</v>
+        <v>965.5345043999999</v>
       </c>
       <c r="N87">
-        <v>-594.0073589999997</v>
+        <v>-605.2345043999999</v>
       </c>
       <c r="O87">
-        <v>-178.2022076999999</v>
+        <v>-181.57035132</v>
       </c>
       <c r="P87">
-        <v>-415.8051512999998</v>
+        <v>-423.6641530799999</v>
       </c>
       <c r="Q87">
-        <v>-176.6051512999998</v>
+        <v>-184.4641530799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2676501404184852</v>
+        <v>0.2834965790198056</v>
       </c>
       <c r="T87">
-        <v>5.12355982490728</v>
+        <v>5.48952838382923</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1132653950329645</v>
+        <v>0.1119483555558369</v>
       </c>
       <c r="W87">
-        <v>0.209092019851227</v>
+        <v>0.2094025777599337</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3775513167765483</v>
+        <v>0.3731611851861232</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2197757379363157</v>
+        <v>0.2216757379363157</v>
       </c>
       <c r="C88">
-        <v>-2526.230185423617</v>
+        <v>-2582.553956101276</v>
       </c>
       <c r="D88">
-        <v>827.3878145763824</v>
+        <v>818.6770438987238</v>
       </c>
       <c r="E88">
-        <v>2738.918</v>
+        <v>2786.530999999999</v>
       </c>
       <c r="F88">
-        <v>4094.717999999999</v>
+        <v>4142.330999999999</v>
       </c>
       <c r="G88">
         <v>741.1</v>
@@ -8503,37 +8503,37 @@
         <v>360.3</v>
       </c>
       <c r="M88">
-        <v>965.5345043999999</v>
+        <v>976.7616497999999</v>
       </c>
       <c r="N88">
-        <v>-605.2345043999999</v>
+        <v>-616.4616497999998</v>
       </c>
       <c r="O88">
-        <v>-181.57035132</v>
+        <v>-184.9384949399999</v>
       </c>
       <c r="P88">
-        <v>-423.6641530799999</v>
+        <v>-431.5231548599999</v>
       </c>
       <c r="Q88">
-        <v>-184.4641530799999</v>
+        <v>-192.3231548599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2834965790198056</v>
+        <v>0.3017809312520984</v>
       </c>
       <c r="T88">
-        <v>5.48952838382923</v>
+        <v>5.911799797969939</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1119483555558369</v>
+        <v>0.1106615928482986</v>
       </c>
       <c r="W88">
-        <v>0.2094025777599337</v>
+        <v>0.2097059964063712</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3731611851861232</v>
+        <v>0.3688719761609954</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2216757379363157</v>
+        <v>0.2235757379363157</v>
       </c>
       <c r="C89">
-        <v>-2582.553956101276</v>
+        <v>-2638.696223001421</v>
       </c>
       <c r="D89">
-        <v>818.6770438987238</v>
+        <v>810.147776998579</v>
       </c>
       <c r="E89">
-        <v>2786.530999999999</v>
+        <v>2834.144</v>
       </c>
       <c r="F89">
-        <v>4142.330999999999</v>
+        <v>4189.944</v>
       </c>
       <c r="G89">
         <v>741.1</v>
@@ -8585,37 +8585,37 @@
         <v>360.3</v>
       </c>
       <c r="M89">
-        <v>976.7616497999999</v>
+        <v>987.9887951999999</v>
       </c>
       <c r="N89">
-        <v>-616.4616497999998</v>
+        <v>-627.6887952</v>
       </c>
       <c r="O89">
-        <v>-184.9384949399999</v>
+        <v>-188.30663856</v>
       </c>
       <c r="P89">
-        <v>-431.5231548599999</v>
+        <v>-439.3821566399999</v>
       </c>
       <c r="Q89">
-        <v>-192.3231548599999</v>
+        <v>-200.18215664</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3017809312520984</v>
+        <v>0.3231126755231066</v>
       </c>
       <c r="T89">
-        <v>5.911799797969939</v>
+        <v>6.404449781134103</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1106615928482986</v>
+        <v>0.1094040747477497</v>
       </c>
       <c r="W89">
-        <v>0.2097059964063712</v>
+        <v>0.2100025191744806</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3688719761609954</v>
+        <v>0.3646802491591657</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2235757379363157</v>
+        <v>0.2254757379363157</v>
       </c>
       <c r="C90">
-        <v>-2638.696223001421</v>
+        <v>-2694.662600542636</v>
       </c>
       <c r="D90">
-        <v>810.147776998579</v>
+        <v>801.7943994573636</v>
       </c>
       <c r="E90">
-        <v>2834.144</v>
+        <v>2881.757</v>
       </c>
       <c r="F90">
-        <v>4189.944</v>
+        <v>4237.557</v>
       </c>
       <c r="G90">
         <v>741.1</v>
@@ -8667,37 +8667,37 @@
         <v>360.3</v>
       </c>
       <c r="M90">
-        <v>987.9887951999999</v>
+        <v>999.2159406</v>
       </c>
       <c r="N90">
-        <v>-627.6887952</v>
+        <v>-638.9159405999999</v>
       </c>
       <c r="O90">
-        <v>-188.30663856</v>
+        <v>-191.67478218</v>
       </c>
       <c r="P90">
-        <v>-439.3821566399999</v>
+        <v>-447.2411584199999</v>
       </c>
       <c r="Q90">
-        <v>-200.18215664</v>
+        <v>-208.0411584199999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3231126755231066</v>
+        <v>0.3483229187524799</v>
       </c>
       <c r="T90">
-        <v>6.404449781134103</v>
+        <v>6.986672488509929</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1094040747477497</v>
+        <v>0.1081748154809211</v>
       </c>
       <c r="W90">
-        <v>0.2100025191744806</v>
+        <v>0.2102923785095988</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3646802491591657</v>
+        <v>0.360582718269737</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2254757379363157</v>
+        <v>0.2273757379363157</v>
       </c>
       <c r="C91">
-        <v>-2694.662600542636</v>
+        <v>-2750.458473947214</v>
       </c>
       <c r="D91">
-        <v>801.7943994573636</v>
+        <v>793.6115260527848</v>
       </c>
       <c r="E91">
-        <v>2881.757</v>
+        <v>2929.369999999999</v>
       </c>
       <c r="F91">
-        <v>4237.557</v>
+        <v>4285.169999999999</v>
       </c>
       <c r="G91">
         <v>741.1</v>
@@ -8749,37 +8749,37 @@
         <v>360.3</v>
       </c>
       <c r="M91">
-        <v>999.2159406</v>
+        <v>1010.443086</v>
       </c>
       <c r="N91">
-        <v>-638.9159405999999</v>
+        <v>-650.1430859999998</v>
       </c>
       <c r="O91">
-        <v>-191.67478218</v>
+        <v>-195.0429257999999</v>
       </c>
       <c r="P91">
-        <v>-447.2411584199999</v>
+        <v>-455.1001601999999</v>
       </c>
       <c r="Q91">
-        <v>-208.0411584199999</v>
+        <v>-215.9001601999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3483229187524799</v>
+        <v>0.3785752106277279</v>
       </c>
       <c r="T91">
-        <v>6.986672488509929</v>
+        <v>7.685339737360922</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1081748154809211</v>
+        <v>0.1069728730866886</v>
       </c>
       <c r="W91">
-        <v>0.2102923785095988</v>
+        <v>0.2105757965261588</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.360582718269737</v>
+        <v>0.3565762436222956</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2273757379363157</v>
+        <v>0.2292757379363157</v>
       </c>
       <c r="C92">
-        <v>-2750.458473947214</v>
+        <v>-2806.089010818539</v>
       </c>
       <c r="D92">
-        <v>793.6115260527848</v>
+        <v>785.5939891814609</v>
       </c>
       <c r="E92">
-        <v>2929.369999999999</v>
+        <v>2976.983</v>
       </c>
       <c r="F92">
-        <v>4285.169999999999</v>
+        <v>4332.782999999999</v>
       </c>
       <c r="G92">
         <v>741.1</v>
@@ -8831,37 +8831,37 @@
         <v>360.3</v>
       </c>
       <c r="M92">
-        <v>1010.443086</v>
+        <v>1021.6702314</v>
       </c>
       <c r="N92">
-        <v>-650.1430859999998</v>
+        <v>-661.3702314</v>
       </c>
       <c r="O92">
-        <v>-195.0429257999999</v>
+        <v>-198.41106942</v>
       </c>
       <c r="P92">
-        <v>-455.1001601999999</v>
+        <v>-462.95916198</v>
       </c>
       <c r="Q92">
-        <v>-215.9001601999999</v>
+        <v>-223.75916198</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3785752106277279</v>
+        <v>0.4155502340308089</v>
       </c>
       <c r="T92">
-        <v>7.685339737360922</v>
+        <v>8.539266374845472</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1069728730866886</v>
+        <v>0.1057973470088129</v>
       </c>
       <c r="W92">
-        <v>0.2105757965261588</v>
+        <v>0.2108529855753219</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3565762436222956</v>
+        <v>0.3526578233627098</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2292757379363157</v>
+        <v>0.2311757379363157</v>
       </c>
       <c r="C93">
-        <v>-2806.089010818539</v>
+        <v>-2861.559172023718</v>
       </c>
       <c r="D93">
-        <v>785.5939891814609</v>
+        <v>777.7368279762811</v>
       </c>
       <c r="E93">
-        <v>2976.983</v>
+        <v>3024.596</v>
       </c>
       <c r="F93">
-        <v>4332.782999999999</v>
+        <v>4380.396</v>
       </c>
       <c r="G93">
         <v>741.1</v>
@@ -8913,37 +8913,37 @@
         <v>360.3</v>
       </c>
       <c r="M93">
-        <v>1021.6702314</v>
+        <v>1032.8973768</v>
       </c>
       <c r="N93">
-        <v>-661.3702314</v>
+        <v>-672.5973768000001</v>
       </c>
       <c r="O93">
-        <v>-198.41106942</v>
+        <v>-201.77921304</v>
       </c>
       <c r="P93">
-        <v>-462.95916198</v>
+        <v>-470.8181637600001</v>
       </c>
       <c r="Q93">
-        <v>-223.75916198</v>
+        <v>-231.6181637600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4155502340308089</v>
+        <v>0.4617690132846601</v>
       </c>
       <c r="T93">
-        <v>8.539266374845472</v>
+        <v>9.606674671701159</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1057973470088129</v>
+        <v>0.1046473758456736</v>
       </c>
       <c r="W93">
-        <v>0.2108529855753219</v>
+        <v>0.2111241487755902</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3526578233627098</v>
+        <v>0.3488245861522454</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2311757379363157</v>
+        <v>0.2330757379363157</v>
       </c>
       <c r="C94">
-        <v>-2861.559172023718</v>
+        <v>-2916.87372192964</v>
       </c>
       <c r="D94">
-        <v>777.7368279762811</v>
+        <v>770.0352780703588</v>
       </c>
       <c r="E94">
-        <v>3024.596</v>
+        <v>3072.208999999999</v>
       </c>
       <c r="F94">
-        <v>4380.396</v>
+        <v>4428.008999999999</v>
       </c>
       <c r="G94">
         <v>741.1</v>
@@ -8995,37 +8995,37 @@
         <v>360.3</v>
       </c>
       <c r="M94">
-        <v>1032.8973768</v>
+        <v>1044.1245222</v>
       </c>
       <c r="N94">
-        <v>-672.5973768000001</v>
+        <v>-683.8245221999998</v>
       </c>
       <c r="O94">
-        <v>-201.77921304</v>
+        <v>-205.1473566599999</v>
       </c>
       <c r="P94">
-        <v>-470.8181637600001</v>
+        <v>-478.6771655399999</v>
       </c>
       <c r="Q94">
-        <v>-231.6181637600001</v>
+        <v>-239.4771655399999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4617690132846601</v>
+        <v>0.5211931580396115</v>
       </c>
       <c r="T94">
-        <v>9.606674671701159</v>
+        <v>10.97905676765847</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1046473758456736</v>
+        <v>0.1035221352451826</v>
       </c>
       <c r="W94">
-        <v>0.2111241487755902</v>
+        <v>0.211389480509186</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3488245861522454</v>
+        <v>0.3450737841506085</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2330757379363157</v>
+        <v>0.2349757379363157</v>
       </c>
       <c r="C95">
-        <v>-2916.87372192964</v>
+        <v>-2972.037238036799</v>
       </c>
       <c r="D95">
-        <v>770.0352780703588</v>
+        <v>762.4847619631998</v>
       </c>
       <c r="E95">
-        <v>3072.208999999999</v>
+        <v>3119.822</v>
       </c>
       <c r="F95">
-        <v>4428.008999999999</v>
+        <v>4475.621999999999</v>
       </c>
       <c r="G95">
         <v>741.1</v>
@@ -9077,37 +9077,37 @@
         <v>360.3</v>
       </c>
       <c r="M95">
-        <v>1044.1245222</v>
+        <v>1055.3516676</v>
       </c>
       <c r="N95">
-        <v>-683.8245221999998</v>
+        <v>-695.0516676</v>
       </c>
       <c r="O95">
-        <v>-205.1473566599999</v>
+        <v>-208.51550028</v>
       </c>
       <c r="P95">
-        <v>-478.6771655399999</v>
+        <v>-486.53616732</v>
       </c>
       <c r="Q95">
-        <v>-239.4771655399999</v>
+        <v>-247.33616732</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5211931580396115</v>
+        <v>0.6004253510462136</v>
       </c>
       <c r="T95">
-        <v>10.97905676765847</v>
+        <v>12.80889956226822</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1035221352451826</v>
+        <v>0.1024208359340636</v>
       </c>
       <c r="W95">
-        <v>0.211389480509186</v>
+        <v>0.2116491668867478</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3450737841506085</v>
+        <v>0.3414027864468786</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2349757379363157</v>
+        <v>0.2368757379363158</v>
       </c>
       <c r="C96">
-        <v>-2972.037238036799</v>
+        <v>-3027.054120051847</v>
       </c>
       <c r="D96">
-        <v>762.4847619631998</v>
+        <v>755.0808799481522</v>
       </c>
       <c r="E96">
-        <v>3119.822</v>
+        <v>3167.435</v>
       </c>
       <c r="F96">
-        <v>4475.621999999999</v>
+        <v>4523.235</v>
       </c>
       <c r="G96">
         <v>741.1</v>
@@ -9159,37 +9159,37 @@
         <v>360.3</v>
       </c>
       <c r="M96">
-        <v>1055.3516676</v>
+        <v>1066.578813</v>
       </c>
       <c r="N96">
-        <v>-695.0516676</v>
+        <v>-706.2788129999999</v>
       </c>
       <c r="O96">
-        <v>-208.51550028</v>
+        <v>-211.8836439</v>
       </c>
       <c r="P96">
-        <v>-486.53616732</v>
+        <v>-494.3951691</v>
       </c>
       <c r="Q96">
-        <v>-247.33616732</v>
+        <v>-255.1951691</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6004253510462136</v>
+        <v>0.7113504212554568</v>
       </c>
       <c r="T96">
-        <v>12.80889956226822</v>
+        <v>15.37067947472187</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1024208359340636</v>
+        <v>0.1013427218715998</v>
       </c>
       <c r="W96">
-        <v>0.2116491668867478</v>
+        <v>0.2119033861826768</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3414027864468786</v>
+        <v>0.3378090729053325</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2368757379363158</v>
+        <v>0.2387757379363158</v>
       </c>
       <c r="C97">
-        <v>-3027.054120051847</v>
+        <v>-3081.92859843665</v>
       </c>
       <c r="D97">
-        <v>755.0808799481522</v>
+        <v>747.8194015633502</v>
       </c>
       <c r="E97">
-        <v>3167.435</v>
+        <v>3215.048</v>
       </c>
       <c r="F97">
-        <v>4523.235</v>
+        <v>4570.848</v>
       </c>
       <c r="G97">
         <v>741.1</v>
@@ -9241,37 +9241,37 @@
         <v>360.3</v>
       </c>
       <c r="M97">
-        <v>1066.578813</v>
+        <v>1077.8059584</v>
       </c>
       <c r="N97">
-        <v>-706.2788129999999</v>
+        <v>-717.5059584000001</v>
       </c>
       <c r="O97">
-        <v>-211.8836439</v>
+        <v>-215.25178752</v>
       </c>
       <c r="P97">
-        <v>-494.3951691</v>
+        <v>-502.2541708800001</v>
       </c>
       <c r="Q97">
-        <v>-255.1951691</v>
+        <v>-263.0541708800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7113504212554568</v>
+        <v>0.8777380265693213</v>
       </c>
       <c r="T97">
-        <v>15.37067947472187</v>
+        <v>19.21334934340234</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1013427218715998</v>
+        <v>0.1002870685187706</v>
       </c>
       <c r="W97">
-        <v>0.2119033861826768</v>
+        <v>0.2121523092432739</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3378090729053325</v>
+        <v>0.3342902283959019</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2387757379363157</v>
+        <v>0.2406757379363157</v>
       </c>
       <c r="C98">
-        <v>-3081.928598436648</v>
+        <v>-3136.664742468766</v>
       </c>
       <c r="D98">
-        <v>747.8194015633507</v>
+        <v>740.6962575312332</v>
       </c>
       <c r="E98">
-        <v>3215.047999999999</v>
+        <v>3262.661</v>
       </c>
       <c r="F98">
-        <v>4570.847999999999</v>
+        <v>4618.460999999999</v>
       </c>
       <c r="G98">
         <v>741.1</v>
@@ -9323,37 +9323,37 @@
         <v>360.3</v>
       </c>
       <c r="M98">
-        <v>1077.8059584</v>
+        <v>1089.0331038</v>
       </c>
       <c r="N98">
-        <v>-717.5059583999998</v>
+        <v>-728.7331038</v>
       </c>
       <c r="O98">
-        <v>-215.2517875199999</v>
+        <v>-218.61993114</v>
       </c>
       <c r="P98">
-        <v>-502.2541708799999</v>
+        <v>-510.11317266</v>
       </c>
       <c r="Q98">
-        <v>-263.0541708799999</v>
+        <v>-270.91317266</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8777380265693189</v>
+        <v>1.155050702092425</v>
       </c>
       <c r="T98">
-        <v>19.21334934340229</v>
+        <v>25.61779912453639</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1002870685187706</v>
+        <v>0.09925318121445337</v>
       </c>
       <c r="W98">
-        <v>0.2121523092432739</v>
+        <v>0.2123960998696319</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3342902283959019</v>
+        <v>0.3308439373815112</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2406757379363157</v>
+        <v>0.2425757379363158</v>
       </c>
       <c r="C99">
-        <v>-3136.664742468766</v>
+        <v>-3191.266467845587</v>
       </c>
       <c r="D99">
-        <v>740.6962575312332</v>
+        <v>733.7075321544131</v>
       </c>
       <c r="E99">
-        <v>3262.661</v>
+        <v>3310.274</v>
       </c>
       <c r="F99">
-        <v>4618.460999999999</v>
+        <v>4666.074</v>
       </c>
       <c r="G99">
         <v>741.1</v>
@@ -9405,37 +9405,37 @@
         <v>360.3</v>
       </c>
       <c r="M99">
-        <v>1089.0331038</v>
+        <v>1100.2602492</v>
       </c>
       <c r="N99">
-        <v>-728.7331038</v>
+        <v>-739.9602491999999</v>
       </c>
       <c r="O99">
-        <v>-218.61993114</v>
+        <v>-221.98807476</v>
       </c>
       <c r="P99">
-        <v>-510.11317266</v>
+        <v>-517.9721744399999</v>
       </c>
       <c r="Q99">
-        <v>-270.91317266</v>
+        <v>-278.7721744399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.155050702092425</v>
+        <v>1.709676053138638</v>
       </c>
       <c r="T99">
-        <v>25.61779912453639</v>
+        <v>38.42669868680458</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09925318121445337</v>
+        <v>0.09824039365104058</v>
       </c>
       <c r="W99">
-        <v>0.2123960998696319</v>
+        <v>0.2126349151770847</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3308439373815112</v>
+        <v>0.3274679788368019</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2425757379363158</v>
+        <v>0.2444757379363157</v>
       </c>
       <c r="C100">
-        <v>-3191.266467845587</v>
+        <v>-3245.737543862023</v>
       </c>
       <c r="D100">
-        <v>733.7075321544131</v>
+        <v>726.8494561379763</v>
       </c>
       <c r="E100">
-        <v>3310.274</v>
+        <v>3357.886999999999</v>
       </c>
       <c r="F100">
-        <v>4666.074</v>
+        <v>4713.686999999999</v>
       </c>
       <c r="G100">
         <v>741.1</v>
@@ -9487,37 +9487,37 @@
         <v>360.3</v>
       </c>
       <c r="M100">
-        <v>1100.2602492</v>
+        <v>1111.4873946</v>
       </c>
       <c r="N100">
-        <v>-739.9602491999999</v>
+        <v>-751.1873945999998</v>
       </c>
       <c r="O100">
-        <v>-221.98807476</v>
+        <v>-225.3562183799999</v>
       </c>
       <c r="P100">
-        <v>-517.9721744399999</v>
+        <v>-525.8311762199999</v>
       </c>
       <c r="Q100">
-        <v>-278.7721744399999</v>
+        <v>-286.6311762199999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.709676053138638</v>
+        <v>3.373552106277276</v>
       </c>
       <c r="T100">
-        <v>38.42669868680458</v>
+        <v>76.85339737360916</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09824039365104058</v>
+        <v>0.09724806644244423</v>
       </c>
       <c r="W100">
-        <v>0.2126349151770847</v>
+        <v>0.2128689059328717</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3274679788368019</v>
+        <v>0.324160221474814</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2444757379363157</v>
-      </c>
-      <c r="C101">
-        <v>-3245.737543862023</v>
-      </c>
-      <c r="D101">
-        <v>726.8494561379763</v>
-      </c>
-      <c r="E101">
-        <v>3357.886999999999</v>
-      </c>
-      <c r="F101">
-        <v>4713.686999999999</v>
-      </c>
-      <c r="G101">
-        <v>741.1</v>
-      </c>
-      <c r="H101">
-        <v>3405.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>599.5</v>
-      </c>
-      <c r="K101">
-        <v>239.2</v>
-      </c>
-      <c r="L101">
-        <v>360.3</v>
-      </c>
-      <c r="M101">
-        <v>1111.4873946</v>
-      </c>
-      <c r="N101">
-        <v>-751.1873945999998</v>
-      </c>
-      <c r="O101">
-        <v>-225.3562183799999</v>
-      </c>
-      <c r="P101">
-        <v>-525.8311762199999</v>
-      </c>
-      <c r="Q101">
-        <v>-286.6311762199999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.373552106277276</v>
-      </c>
-      <c r="T101">
-        <v>76.85339737360916</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09724806644244423</v>
-      </c>
-      <c r="W101">
-        <v>0.2128689059328717</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.324160221474814</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
